--- a/palisades_lots/Palisades_Lot_Screen.xlsx
+++ b/palisades_lots/Palisades_Lot_Screen.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Sold Comps" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'All Lots'!$A$2:$AP$137</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'All Lots'!$A$2:$AP$138</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="477">
   <si>
     <t xml:space="preserve">Palisades lots — deal breakdown for the shortlist</t>
   </si>
@@ -914,6 +914,12 @@
   </si>
   <si>
     <t xml:space="preserve">17635 Porto Marina Way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1339 Chautauqua Blvd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-02; no new-house application in LADBS open data (APN 4422006011, 10/2/26)</t>
   </si>
   <si>
     <t xml:space="preserve">Assumptions — change the yellow cells and the whole workbook updates</t>
@@ -2400,27 +2406,27 @@
         <v>9</v>
       </c>
       <c r="B7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>Huntington</v>
       </c>
       <c r="C7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>Huntington</v>
       </c>
       <c r="D7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>Bluffs / El Medio</v>
       </c>
       <c r="E7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>Riviera</v>
       </c>
       <c r="F7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>Riviera</v>
       </c>
       <c r="G7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>Bluffs / El Medio</v>
       </c>
     </row>
@@ -2429,27 +2435,27 @@
         <v>10</v>
       </c>
       <c r="B8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>4375000</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>4495000</v>
       </c>
       <c r="D8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>1395000</v>
       </c>
       <c r="E8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>2795000</v>
       </c>
       <c r="F8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>3750000</v>
       </c>
       <c r="G8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>995000</v>
       </c>
     </row>
@@ -2458,27 +2464,27 @@
         <v>11</v>
       </c>
       <c r="B9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>8008</v>
       </c>
       <c r="C9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>8205</v>
       </c>
       <c r="D9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>5556</v>
       </c>
       <c r="E9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>13724</v>
       </c>
       <c r="F9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>18344</v>
       </c>
       <c r="G9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>4382</v>
       </c>
     </row>
@@ -2487,27 +2493,27 @@
         <v>12</v>
       </c>
       <c r="B10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>Yes</v>
       </c>
       <c r="C10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>Yes</v>
       </c>
       <c r="D10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>Yes</v>
       </c>
       <c r="E10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>No</v>
       </c>
       <c r="F10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>No</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>No</v>
       </c>
     </row>
@@ -2527,27 +2533,27 @@
         <v>14</v>
       </c>
       <c r="B12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>7504</v>
       </c>
       <c r="C12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>7154</v>
       </c>
       <c r="D12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>4270</v>
       </c>
       <c r="E12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>5490</v>
       </c>
       <c r="F12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>7338</v>
       </c>
       <c r="G12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>3315</v>
       </c>
     </row>
@@ -2556,27 +2562,27 @@
         <v>15</v>
       </c>
       <c r="B13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>Approved plans</v>
       </c>
       <c r="C13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>Approved plans</v>
       </c>
       <c r="D13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>Approved plans</v>
       </c>
       <c r="E13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>Zoning estimate</v>
       </c>
       <c r="F13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>Zoning estimate</v>
       </c>
       <c r="G13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>110% old house</v>
       </c>
     </row>
@@ -2585,27 +2591,27 @@
         <v>16</v>
       </c>
       <c r="B14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>2035</v>
       </c>
       <c r="C14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>2035</v>
       </c>
       <c r="D14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>1540</v>
       </c>
       <c r="E14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>2046</v>
       </c>
       <c r="F14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>2046</v>
       </c>
       <c r="G14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>1540</v>
       </c>
     </row>
@@ -2614,27 +2620,27 @@
         <v>17</v>
       </c>
       <c r="B15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>15270640</v>
       </c>
       <c r="C15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>14558390</v>
       </c>
       <c r="D15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>6575800</v>
       </c>
       <c r="E15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>11232540</v>
       </c>
       <c r="F15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>15013548</v>
       </c>
       <c r="G15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>5105100</v>
       </c>
     </row>
@@ -2654,27 +2660,27 @@
         <v>19</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>4375000</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>4495000</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>1395000</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>2795000</v>
       </c>
       <c r="F17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>3750000</v>
       </c>
       <c r="G17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>995000</v>
       </c>
     </row>
@@ -2683,27 +2689,27 @@
         <v>20</v>
       </c>
       <c r="B18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>5252800</v>
       </c>
       <c r="C18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>5007800</v>
       </c>
       <c r="D18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>2989000</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>3843000</v>
       </c>
       <c r="F18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>5136600</v>
       </c>
       <c r="G18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>2320500</v>
       </c>
     </row>
@@ -2712,27 +2718,27 @@
         <v>21</v>
       </c>
       <c r="B19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>218750</v>
       </c>
       <c r="C19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>224750</v>
       </c>
       <c r="D19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>69750</v>
       </c>
       <c r="E19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>411750</v>
       </c>
       <c r="F19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>550350</v>
       </c>
       <c r="G19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>248625</v>
       </c>
     </row>
@@ -2741,27 +2747,27 @@
         <v>22</v>
       </c>
       <c r="B20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>864034.7625</v>
       </c>
       <c r="C20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>853592.5125</v>
       </c>
       <c r="D20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>390816.5625</v>
       </c>
       <c r="E20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>893555.8125</v>
       </c>
       <c r="F20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>1196133.4125</v>
       </c>
       <c r="G20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>312751.96875</v>
       </c>
     </row>
@@ -2770,27 +2776,27 @@
         <v>23</v>
       </c>
       <c r="B21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>105000</v>
       </c>
       <c r="C21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>107880</v>
       </c>
       <c r="D21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>33480</v>
       </c>
       <c r="E21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>100620</v>
       </c>
       <c r="F21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>135000</v>
       </c>
       <c r="G21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>23880</v>
       </c>
     </row>
@@ -2799,27 +2805,27 @@
         <v>24</v>
       </c>
       <c r="B22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>619987.984</v>
       </c>
       <c r="C22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>591070.634</v>
       </c>
       <c r="D22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>266977.48</v>
       </c>
       <c r="E22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>456041.124</v>
       </c>
       <c r="F22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>609550.0488</v>
       </c>
       <c r="G22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>207267.06</v>
       </c>
     </row>
@@ -2828,27 +2834,27 @@
         <v>25</v>
       </c>
       <c r="B23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>839885.2</v>
       </c>
       <c r="C23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>800711.45</v>
       </c>
       <c r="D23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>263032</v>
       </c>
       <c r="E23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>617789.7</v>
       </c>
       <c r="F23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>825745.14</v>
       </c>
       <c r="G23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -2857,27 +2863,27 @@
         <v>26</v>
       </c>
       <c r="B24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>12275457.9465</v>
       </c>
       <c r="C24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>12080804.5965</v>
       </c>
       <c r="D24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>5408056.0425</v>
       </c>
       <c r="E24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>9117756.6365</v>
       </c>
       <c r="F24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>12203378.6013</v>
       </c>
       <c r="G24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>4108024.02875</v>
       </c>
     </row>
@@ -2897,27 +2903,27 @@
         <v>28</v>
       </c>
       <c r="B26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>2995182.0535</v>
       </c>
       <c r="C26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>2477585.4035</v>
       </c>
       <c r="D26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>1167743.9575</v>
       </c>
       <c r="E26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>2114783.3635</v>
       </c>
       <c r="F26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>2810169.3987</v>
       </c>
       <c r="G26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>997075.971250001</v>
       </c>
     </row>
@@ -2926,27 +2932,27 @@
         <v>29</v>
       </c>
       <c r="B27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.243997581723947</v>
       </c>
       <c r="C27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.205084469640192</v>
       </c>
       <c r="D27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.215926748599333</v>
       </c>
       <c r="E27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.231941194288313</v>
       </c>
       <c r="F27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.230277982066429</v>
       </c>
       <c r="G27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.242714250031637</v>
       </c>
     </row>
@@ -2955,27 +2961,27 @@
         <v>30</v>
       </c>
       <c r="B28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>5235412.63985109</v>
       </c>
       <c r="C28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>4991223.61746998</v>
       </c>
       <c r="D28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>1660861.37056886</v>
       </c>
       <c r="E28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>3353735.28312752</v>
       </c>
       <c r="F28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>4482642.89755733</v>
       </c>
       <c r="G28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>1292902.73222788</v>
       </c>
     </row>
@@ -2984,27 +2990,27 @@
         <v>31</v>
       </c>
       <c r="B29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.835655238843683</v>
       </c>
       <c r="C29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.900580768264294</v>
       </c>
       <c r="D29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.839925610120129</v>
       </c>
       <c r="E29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.833399109960023</v>
       </c>
       <c r="F29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.836560057470436</v>
       </c>
       <c r="G29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>0.769586122140412</v>
       </c>
     </row>
@@ -3024,27 +3030,27 @@
         <v>33</v>
       </c>
       <c r="B31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>1850</v>
       </c>
       <c r="C31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>1850</v>
       </c>
       <c r="D31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>1400</v>
       </c>
       <c r="E31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>1860</v>
       </c>
       <c r="F31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>1860</v>
       </c>
       <c r="G31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>1400</v>
       </c>
     </row>
@@ -3053,27 +3059,27 @@
         <v>34</v>
       </c>
       <c r="B32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>1739657.7975</v>
       </c>
       <c r="C32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>1280621.0475</v>
       </c>
       <c r="D32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>618126.6375</v>
       </c>
       <c r="E32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>1344435.3475</v>
       </c>
       <c r="F32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>1575782.7795</v>
       </c>
       <c r="G32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>551818.43125</v>
       </c>
     </row>
@@ -3082,27 +3088,27 @@
         <v>35</v>
       </c>
       <c r="B33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>2035</v>
       </c>
       <c r="C33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>2035</v>
       </c>
       <c r="D33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>1540</v>
       </c>
       <c r="E33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>2046</v>
       </c>
       <c r="F33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>2046</v>
       </c>
       <c r="G33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>1540</v>
       </c>
     </row>
@@ -3111,27 +3117,27 @@
         <v>36</v>
       </c>
       <c r="B34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>2995182.0535</v>
       </c>
       <c r="C34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>2477585.4035</v>
       </c>
       <c r="D34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>1167743.9575</v>
       </c>
       <c r="E34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>2114783.3635</v>
       </c>
       <c r="F34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>2810169.3987</v>
       </c>
       <c r="G34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>997075.971250001</v>
       </c>
     </row>
@@ -3140,27 +3146,27 @@
         <v>37</v>
       </c>
       <c r="B35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>2220</v>
       </c>
       <c r="C35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>2220</v>
       </c>
       <c r="D35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>1680</v>
       </c>
       <c r="E35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>2232</v>
       </c>
       <c r="F35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>2232</v>
       </c>
       <c r="G35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>1680</v>
       </c>
     </row>
@@ -3169,27 +3175,27 @@
         <v>38</v>
       </c>
       <c r="B36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$137,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>4250706.3095</v>
       </c>
       <c r="C36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$137,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
         <v>3674549.7595</v>
       </c>
       <c r="D36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$137,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
         <v>1717361.2775</v>
       </c>
       <c r="E36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$137,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
         <v>3038302.3795</v>
       </c>
       <c r="F36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$137,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
         <v>4044556.0179</v>
       </c>
       <c r="G36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$137,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$137,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
         <v>1219565.51125</v>
       </c>
     </row>
@@ -3311,7 +3317,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AP137"/>
+  <dimension ref="A1:AP138"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -24514,8 +24520,164 @@
         <v>1461313.75</v>
       </c>
     </row>
+    <row r="138" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="40" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="C138" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D138" s="41" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="E138" s="42" t="n">
+        <v>8490</v>
+      </c>
+      <c r="F138" s="42" t="n">
+        <v>4204</v>
+      </c>
+      <c r="G138" s="42"/>
+      <c r="H138" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="I138" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="J138" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K138" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="L138" s="45" t="n">
+        <f aca="false">IF(AO138&gt;AN138,AM138,AL138)</f>
+        <v>4624</v>
+      </c>
+      <c r="M138" s="40" t="str">
+        <f aca="false">IF(AO138&gt;AN138,"Zoning estimate",IF(H138="Yes","Approved plans",IF(G138&gt;0,"Listing claim","110% old house")))</f>
+        <v>110% old house</v>
+      </c>
+      <c r="N138" s="45" t="n">
+        <f aca="false">IF(AO138&gt;AN138,IF(AM138&gt;AL138,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O138" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK138,Assumptions!$A$36:$A$48,0))+IF(I138="Yes",Assumptions!$B$23,0)+IF(J138="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1430</v>
+      </c>
+      <c r="P138" s="47" t="n">
+        <f aca="false">L138*O138</f>
+        <v>6612320</v>
+      </c>
+      <c r="Q138" s="47" t="n">
+        <f aca="false">D138</f>
+        <v>2750000</v>
+      </c>
+      <c r="R138" s="47" t="n">
+        <f aca="false">L138*Assumptions!$B$4</f>
+        <v>3236800</v>
+      </c>
+      <c r="S138" s="47" t="n">
+        <f aca="false">IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5)</f>
+        <v>346800</v>
+      </c>
+      <c r="T138" s="47" t="n">
+        <f aca="false">AP138*(Assumptions!$B$8*N138*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>555773.4</v>
+      </c>
+      <c r="U138" s="47" t="n">
+        <f aca="false">Q138*Assumptions!$B$11*N138</f>
+        <v>66000</v>
+      </c>
+      <c r="V138" s="47" t="n">
+        <f aca="false">P138*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>268460.192</v>
+      </c>
+      <c r="W138" s="47" t="n">
+        <f aca="false">P138*IF(P138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>264492.8</v>
+      </c>
+      <c r="X138" s="48" t="n">
+        <f aca="false">SUM(Q138:W138)</f>
+        <v>7488326.392</v>
+      </c>
+      <c r="Y138" s="48" t="n">
+        <f aca="false">P138-X138</f>
+        <v>-876006.391999999</v>
+      </c>
+      <c r="Z138" s="49" t="n">
+        <f aca="false">IF(X138=0,0,Y138/X138)</f>
+        <v>-0.116982933988543</v>
+      </c>
+      <c r="AA138" s="47" t="n">
+        <f aca="false">MAX(0,(P138/(1+Assumptions!$B$27)-(L138*(Assumptions!$B$4+IF(H138="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N138*Assumptions!$B$9+Assumptions!$B$10)))-P138*(Assumptions!$B$12+Assumptions!$B$13+IF(P138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H138="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N138*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N138))</f>
+        <v>1186264.5255326</v>
+      </c>
+      <c r="AB138" s="50" t="n">
+        <f aca="false">IF(AA138&lt;=0,"no price works",D138/AA138)</f>
+        <v>2.31820132930749</v>
+      </c>
+      <c r="AC138" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK138,Assumptions!$A$36:$A$48,0))+IF(I138="Yes",Assumptions!$B$23,0)+IF(J138="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1300</v>
+      </c>
+      <c r="AD138" s="47" t="n">
+        <f aca="false">(L138)*AC138-(((D138)+(L138)*Assumptions!$B$4+IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N138)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(N138)+(L138)*AC138*(Assumptions!$B$12+Assumptions!$B$13+IF((L138)*AC138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L138)*AC138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1428676.12</v>
+      </c>
+      <c r="AE138" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK138,Assumptions!$A$36:$A$48,0))+IF(I138="Yes",Assumptions!$B$23,0)+IF(J138="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1430</v>
+      </c>
+      <c r="AF138" s="47" t="n">
+        <f aca="false">(L138)*AE138-(((D138)+(L138)*Assumptions!$B$4+IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N138)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(N138)+(L138)*AE138*(Assumptions!$B$12+Assumptions!$B$13+IF((L138)*AE138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L138)*AE138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-876006.392</v>
+      </c>
+      <c r="AG138" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK138,Assumptions!$A$36:$A$48,0))+IF(I138="Yes",Assumptions!$B$23,0)+IF(J138="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1560</v>
+      </c>
+      <c r="AH138" s="47" t="n">
+        <f aca="false">(L138)*AG138-(((D138)+(L138)*Assumptions!$B$4+IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N138)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(N138)+(L138)*AG138*(Assumptions!$B$12+Assumptions!$B$13+IF((L138)*AG138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L138)*AG138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-323336.664000001</v>
+      </c>
+      <c r="AI138" s="47" t="n">
+        <f aca="false">(L138)*AE138-(((D138)+(L138)*Assumptions!$B$25+IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N138)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(N138)+(L138)*AE138*(Assumptions!$B$12+Assumptions!$B$13+IF((L138)*AE138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L138)*AE138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-624518.591999999</v>
+      </c>
+      <c r="AJ138" s="47" t="n">
+        <f aca="false">(L138)*AE138-(((D138)+(L138)*Assumptions!$B$26+IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N138)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(N138)+(L138)*AE138*(Assumptions!$B$12+Assumptions!$B$13+IF((L138)*AE138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L138)*AE138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-373030.791999999</v>
+      </c>
+      <c r="AK138" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL138" s="45" t="n">
+        <f aca="false">IF(G138&gt;0,G138,ROUND(F138*Assumptions!$B$18,0))</f>
+        <v>4624</v>
+      </c>
+      <c r="AM138" s="45" t="n">
+        <f aca="false">IF(H138="Yes",AL138,MAX(AL138,MIN(Assumptions!$B$20,ROUND(E138*Assumptions!$B$19,0))))</f>
+        <v>4624</v>
+      </c>
+      <c r="AN138" s="47" t="n">
+        <f aca="false">(AL138)*AE138-(((D138)+(AL138)*Assumptions!$B$4+IF(H138="Yes",Assumptions!$B$6*(D138),(AL138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(Assumptions!$B$21)+(AL138)*AE138*(Assumptions!$B$12+Assumptions!$B$13+IF((AL138)*AE138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL138)*AE138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-876006.392</v>
+      </c>
+      <c r="AO138" s="47" t="n">
+        <f aca="false">(AM138)*AE138-(((D138)+(AM138)*Assumptions!$B$4+IF(H138="Yes",Assumptions!$B$6*(D138),(AM138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM138&gt;AL138,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(IF(AM138&gt;AL138,Assumptions!$B$22,Assumptions!$B$21))+(AM138)*AE138*(Assumptions!$B$12+Assumptions!$B$13+IF((AM138)*AE138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM138)*AE138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-876006.392</v>
+      </c>
+      <c r="AP138" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q138+R138+S138)</f>
+        <v>4116840</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AP137"/>
+  <autoFilter ref="A2:AP138"/>
   <mergeCells count="6">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="L1:P1"/>
@@ -24524,7 +24686,7 @@
     <mergeCell ref="AC1:AJ1"/>
     <mergeCell ref="AK1:AP1"/>
   </mergeCells>
-  <conditionalFormatting sqref="AB3:AB137">
+  <conditionalFormatting sqref="AB3:AB138">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(AB3),AB3&lt;=1)</formula>
     </cfRule>
@@ -24558,342 +24720,342 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="51" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B4" s="52" t="n">
         <v>700</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B5" s="52" t="n">
         <v>75</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B6" s="53" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B7" s="53" t="n">
         <v>0.65</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B8" s="53" t="n">
         <v>0.1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B9" s="53" t="n">
         <v>0.6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B10" s="53" t="n">
         <v>0.015</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B11" s="53" t="n">
         <v>0.012</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B12" s="53" t="n">
         <v>0.035</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B13" s="53" t="n">
         <v>0.0056</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B14" s="52" t="n">
         <v>5400000</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B15" s="53" t="n">
         <v>0.04</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B16" s="52" t="n">
         <v>10900000</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B17" s="53" t="n">
         <v>0.055</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B18" s="54" t="n">
         <v>1.1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B19" s="54" t="n">
         <v>0.4</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B20" s="55" t="n">
         <v>8000</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B21" s="55" t="n">
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B22" s="55" t="n">
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B23" s="52" t="n">
         <v>100</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B24" s="52" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B25" s="52" t="n">
         <v>650</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B26" s="52" t="n">
         <v>600</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B27" s="53" t="n">
         <v>0.15</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B28" s="53" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B29" s="53" t="n">
         <v>0.1</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B30" s="53" t="n">
         <v>0.2</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="57" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="51" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C35" s="51" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24904,7 +25066,7 @@
         <v>1860</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24915,18 +25077,18 @@
         <v>1850</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B38" s="52" t="n">
         <v>1750</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24937,7 +25099,7 @@
         <v>1400</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24948,7 +25110,7 @@
         <v>1400</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24959,7 +25121,7 @@
         <v>1300</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24970,7 +25132,7 @@
         <v>1250</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24981,7 +25143,7 @@
         <v>1250</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24992,7 +25154,7 @@
         <v>1250</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25003,7 +25165,7 @@
         <v>1200</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25014,7 +25176,7 @@
         <v>1000</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25025,7 +25187,7 @@
         <v>900</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25036,7 +25198,7 @@
         <v>900</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -25071,12 +25233,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="51" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B2" s="51" t="s">
         <v>49</v>
@@ -25085,30 +25247,30 @@
         <v>9</v>
       </c>
       <c r="D2" s="51" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G2" s="51" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H2" s="51" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I2" s="51" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>126</v>
@@ -25126,18 +25288,18 @@
         <v>2026</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>75</v>
@@ -25155,18 +25317,18 @@
         <v>2014</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>75</v>
@@ -25184,18 +25346,18 @@
         <v>2018</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>70</v>
@@ -25213,18 +25375,18 @@
         <v>2021</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>79</v>
@@ -25242,21 +25404,21 @@
         <v>2013</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D8" s="58" t="n">
         <v>9735000</v>
@@ -25271,18 +25433,18 @@
         <v>2012</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>202</v>
@@ -25300,18 +25462,18 @@
         <v>2020</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>202</v>
@@ -25329,18 +25491,18 @@
         <v>2016</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>70</v>
@@ -25358,18 +25520,18 @@
         <v>2025</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>70</v>
@@ -25387,18 +25549,18 @@
         <v>2021</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>70</v>
@@ -25416,18 +25578,18 @@
         <v>2022</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>75</v>
@@ -25445,18 +25607,18 @@
         <v>2020</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>202</v>
@@ -25474,18 +25636,18 @@
         <v>2015</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>117</v>
@@ -25503,18 +25665,18 @@
         <v>2010</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>117</v>
@@ -25532,18 +25694,18 @@
         <v>2019</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>70</v>
@@ -25561,18 +25723,18 @@
         <v>2020</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>70</v>
@@ -25590,18 +25752,18 @@
         <v>2023</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>70</v>
@@ -25619,18 +25781,18 @@
         <v>2019</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>126</v>
@@ -25648,18 +25810,18 @@
         <v>2019</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>70</v>
@@ -25677,18 +25839,18 @@
         <v>2013</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>79</v>
@@ -25706,10 +25868,10 @@
         <v>2017</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25725,7 +25887,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -25738,7 +25900,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="60" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B26" s="60" t="s">
         <v>49</v>
@@ -25747,33 +25909,33 @@
         <v>9</v>
       </c>
       <c r="D26" s="60" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E26" s="60" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F26" s="60" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G26" s="60" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H26" s="60" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I26" s="60" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D27" s="58" t="n">
         <v>9990000</v>
@@ -25785,24 +25947,24 @@
         <v>1523</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D28" s="58" t="n">
         <v>4295000</v>
@@ -25814,22 +25976,22 @@
         <v>1387</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D29" s="58" t="n">
         <v>5495000</v>
@@ -25841,24 +26003,24 @@
         <v>1390</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H29" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D30" s="58" t="n">
         <v>4995000</v>
@@ -25870,24 +26032,24 @@
         <v>1362</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D31" s="58" t="n">
         <v>13995000</v>
@@ -25899,24 +26061,24 @@
         <v>2149</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D32" s="58" t="n">
         <v>5995000</v>
@@ -25928,13 +26090,13 @@
         <v>1389</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/palisades_lots/Palisades_Lot_Screen.xlsx
+++ b/palisades_lots/Palisades_Lot_Screen.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Sold Comps" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'All Lots'!$A$2:$AP$138</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'All Lots'!$A$2:$AP$145</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="491">
   <si>
     <t xml:space="preserve">Palisades lots — deal breakdown for the shortlist</t>
   </si>
@@ -920,6 +920,48 @@
   </si>
   <si>
     <t xml:space="preserve">new listing 2026-10-02; no new-house application in LADBS open data (APN 4422006011, 10/2/26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16640 Linda Ter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-05; no new-house application in LADBS open data (APN 4419014016, 10/5/26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16778 Edgar St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-05; LADBS 25010-30000-02133: PERMIT ISSUED 6/3/26, 3,455 sf (open-data square_footage 3,454.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">717 Via De La Paz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-05; LADBS 25010-10000-06355: plan check approved 3/13/26, 3,579 sf (open-data square_footage; permit report shows no size); 456 sf ADU 25010-10000-06357 also approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">906 Kagawa St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-05; no new-house application in LADBS open data (APN 4423023002, 10/5/26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1115 Via De La Paz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-05; LADBS 25010-30000-01756: new-house application, verifications in progress 9/25/26, not approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16661 Cumbre Verde Ct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-05; no new-house application in LADBS open data (APN 4431033021, 10/5/26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15241 Via de las Olas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bluff-front; relisted 10/2/26 after leaving listings 10/1 (Redfin history); no new-house application in LADBS open data (APN 4412025006, 10/5/26)</t>
   </si>
   <si>
     <t xml:space="preserve">Assumptions — change the yellow cells and the whole workbook updates</t>
@@ -2406,27 +2448,27 @@
         <v>9</v>
       </c>
       <c r="B7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>Huntington</v>
       </c>
       <c r="C7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>Huntington</v>
       </c>
       <c r="D7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>Bluffs / El Medio</v>
       </c>
       <c r="E7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>Riviera</v>
       </c>
       <c r="F7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>Riviera</v>
       </c>
       <c r="G7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>Bluffs / El Medio</v>
       </c>
     </row>
@@ -2435,27 +2477,27 @@
         <v>10</v>
       </c>
       <c r="B8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>4375000</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>4495000</v>
       </c>
       <c r="D8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>1395000</v>
       </c>
       <c r="E8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>2795000</v>
       </c>
       <c r="F8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>3750000</v>
       </c>
       <c r="G8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>995000</v>
       </c>
     </row>
@@ -2464,27 +2506,27 @@
         <v>11</v>
       </c>
       <c r="B9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>8008</v>
       </c>
       <c r="C9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>8205</v>
       </c>
       <c r="D9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>5556</v>
       </c>
       <c r="E9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>13724</v>
       </c>
       <c r="F9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>18344</v>
       </c>
       <c r="G9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>4382</v>
       </c>
     </row>
@@ -2493,27 +2535,27 @@
         <v>12</v>
       </c>
       <c r="B10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>Yes</v>
       </c>
       <c r="C10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>Yes</v>
       </c>
       <c r="D10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>Yes</v>
       </c>
       <c r="E10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>No</v>
       </c>
       <c r="F10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>No</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>No</v>
       </c>
     </row>
@@ -2533,27 +2575,27 @@
         <v>14</v>
       </c>
       <c r="B12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>7504</v>
       </c>
       <c r="C12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>7154</v>
       </c>
       <c r="D12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>4270</v>
       </c>
       <c r="E12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>5490</v>
       </c>
       <c r="F12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>7338</v>
       </c>
       <c r="G12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>3315</v>
       </c>
     </row>
@@ -2562,27 +2604,27 @@
         <v>15</v>
       </c>
       <c r="B13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>Approved plans</v>
       </c>
       <c r="C13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>Approved plans</v>
       </c>
       <c r="D13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>Approved plans</v>
       </c>
       <c r="E13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>Zoning estimate</v>
       </c>
       <c r="F13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>Zoning estimate</v>
       </c>
       <c r="G13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>110% old house</v>
       </c>
     </row>
@@ -2591,27 +2633,27 @@
         <v>16</v>
       </c>
       <c r="B14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>2035</v>
       </c>
       <c r="C14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>2035</v>
       </c>
       <c r="D14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>1540</v>
       </c>
       <c r="E14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>2046</v>
       </c>
       <c r="F14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>2046</v>
       </c>
       <c r="G14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>1540</v>
       </c>
     </row>
@@ -2620,27 +2662,27 @@
         <v>17</v>
       </c>
       <c r="B15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>15270640</v>
       </c>
       <c r="C15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>14558390</v>
       </c>
       <c r="D15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>6575800</v>
       </c>
       <c r="E15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>11232540</v>
       </c>
       <c r="F15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>15013548</v>
       </c>
       <c r="G15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>5105100</v>
       </c>
     </row>
@@ -2660,27 +2702,27 @@
         <v>19</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>4375000</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>4495000</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>1395000</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>2795000</v>
       </c>
       <c r="F17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>3750000</v>
       </c>
       <c r="G17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>995000</v>
       </c>
     </row>
@@ -2689,27 +2731,27 @@
         <v>20</v>
       </c>
       <c r="B18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>5252800</v>
       </c>
       <c r="C18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>5007800</v>
       </c>
       <c r="D18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>2989000</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>3843000</v>
       </c>
       <c r="F18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>5136600</v>
       </c>
       <c r="G18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>2320500</v>
       </c>
     </row>
@@ -2718,27 +2760,27 @@
         <v>21</v>
       </c>
       <c r="B19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>218750</v>
       </c>
       <c r="C19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>224750</v>
       </c>
       <c r="D19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>69750</v>
       </c>
       <c r="E19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>411750</v>
       </c>
       <c r="F19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>550350</v>
       </c>
       <c r="G19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>248625</v>
       </c>
     </row>
@@ -2747,27 +2789,27 @@
         <v>22</v>
       </c>
       <c r="B20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>864034.7625</v>
       </c>
       <c r="C20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>853592.5125</v>
       </c>
       <c r="D20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>390816.5625</v>
       </c>
       <c r="E20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>893555.8125</v>
       </c>
       <c r="F20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>1196133.4125</v>
       </c>
       <c r="G20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>312751.96875</v>
       </c>
     </row>
@@ -2776,27 +2818,27 @@
         <v>23</v>
       </c>
       <c r="B21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>105000</v>
       </c>
       <c r="C21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>107880</v>
       </c>
       <c r="D21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>33480</v>
       </c>
       <c r="E21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>100620</v>
       </c>
       <c r="F21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>135000</v>
       </c>
       <c r="G21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>23880</v>
       </c>
     </row>
@@ -2805,27 +2847,27 @@
         <v>24</v>
       </c>
       <c r="B22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>619987.984</v>
       </c>
       <c r="C22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>591070.634</v>
       </c>
       <c r="D22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>266977.48</v>
       </c>
       <c r="E22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>456041.124</v>
       </c>
       <c r="F22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>609550.0488</v>
       </c>
       <c r="G22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>207267.06</v>
       </c>
     </row>
@@ -2834,27 +2876,27 @@
         <v>25</v>
       </c>
       <c r="B23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>839885.2</v>
       </c>
       <c r="C23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>800711.45</v>
       </c>
       <c r="D23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>263032</v>
       </c>
       <c r="E23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>617789.7</v>
       </c>
       <c r="F23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>825745.14</v>
       </c>
       <c r="G23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -2863,27 +2905,27 @@
         <v>26</v>
       </c>
       <c r="B24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>12275457.9465</v>
       </c>
       <c r="C24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>12080804.5965</v>
       </c>
       <c r="D24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>5408056.0425</v>
       </c>
       <c r="E24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>9117756.6365</v>
       </c>
       <c r="F24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>12203378.6013</v>
       </c>
       <c r="G24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>4108024.02875</v>
       </c>
     </row>
@@ -2903,27 +2945,27 @@
         <v>28</v>
       </c>
       <c r="B26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>2995182.0535</v>
       </c>
       <c r="C26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>2477585.4035</v>
       </c>
       <c r="D26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>1167743.9575</v>
       </c>
       <c r="E26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>2114783.3635</v>
       </c>
       <c r="F26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>2810169.3987</v>
       </c>
       <c r="G26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>997075.971250001</v>
       </c>
     </row>
@@ -2932,27 +2974,27 @@
         <v>29</v>
       </c>
       <c r="B27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.243997581723947</v>
       </c>
       <c r="C27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.205084469640192</v>
       </c>
       <c r="D27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.215926748599333</v>
       </c>
       <c r="E27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.231941194288313</v>
       </c>
       <c r="F27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.230277982066429</v>
       </c>
       <c r="G27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.242714250031637</v>
       </c>
     </row>
@@ -2961,27 +3003,27 @@
         <v>30</v>
       </c>
       <c r="B28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>5235412.63985109</v>
       </c>
       <c r="C28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>4991223.61746998</v>
       </c>
       <c r="D28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>1660861.37056886</v>
       </c>
       <c r="E28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>3353735.28312752</v>
       </c>
       <c r="F28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>4482642.89755733</v>
       </c>
       <c r="G28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>1292902.73222788</v>
       </c>
     </row>
@@ -2990,27 +3032,27 @@
         <v>31</v>
       </c>
       <c r="B29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.835655238843683</v>
       </c>
       <c r="C29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.900580768264294</v>
       </c>
       <c r="D29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.839925610120129</v>
       </c>
       <c r="E29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.833399109960023</v>
       </c>
       <c r="F29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.836560057470436</v>
       </c>
       <c r="G29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>0.769586122140412</v>
       </c>
     </row>
@@ -3030,27 +3072,27 @@
         <v>33</v>
       </c>
       <c r="B31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>1850</v>
       </c>
       <c r="C31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>1850</v>
       </c>
       <c r="D31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>1400</v>
       </c>
       <c r="E31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>1860</v>
       </c>
       <c r="F31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>1860</v>
       </c>
       <c r="G31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>1400</v>
       </c>
     </row>
@@ -3059,27 +3101,27 @@
         <v>34</v>
       </c>
       <c r="B32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>1739657.7975</v>
       </c>
       <c r="C32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>1280621.0475</v>
       </c>
       <c r="D32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>618126.6375</v>
       </c>
       <c r="E32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>1344435.3475</v>
       </c>
       <c r="F32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>1575782.7795</v>
       </c>
       <c r="G32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>551818.43125</v>
       </c>
     </row>
@@ -3088,27 +3130,27 @@
         <v>35</v>
       </c>
       <c r="B33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>2035</v>
       </c>
       <c r="C33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>2035</v>
       </c>
       <c r="D33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>1540</v>
       </c>
       <c r="E33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>2046</v>
       </c>
       <c r="F33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>2046</v>
       </c>
       <c r="G33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>1540</v>
       </c>
     </row>
@@ -3117,27 +3159,27 @@
         <v>36</v>
       </c>
       <c r="B34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>2995182.0535</v>
       </c>
       <c r="C34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>2477585.4035</v>
       </c>
       <c r="D34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>1167743.9575</v>
       </c>
       <c r="E34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>2114783.3635</v>
       </c>
       <c r="F34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>2810169.3987</v>
       </c>
       <c r="G34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>997075.971250001</v>
       </c>
     </row>
@@ -3146,27 +3188,27 @@
         <v>37</v>
       </c>
       <c r="B35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>2220</v>
       </c>
       <c r="C35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>2220</v>
       </c>
       <c r="D35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>1680</v>
       </c>
       <c r="E35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>2232</v>
       </c>
       <c r="F35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>2232</v>
       </c>
       <c r="G35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>1680</v>
       </c>
     </row>
@@ -3175,27 +3217,27 @@
         <v>38</v>
       </c>
       <c r="B36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$145,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>4250706.3095</v>
       </c>
       <c r="C36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$145,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$145,0))</f>
         <v>3674549.7595</v>
       </c>
       <c r="D36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$145,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$145,0))</f>
         <v>1717361.2775</v>
       </c>
       <c r="E36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$145,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$145,0))</f>
         <v>3038302.3795</v>
       </c>
       <c r="F36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$145,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$145,0))</f>
         <v>4044556.0179</v>
       </c>
       <c r="G36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$138,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$138,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$145,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$145,0))</f>
         <v>1219565.51125</v>
       </c>
     </row>
@@ -3317,7 +3359,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AP138"/>
+  <dimension ref="A1:AP145"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -24676,8 +24718,1104 @@
         <v>4116840</v>
       </c>
     </row>
+    <row r="139" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="40" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="40" t="s">
+        <v>298</v>
+      </c>
+      <c r="C139" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D139" s="41" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="E139" s="42" t="n">
+        <v>7455</v>
+      </c>
+      <c r="F139" s="42" t="n">
+        <v>4695</v>
+      </c>
+      <c r="G139" s="42"/>
+      <c r="H139" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="I139" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J139" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K139" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="L139" s="45" t="n">
+        <f aca="false">IF(AO139&gt;AN139,AM139,AL139)</f>
+        <v>5165</v>
+      </c>
+      <c r="M139" s="40" t="str">
+        <f aca="false">IF(AO139&gt;AN139,"Zoning estimate",IF(H139="Yes","Approved plans",IF(G139&gt;0,"Listing claim","110% old house")))</f>
+        <v>110% old house</v>
+      </c>
+      <c r="N139" s="45" t="n">
+        <f aca="false">IF(AO139&gt;AN139,IF(AM139&gt;AL139,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O139" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK139,Assumptions!$A$36:$A$48,0))+IF(I139="Yes",Assumptions!$B$23,0)+IF(J139="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1485</v>
+      </c>
+      <c r="P139" s="47" t="n">
+        <f aca="false">L139*O139</f>
+        <v>7670025</v>
+      </c>
+      <c r="Q139" s="47" t="n">
+        <f aca="false">D139</f>
+        <v>1750000</v>
+      </c>
+      <c r="R139" s="47" t="n">
+        <f aca="false">L139*Assumptions!$B$4</f>
+        <v>3615500</v>
+      </c>
+      <c r="S139" s="47" t="n">
+        <f aca="false">IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5)</f>
+        <v>387375</v>
+      </c>
+      <c r="T139" s="47" t="n">
+        <f aca="false">AP139*(Assumptions!$B$8*N139*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>504814.78125</v>
+      </c>
+      <c r="U139" s="47" t="n">
+        <f aca="false">Q139*Assumptions!$B$11*N139</f>
+        <v>42000</v>
+      </c>
+      <c r="V139" s="47" t="n">
+        <f aca="false">P139*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>311403.015</v>
+      </c>
+      <c r="W139" s="47" t="n">
+        <f aca="false">P139*IF(P139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>306801</v>
+      </c>
+      <c r="X139" s="48" t="n">
+        <f aca="false">SUM(Q139:W139)</f>
+        <v>6917893.79625</v>
+      </c>
+      <c r="Y139" s="48" t="n">
+        <f aca="false">P139-X139</f>
+        <v>752131.20375</v>
+      </c>
+      <c r="Z139" s="49" t="n">
+        <f aca="false">IF(X139=0,0,Y139/X139)</f>
+        <v>0.108722571623998</v>
+      </c>
+      <c r="AA139" s="47" t="n">
+        <f aca="false">MAX(0,(P139/(1+Assumptions!$B$27)-(L139*(Assumptions!$B$4+IF(H139="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N139*Assumptions!$B$9+Assumptions!$B$10)))-P139*(Assumptions!$B$12+Assumptions!$B$13+IF(P139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H139="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N139*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N139))</f>
+        <v>1526652.26918978</v>
+      </c>
+      <c r="AB139" s="50" t="n">
+        <f aca="false">IF(AA139&lt;=0,"no price works",D139/AA139)</f>
+        <v>1.14629901996527</v>
+      </c>
+      <c r="AC139" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK139,Assumptions!$A$36:$A$48,0))+IF(I139="Yes",Assumptions!$B$23,0)+IF(J139="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1350</v>
+      </c>
+      <c r="AD139" s="47" t="n">
+        <f aca="false">(L139)*AC139-(((D139)+(L139)*Assumptions!$B$4+IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N139)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(N139)+(L139)*AC139*(Assumptions!$B$12+Assumptions!$B$13+IF((L139)*AC139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L139)*AC139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>111056.56875</v>
+      </c>
+      <c r="AE139" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK139,Assumptions!$A$36:$A$48,0))+IF(I139="Yes",Assumptions!$B$23,0)+IF(J139="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1485</v>
+      </c>
+      <c r="AF139" s="47" t="n">
+        <f aca="false">(L139)*AE139-(((D139)+(L139)*Assumptions!$B$4+IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N139)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(N139)+(L139)*AE139*(Assumptions!$B$12+Assumptions!$B$13+IF((L139)*AE139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L139)*AE139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>752131.20375</v>
+      </c>
+      <c r="AG139" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK139,Assumptions!$A$36:$A$48,0))+IF(I139="Yes",Assumptions!$B$23,0)+IF(J139="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1620</v>
+      </c>
+      <c r="AH139" s="47" t="n">
+        <f aca="false">(L139)*AG139-(((D139)+(L139)*Assumptions!$B$4+IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N139)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(N139)+(L139)*AG139*(Assumptions!$B$12+Assumptions!$B$13+IF((L139)*AG139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L139)*AG139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>1393205.83875</v>
+      </c>
+      <c r="AI139" s="47" t="n">
+        <f aca="false">(L139)*AE139-(((D139)+(L139)*Assumptions!$B$25+IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N139)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(N139)+(L139)*AE139*(Assumptions!$B$12+Assumptions!$B$13+IF((L139)*AE139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L139)*AE139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>1033042.64125</v>
+      </c>
+      <c r="AJ139" s="47" t="n">
+        <f aca="false">(L139)*AE139-(((D139)+(L139)*Assumptions!$B$26+IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N139)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(N139)+(L139)*AE139*(Assumptions!$B$12+Assumptions!$B$13+IF((L139)*AE139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L139)*AE139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>1313954.07875</v>
+      </c>
+      <c r="AK139" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="AL139" s="45" t="n">
+        <f aca="false">IF(G139&gt;0,G139,ROUND(F139*Assumptions!$B$18,0))</f>
+        <v>5165</v>
+      </c>
+      <c r="AM139" s="45" t="n">
+        <f aca="false">IF(H139="Yes",AL139,MAX(AL139,MIN(Assumptions!$B$20,ROUND(E139*Assumptions!$B$19,0))))</f>
+        <v>5165</v>
+      </c>
+      <c r="AN139" s="47" t="n">
+        <f aca="false">(AL139)*AE139-(((D139)+(AL139)*Assumptions!$B$4+IF(H139="Yes",Assumptions!$B$6*(D139),(AL139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(Assumptions!$B$21)+(AL139)*AE139*(Assumptions!$B$12+Assumptions!$B$13+IF((AL139)*AE139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL139)*AE139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>752131.20375</v>
+      </c>
+      <c r="AO139" s="47" t="n">
+        <f aca="false">(AM139)*AE139-(((D139)+(AM139)*Assumptions!$B$4+IF(H139="Yes",Assumptions!$B$6*(D139),(AM139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM139&gt;AL139,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(IF(AM139&gt;AL139,Assumptions!$B$22,Assumptions!$B$21))+(AM139)*AE139*(Assumptions!$B$12+Assumptions!$B$13+IF((AM139)*AE139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM139)*AE139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>752131.20375</v>
+      </c>
+      <c r="AP139" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q139+R139+S139)</f>
+        <v>3739368.75</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="40" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="40" t="s">
+        <v>300</v>
+      </c>
+      <c r="C140" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D140" s="41" t="n">
+        <v>1385000</v>
+      </c>
+      <c r="E140" s="42" t="n">
+        <v>5698</v>
+      </c>
+      <c r="F140" s="42" t="n">
+        <v>3641</v>
+      </c>
+      <c r="G140" s="42" t="n">
+        <v>3455</v>
+      </c>
+      <c r="H140" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="I140" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="J140" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K140" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="L140" s="45" t="n">
+        <f aca="false">IF(AO140&gt;AN140,AM140,AL140)</f>
+        <v>3455</v>
+      </c>
+      <c r="M140" s="40" t="str">
+        <f aca="false">IF(AO140&gt;AN140,"Zoning estimate",IF(H140="Yes","Approved plans",IF(G140&gt;0,"Listing claim","110% old house")))</f>
+        <v>Approved plans</v>
+      </c>
+      <c r="N140" s="45" t="n">
+        <f aca="false">IF(AO140&gt;AN140,IF(AM140&gt;AL140,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O140" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK140,Assumptions!$A$36:$A$48,0))+IF(I140="Yes",Assumptions!$B$23,0)+IF(J140="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1540</v>
+      </c>
+      <c r="P140" s="47" t="n">
+        <f aca="false">L140*O140</f>
+        <v>5320700</v>
+      </c>
+      <c r="Q140" s="47" t="n">
+        <f aca="false">D140</f>
+        <v>1385000</v>
+      </c>
+      <c r="R140" s="47" t="n">
+        <f aca="false">L140*Assumptions!$B$4</f>
+        <v>2418500</v>
+      </c>
+      <c r="S140" s="47" t="n">
+        <f aca="false">IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5)</f>
+        <v>69250</v>
+      </c>
+      <c r="T140" s="47" t="n">
+        <f aca="false">AP140*(Assumptions!$B$8*N140*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>339833.8125</v>
+      </c>
+      <c r="U140" s="47" t="n">
+        <f aca="false">Q140*Assumptions!$B$11*N140</f>
+        <v>33240</v>
+      </c>
+      <c r="V140" s="47" t="n">
+        <f aca="false">P140*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>216020.42</v>
+      </c>
+      <c r="W140" s="47" t="n">
+        <f aca="false">P140*IF(P140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X140" s="48" t="n">
+        <f aca="false">SUM(Q140:W140)</f>
+        <v>4461844.2325</v>
+      </c>
+      <c r="Y140" s="48" t="n">
+        <f aca="false">P140-X140</f>
+        <v>858855.767500001</v>
+      </c>
+      <c r="Z140" s="49" t="n">
+        <f aca="false">IF(X140=0,0,Y140/X140)</f>
+        <v>0.192488962578323</v>
+      </c>
+      <c r="AA140" s="47" t="n">
+        <f aca="false">MAX(0,(P140/(1+Assumptions!$B$27)-(L140*(Assumptions!$B$4+IF(H140="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N140*Assumptions!$B$9+Assumptions!$B$10)))-P140*(Assumptions!$B$12+Assumptions!$B$13+IF(P140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H140="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N140*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N140))</f>
+        <v>1526365.33614082</v>
+      </c>
+      <c r="AB140" s="50" t="n">
+        <f aca="false">IF(AA140&lt;=0,"no price works",D140/AA140)</f>
+        <v>0.907384337947402</v>
+      </c>
+      <c r="AC140" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK140,Assumptions!$A$36:$A$48,0))+IF(I140="Yes",Assumptions!$B$23,0)+IF(J140="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1400</v>
+      </c>
+      <c r="AD140" s="47" t="n">
+        <f aca="false">(L140)*AC140-(((D140)+(L140)*Assumptions!$B$4+IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N140)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(N140)+(L140)*AC140*(Assumptions!$B$12+Assumptions!$B$13+IF((L140)*AC140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L140)*AC140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>394793.9875</v>
+      </c>
+      <c r="AE140" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK140,Assumptions!$A$36:$A$48,0))+IF(I140="Yes",Assumptions!$B$23,0)+IF(J140="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1540</v>
+      </c>
+      <c r="AF140" s="47" t="n">
+        <f aca="false">(L140)*AE140-(((D140)+(L140)*Assumptions!$B$4+IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N140)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(N140)+(L140)*AE140*(Assumptions!$B$12+Assumptions!$B$13+IF((L140)*AE140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L140)*AE140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>858855.767500001</v>
+      </c>
+      <c r="AG140" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK140,Assumptions!$A$36:$A$48,0))+IF(I140="Yes",Assumptions!$B$23,0)+IF(J140="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1680</v>
+      </c>
+      <c r="AH140" s="47" t="n">
+        <f aca="false">(L140)*AG140-(((D140)+(L140)*Assumptions!$B$4+IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N140)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(N140)+(L140)*AG140*(Assumptions!$B$12+Assumptions!$B$13+IF((L140)*AG140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L140)*AG140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>1090741.5475</v>
+      </c>
+      <c r="AI140" s="47" t="n">
+        <f aca="false">(L140)*AE140-(((D140)+(L140)*Assumptions!$B$25+IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N140)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(N140)+(L140)*AE140*(Assumptions!$B$12+Assumptions!$B$13+IF((L140)*AE140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L140)*AE140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>1046764.58</v>
+      </c>
+      <c r="AJ140" s="47" t="n">
+        <f aca="false">(L140)*AE140-(((D140)+(L140)*Assumptions!$B$26+IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N140)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(N140)+(L140)*AE140*(Assumptions!$B$12+Assumptions!$B$13+IF((L140)*AE140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L140)*AE140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>1234673.3925</v>
+      </c>
+      <c r="AK140" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL140" s="45" t="n">
+        <f aca="false">IF(G140&gt;0,G140,ROUND(F140*Assumptions!$B$18,0))</f>
+        <v>3455</v>
+      </c>
+      <c r="AM140" s="45" t="n">
+        <f aca="false">IF(H140="Yes",AL140,MAX(AL140,MIN(Assumptions!$B$20,ROUND(E140*Assumptions!$B$19,0))))</f>
+        <v>3455</v>
+      </c>
+      <c r="AN140" s="47" t="n">
+        <f aca="false">(AL140)*AE140-(((D140)+(AL140)*Assumptions!$B$4+IF(H140="Yes",Assumptions!$B$6*(D140),(AL140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(Assumptions!$B$21)+(AL140)*AE140*(Assumptions!$B$12+Assumptions!$B$13+IF((AL140)*AE140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL140)*AE140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>858855.767500001</v>
+      </c>
+      <c r="AO140" s="47" t="n">
+        <f aca="false">(AM140)*AE140-(((D140)+(AM140)*Assumptions!$B$4+IF(H140="Yes",Assumptions!$B$6*(D140),(AM140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM140&gt;AL140,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(IF(AM140&gt;AL140,Assumptions!$B$22,Assumptions!$B$21))+(AM140)*AE140*(Assumptions!$B$12+Assumptions!$B$13+IF((AM140)*AE140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM140)*AE140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>858855.767500001</v>
+      </c>
+      <c r="AP140" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q140+R140+S140)</f>
+        <v>2517287.5</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="40" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="40" t="s">
+        <v>302</v>
+      </c>
+      <c r="C141" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D141" s="41" t="n">
+        <v>2950000</v>
+      </c>
+      <c r="E141" s="42" t="n">
+        <v>8302</v>
+      </c>
+      <c r="F141" s="42" t="n">
+        <v>3351</v>
+      </c>
+      <c r="G141" s="42" t="n">
+        <v>3579</v>
+      </c>
+      <c r="H141" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="I141" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J141" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K141" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L141" s="45" t="n">
+        <f aca="false">IF(AO141&gt;AN141,AM141,AL141)</f>
+        <v>3579</v>
+      </c>
+      <c r="M141" s="40" t="str">
+        <f aca="false">IF(AO141&gt;AN141,"Zoning estimate",IF(H141="Yes","Approved plans",IF(G141&gt;0,"Listing claim","110% old house")))</f>
+        <v>Approved plans</v>
+      </c>
+      <c r="N141" s="45" t="n">
+        <f aca="false">IF(AO141&gt;AN141,IF(AM141&gt;AL141,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O141" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK141,Assumptions!$A$36:$A$48,0))+IF(I141="Yes",Assumptions!$B$23,0)+IF(J141="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1650</v>
+      </c>
+      <c r="P141" s="47" t="n">
+        <f aca="false">L141*O141</f>
+        <v>5905350</v>
+      </c>
+      <c r="Q141" s="47" t="n">
+        <f aca="false">D141</f>
+        <v>2950000</v>
+      </c>
+      <c r="R141" s="47" t="n">
+        <f aca="false">L141*Assumptions!$B$4</f>
+        <v>2505300</v>
+      </c>
+      <c r="S141" s="47" t="n">
+        <f aca="false">IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5)</f>
+        <v>147500</v>
+      </c>
+      <c r="T141" s="47" t="n">
+        <f aca="false">AP141*(Assumptions!$B$8*N141*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>491645.7</v>
+      </c>
+      <c r="U141" s="47" t="n">
+        <f aca="false">Q141*Assumptions!$B$11*N141</f>
+        <v>70800</v>
+      </c>
+      <c r="V141" s="47" t="n">
+        <f aca="false">P141*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>239757.21</v>
+      </c>
+      <c r="W141" s="47" t="n">
+        <f aca="false">P141*IF(P141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>236214</v>
+      </c>
+      <c r="X141" s="48" t="n">
+        <f aca="false">SUM(Q141:W141)</f>
+        <v>6641216.91</v>
+      </c>
+      <c r="Y141" s="48" t="n">
+        <f aca="false">P141-X141</f>
+        <v>-735866.909999999</v>
+      </c>
+      <c r="Z141" s="49" t="n">
+        <f aca="false">IF(X141=0,0,Y141/X141)</f>
+        <v>-0.110803022995977</v>
+      </c>
+      <c r="AA141" s="47" t="n">
+        <f aca="false">MAX(0,(P141/(1+Assumptions!$B$27)-(L141*(Assumptions!$B$4+IF(H141="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N141*Assumptions!$B$9+Assumptions!$B$10)))-P141*(Assumptions!$B$12+Assumptions!$B$13+IF(P141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H141="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N141*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N141))</f>
+        <v>1658445.65629846</v>
+      </c>
+      <c r="AB141" s="50" t="n">
+        <f aca="false">IF(AA141&lt;=0,"no price works",D141/AA141)</f>
+        <v>1.77877399165687</v>
+      </c>
+      <c r="AC141" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK141,Assumptions!$A$36:$A$48,0))+IF(I141="Yes",Assumptions!$B$23,0)+IF(J141="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1500</v>
+      </c>
+      <c r="AD141" s="47" t="n">
+        <f aca="false">(L141)*AC141-(((D141)+(L141)*Assumptions!$B$4+IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N141)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(N141)+(L141)*AC141*(Assumptions!$B$12+Assumptions!$B$13+IF((L141)*AC141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L141)*AC141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1014706.8</v>
+      </c>
+      <c r="AE141" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK141,Assumptions!$A$36:$A$48,0))+IF(I141="Yes",Assumptions!$B$23,0)+IF(J141="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1650</v>
+      </c>
+      <c r="AF141" s="47" t="n">
+        <f aca="false">(L141)*AE141-(((D141)+(L141)*Assumptions!$B$4+IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N141)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(N141)+(L141)*AE141*(Assumptions!$B$12+Assumptions!$B$13+IF((L141)*AE141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L141)*AE141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-735866.909999999</v>
+      </c>
+      <c r="AG141" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK141,Assumptions!$A$36:$A$48,0))+IF(I141="Yes",Assumptions!$B$23,0)+IF(J141="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1800</v>
+      </c>
+      <c r="AH141" s="47" t="n">
+        <f aca="false">(L141)*AG141-(((D141)+(L141)*Assumptions!$B$4+IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N141)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(N141)+(L141)*AG141*(Assumptions!$B$12+Assumptions!$B$13+IF((L141)*AG141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L141)*AG141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-242287.02</v>
+      </c>
+      <c r="AI141" s="47" t="n">
+        <f aca="false">(L141)*AE141-(((D141)+(L141)*Assumptions!$B$25+IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N141)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(N141)+(L141)*AE141*(Assumptions!$B$12+Assumptions!$B$13+IF((L141)*AE141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L141)*AE141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-541214.047499999</v>
+      </c>
+      <c r="AJ141" s="47" t="n">
+        <f aca="false">(L141)*AE141-(((D141)+(L141)*Assumptions!$B$26+IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N141)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(N141)+(L141)*AE141*(Assumptions!$B$12+Assumptions!$B$13+IF((L141)*AE141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L141)*AE141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-346561.184999999</v>
+      </c>
+      <c r="AK141" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL141" s="45" t="n">
+        <f aca="false">IF(G141&gt;0,G141,ROUND(F141*Assumptions!$B$18,0))</f>
+        <v>3579</v>
+      </c>
+      <c r="AM141" s="45" t="n">
+        <f aca="false">IF(H141="Yes",AL141,MAX(AL141,MIN(Assumptions!$B$20,ROUND(E141*Assumptions!$B$19,0))))</f>
+        <v>3579</v>
+      </c>
+      <c r="AN141" s="47" t="n">
+        <f aca="false">(AL141)*AE141-(((D141)+(AL141)*Assumptions!$B$4+IF(H141="Yes",Assumptions!$B$6*(D141),(AL141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(Assumptions!$B$21)+(AL141)*AE141*(Assumptions!$B$12+Assumptions!$B$13+IF((AL141)*AE141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL141)*AE141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-735866.909999999</v>
+      </c>
+      <c r="AO141" s="47" t="n">
+        <f aca="false">(AM141)*AE141-(((D141)+(AM141)*Assumptions!$B$4+IF(H141="Yes",Assumptions!$B$6*(D141),(AM141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM141&gt;AL141,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(IF(AM141&gt;AL141,Assumptions!$B$22,Assumptions!$B$21))+(AM141)*AE141*(Assumptions!$B$12+Assumptions!$B$13+IF((AM141)*AE141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM141)*AE141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-735866.909999999</v>
+      </c>
+      <c r="AP141" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q141+R141+S141)</f>
+        <v>3641820</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="40" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="C142" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D142" s="41" t="n">
+        <v>2499000</v>
+      </c>
+      <c r="E142" s="42" t="n">
+        <v>7503</v>
+      </c>
+      <c r="F142" s="42" t="n">
+        <v>6125</v>
+      </c>
+      <c r="G142" s="42"/>
+      <c r="H142" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="I142" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="J142" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K142" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="L142" s="45" t="n">
+        <f aca="false">IF(AO142&gt;AN142,AM142,AL142)</f>
+        <v>6738</v>
+      </c>
+      <c r="M142" s="40" t="str">
+        <f aca="false">IF(AO142&gt;AN142,"Zoning estimate",IF(H142="Yes","Approved plans",IF(G142&gt;0,"Listing claim","110% old house")))</f>
+        <v>110% old house</v>
+      </c>
+      <c r="N142" s="45" t="n">
+        <f aca="false">IF(AO142&gt;AN142,IF(AM142&gt;AL142,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O142" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK142,Assumptions!$A$36:$A$48,0))+IF(I142="Yes",Assumptions!$B$23,0)+IF(J142="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1430</v>
+      </c>
+      <c r="P142" s="47" t="n">
+        <f aca="false">L142*O142</f>
+        <v>9635340</v>
+      </c>
+      <c r="Q142" s="47" t="n">
+        <f aca="false">D142</f>
+        <v>2499000</v>
+      </c>
+      <c r="R142" s="47" t="n">
+        <f aca="false">L142*Assumptions!$B$4</f>
+        <v>4716600</v>
+      </c>
+      <c r="S142" s="47" t="n">
+        <f aca="false">IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5)</f>
+        <v>505350</v>
+      </c>
+      <c r="T142" s="47" t="n">
+        <f aca="false">AP142*(Assumptions!$B$8*N142*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>677513.3625</v>
+      </c>
+      <c r="U142" s="47" t="n">
+        <f aca="false">Q142*Assumptions!$B$11*N142</f>
+        <v>59976</v>
+      </c>
+      <c r="V142" s="47" t="n">
+        <f aca="false">P142*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>391194.804</v>
+      </c>
+      <c r="W142" s="47" t="n">
+        <f aca="false">P142*IF(P142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>385413.6</v>
+      </c>
+      <c r="X142" s="48" t="n">
+        <f aca="false">SUM(Q142:W142)</f>
+        <v>9235047.7665</v>
+      </c>
+      <c r="Y142" s="48" t="n">
+        <f aca="false">P142-X142</f>
+        <v>400292.233500002</v>
+      </c>
+      <c r="Z142" s="49" t="n">
+        <f aca="false">IF(X142=0,0,Y142/X142)</f>
+        <v>0.0433449012523851</v>
+      </c>
+      <c r="AA142" s="47" t="n">
+        <f aca="false">MAX(0,(P142/(1+Assumptions!$B$27)-(L142*(Assumptions!$B$4+IF(H142="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N142*Assumptions!$B$9+Assumptions!$B$10)))-P142*(Assumptions!$B$12+Assumptions!$B$13+IF(P142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H142="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N142*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N142))</f>
+        <v>1728600.85922117</v>
+      </c>
+      <c r="AB142" s="50" t="n">
+        <f aca="false">IF(AA142&lt;=0,"no price works",D142/AA142)</f>
+        <v>1.4456778652337</v>
+      </c>
+      <c r="AC142" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK142,Assumptions!$A$36:$A$48,0))+IF(I142="Yes",Assumptions!$B$23,0)+IF(J142="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1300</v>
+      </c>
+      <c r="AD142" s="47" t="n">
+        <f aca="false">(L142)*AC142-(((D142)+(L142)*Assumptions!$B$4+IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N142)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(N142)+(L142)*AC142*(Assumptions!$B$12+Assumptions!$B$13+IF((L142)*AC142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L142)*AC142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-405047.002500001</v>
+      </c>
+      <c r="AE142" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK142,Assumptions!$A$36:$A$48,0))+IF(I142="Yes",Assumptions!$B$23,0)+IF(J142="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1430</v>
+      </c>
+      <c r="AF142" s="47" t="n">
+        <f aca="false">(L142)*AE142-(((D142)+(L142)*Assumptions!$B$4+IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N142)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(N142)+(L142)*AE142*(Assumptions!$B$12+Assumptions!$B$13+IF((L142)*AE142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L142)*AE142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>400292.2335</v>
+      </c>
+      <c r="AG142" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK142,Assumptions!$A$36:$A$48,0))+IF(I142="Yes",Assumptions!$B$23,0)+IF(J142="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1560</v>
+      </c>
+      <c r="AH142" s="47" t="n">
+        <f aca="false">(L142)*AG142-(((D142)+(L142)*Assumptions!$B$4+IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N142)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(N142)+(L142)*AG142*(Assumptions!$B$12+Assumptions!$B$13+IF((L142)*AG142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L142)*AG142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>1205631.4695</v>
+      </c>
+      <c r="AI142" s="47" t="n">
+        <f aca="false">(L142)*AE142-(((D142)+(L142)*Assumptions!$B$25+IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N142)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(N142)+(L142)*AE142*(Assumptions!$B$12+Assumptions!$B$13+IF((L142)*AE142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L142)*AE142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>766755.208500002</v>
+      </c>
+      <c r="AJ142" s="47" t="n">
+        <f aca="false">(L142)*AE142-(((D142)+(L142)*Assumptions!$B$26+IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N142)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(N142)+(L142)*AE142*(Assumptions!$B$12+Assumptions!$B$13+IF((L142)*AE142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L142)*AE142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>1133218.1835</v>
+      </c>
+      <c r="AK142" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL142" s="45" t="n">
+        <f aca="false">IF(G142&gt;0,G142,ROUND(F142*Assumptions!$B$18,0))</f>
+        <v>6738</v>
+      </c>
+      <c r="AM142" s="45" t="n">
+        <f aca="false">IF(H142="Yes",AL142,MAX(AL142,MIN(Assumptions!$B$20,ROUND(E142*Assumptions!$B$19,0))))</f>
+        <v>6738</v>
+      </c>
+      <c r="AN142" s="47" t="n">
+        <f aca="false">(AL142)*AE142-(((D142)+(AL142)*Assumptions!$B$4+IF(H142="Yes",Assumptions!$B$6*(D142),(AL142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(Assumptions!$B$21)+(AL142)*AE142*(Assumptions!$B$12+Assumptions!$B$13+IF((AL142)*AE142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL142)*AE142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>400292.2335</v>
+      </c>
+      <c r="AO142" s="47" t="n">
+        <f aca="false">(AM142)*AE142-(((D142)+(AM142)*Assumptions!$B$4+IF(H142="Yes",Assumptions!$B$6*(D142),(AM142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM142&gt;AL142,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(IF(AM142&gt;AL142,Assumptions!$B$22,Assumptions!$B$21))+(AM142)*AE142*(Assumptions!$B$12+Assumptions!$B$13+IF((AM142)*AE142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM142)*AE142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>400292.2335</v>
+      </c>
+      <c r="AP142" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q142+R142+S142)</f>
+        <v>5018617.5</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="40" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="C143" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D143" s="41" t="n">
+        <v>2499000</v>
+      </c>
+      <c r="E143" s="42" t="n">
+        <v>7993</v>
+      </c>
+      <c r="F143" s="42" t="n">
+        <v>5087</v>
+      </c>
+      <c r="G143" s="42"/>
+      <c r="H143" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="I143" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="J143" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K143" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="L143" s="45" t="n">
+        <f aca="false">IF(AO143&gt;AN143,AM143,AL143)</f>
+        <v>5596</v>
+      </c>
+      <c r="M143" s="40" t="str">
+        <f aca="false">IF(AO143&gt;AN143,"Zoning estimate",IF(H143="Yes","Approved plans",IF(G143&gt;0,"Listing claim","110% old house")))</f>
+        <v>110% old house</v>
+      </c>
+      <c r="N143" s="45" t="n">
+        <f aca="false">IF(AO143&gt;AN143,IF(AM143&gt;AL143,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O143" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK143,Assumptions!$A$36:$A$48,0))+IF(I143="Yes",Assumptions!$B$23,0)+IF(J143="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1430</v>
+      </c>
+      <c r="P143" s="47" t="n">
+        <f aca="false">L143*O143</f>
+        <v>8002280</v>
+      </c>
+      <c r="Q143" s="47" t="n">
+        <f aca="false">D143</f>
+        <v>2499000</v>
+      </c>
+      <c r="R143" s="47" t="n">
+        <f aca="false">L143*Assumptions!$B$4</f>
+        <v>3917200</v>
+      </c>
+      <c r="S143" s="47" t="n">
+        <f aca="false">IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5)</f>
+        <v>419700</v>
+      </c>
+      <c r="T143" s="47" t="n">
+        <f aca="false">AP143*(Assumptions!$B$8*N143*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>599850.225</v>
+      </c>
+      <c r="U143" s="47" t="n">
+        <f aca="false">Q143*Assumptions!$B$11*N143</f>
+        <v>59976</v>
+      </c>
+      <c r="V143" s="47" t="n">
+        <f aca="false">P143*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>324892.568</v>
+      </c>
+      <c r="W143" s="47" t="n">
+        <f aca="false">P143*IF(P143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>320091.2</v>
+      </c>
+      <c r="X143" s="48" t="n">
+        <f aca="false">SUM(Q143:W143)</f>
+        <v>8140709.993</v>
+      </c>
+      <c r="Y143" s="48" t="n">
+        <f aca="false">P143-X143</f>
+        <v>-138429.993</v>
+      </c>
+      <c r="Z143" s="49" t="n">
+        <f aca="false">IF(X143=0,0,Y143/X143)</f>
+        <v>-0.017004658453505</v>
+      </c>
+      <c r="AA143" s="47" t="n">
+        <f aca="false">MAX(0,(P143/(1+Assumptions!$B$27)-(L143*(Assumptions!$B$4+IF(H143="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N143*Assumptions!$B$9+Assumptions!$B$10)))-P143*(Assumptions!$B$12+Assumptions!$B$13+IF(P143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H143="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N143*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N143))</f>
+        <v>1435626.35918695</v>
+      </c>
+      <c r="AB143" s="50" t="n">
+        <f aca="false">IF(AA143&lt;=0,"no price works",D143/AA143)</f>
+        <v>1.74070361971849</v>
+      </c>
+      <c r="AC143" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK143,Assumptions!$A$36:$A$48,0))+IF(I143="Yes",Assumptions!$B$23,0)+IF(J143="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1300</v>
+      </c>
+      <c r="AD143" s="47" t="n">
+        <f aca="false">(L143)*AC143-(((D143)+(L143)*Assumptions!$B$4+IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N143)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(N143)+(L143)*AC143*(Assumptions!$B$12+Assumptions!$B$13+IF((L143)*AC143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L143)*AC143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-807275.105</v>
+      </c>
+      <c r="AE143" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK143,Assumptions!$A$36:$A$48,0))+IF(I143="Yes",Assumptions!$B$23,0)+IF(J143="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1430</v>
+      </c>
+      <c r="AF143" s="47" t="n">
+        <f aca="false">(L143)*AE143-(((D143)+(L143)*Assumptions!$B$4+IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N143)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(N143)+(L143)*AE143*(Assumptions!$B$12+Assumptions!$B$13+IF((L143)*AE143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L143)*AE143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-138429.992999999</v>
+      </c>
+      <c r="AG143" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK143,Assumptions!$A$36:$A$48,0))+IF(I143="Yes",Assumptions!$B$23,0)+IF(J143="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1560</v>
+      </c>
+      <c r="AH143" s="47" t="n">
+        <f aca="false">(L143)*AG143-(((D143)+(L143)*Assumptions!$B$4+IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N143)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(N143)+(L143)*AG143*(Assumptions!$B$12+Assumptions!$B$13+IF((L143)*AG143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L143)*AG143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>530415.119</v>
+      </c>
+      <c r="AI143" s="47" t="n">
+        <f aca="false">(L143)*AE143-(((D143)+(L143)*Assumptions!$B$25+IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N143)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(N143)+(L143)*AE143*(Assumptions!$B$12+Assumptions!$B$13+IF((L143)*AE143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L143)*AE143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>165922.457</v>
+      </c>
+      <c r="AJ143" s="47" t="n">
+        <f aca="false">(L143)*AE143-(((D143)+(L143)*Assumptions!$B$26+IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N143)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(N143)+(L143)*AE143*(Assumptions!$B$12+Assumptions!$B$13+IF((L143)*AE143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L143)*AE143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>470274.907000001</v>
+      </c>
+      <c r="AK143" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL143" s="45" t="n">
+        <f aca="false">IF(G143&gt;0,G143,ROUND(F143*Assumptions!$B$18,0))</f>
+        <v>5596</v>
+      </c>
+      <c r="AM143" s="45" t="n">
+        <f aca="false">IF(H143="Yes",AL143,MAX(AL143,MIN(Assumptions!$B$20,ROUND(E143*Assumptions!$B$19,0))))</f>
+        <v>5596</v>
+      </c>
+      <c r="AN143" s="47" t="n">
+        <f aca="false">(AL143)*AE143-(((D143)+(AL143)*Assumptions!$B$4+IF(H143="Yes",Assumptions!$B$6*(D143),(AL143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(Assumptions!$B$21)+(AL143)*AE143*(Assumptions!$B$12+Assumptions!$B$13+IF((AL143)*AE143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL143)*AE143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-138429.992999999</v>
+      </c>
+      <c r="AO143" s="47" t="n">
+        <f aca="false">(AM143)*AE143-(((D143)+(AM143)*Assumptions!$B$4+IF(H143="Yes",Assumptions!$B$6*(D143),(AM143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM143&gt;AL143,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(IF(AM143&gt;AL143,Assumptions!$B$22,Assumptions!$B$21))+(AM143)*AE143*(Assumptions!$B$12+Assumptions!$B$13+IF((AM143)*AE143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM143)*AE143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-138429.992999999</v>
+      </c>
+      <c r="AP143" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q143+R143+S143)</f>
+        <v>4443335</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="40" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="C144" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="D144" s="41" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E144" s="42" t="n">
+        <v>15071</v>
+      </c>
+      <c r="F144" s="42" t="n">
+        <v>7535</v>
+      </c>
+      <c r="G144" s="42"/>
+      <c r="H144" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="I144" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J144" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K144" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="L144" s="45" t="n">
+        <f aca="false">IF(AO144&gt;AN144,AM144,AL144)</f>
+        <v>8289</v>
+      </c>
+      <c r="M144" s="40" t="str">
+        <f aca="false">IF(AO144&gt;AN144,"Zoning estimate",IF(H144="Yes","Approved plans",IF(G144&gt;0,"Listing claim","110% old house")))</f>
+        <v>110% old house</v>
+      </c>
+      <c r="N144" s="45" t="n">
+        <f aca="false">IF(AO144&gt;AN144,IF(AM144&gt;AL144,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O144" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK144,Assumptions!$A$36:$A$48,0))+IF(I144="Yes",Assumptions!$B$23,0)+IF(J144="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1100</v>
+      </c>
+      <c r="P144" s="47" t="n">
+        <f aca="false">L144*O144</f>
+        <v>9117900</v>
+      </c>
+      <c r="Q144" s="47" t="n">
+        <f aca="false">D144</f>
+        <v>1500000</v>
+      </c>
+      <c r="R144" s="47" t="n">
+        <f aca="false">L144*Assumptions!$B$4</f>
+        <v>5802300</v>
+      </c>
+      <c r="S144" s="47" t="n">
+        <f aca="false">IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5)</f>
+        <v>621675</v>
+      </c>
+      <c r="T144" s="47" t="n">
+        <f aca="false">AP144*(Assumptions!$B$8*N144*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>695328.80625</v>
+      </c>
+      <c r="U144" s="47" t="n">
+        <f aca="false">Q144*Assumptions!$B$11*N144</f>
+        <v>36000</v>
+      </c>
+      <c r="V144" s="47" t="n">
+        <f aca="false">P144*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>370186.74</v>
+      </c>
+      <c r="W144" s="47" t="n">
+        <f aca="false">P144*IF(P144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>364716</v>
+      </c>
+      <c r="X144" s="48" t="n">
+        <f aca="false">SUM(Q144:W144)</f>
+        <v>9390206.54625</v>
+      </c>
+      <c r="Y144" s="48" t="n">
+        <f aca="false">P144-X144</f>
+        <v>-272306.546250001</v>
+      </c>
+      <c r="Z144" s="49" t="n">
+        <f aca="false">IF(X144=0,0,Y144/X144)</f>
+        <v>-0.0289989943148532</v>
+      </c>
+      <c r="AA144" s="47" t="n">
+        <f aca="false">MAX(0,(P144/(1+Assumptions!$B$27)-(L144*(Assumptions!$B$4+IF(H144="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N144*Assumptions!$B$9+Assumptions!$B$10)))-P144*(Assumptions!$B$12+Assumptions!$B$13+IF(P144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H144="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N144*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N144))</f>
+        <v>185317.876682864</v>
+      </c>
+      <c r="AB144" s="50" t="n">
+        <f aca="false">IF(AA144&lt;=0,"no price works",D144/AA144)</f>
+        <v>8.09420022962469</v>
+      </c>
+      <c r="AC144" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK144,Assumptions!$A$36:$A$48,0))+IF(I144="Yes",Assumptions!$B$23,0)+IF(J144="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1000</v>
+      </c>
+      <c r="AD144" s="47" t="n">
+        <f aca="false">(L144)*AC144-(((D144)+(L144)*Assumptions!$B$4+IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N144)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(N144)+(L144)*AC144*(Assumptions!$B$12+Assumptions!$B$13+IF((L144)*AC144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L144)*AC144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1034397.20625</v>
+      </c>
+      <c r="AE144" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK144,Assumptions!$A$36:$A$48,0))+IF(I144="Yes",Assumptions!$B$23,0)+IF(J144="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1100</v>
+      </c>
+      <c r="AF144" s="47" t="n">
+        <f aca="false">(L144)*AE144-(((D144)+(L144)*Assumptions!$B$4+IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N144)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(N144)+(L144)*AE144*(Assumptions!$B$12+Assumptions!$B$13+IF((L144)*AE144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L144)*AE144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-272306.546250001</v>
+      </c>
+      <c r="AG144" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK144,Assumptions!$A$36:$A$48,0))+IF(I144="Yes",Assumptions!$B$23,0)+IF(J144="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1200</v>
+      </c>
+      <c r="AH144" s="47" t="n">
+        <f aca="false">(L144)*AG144-(((D144)+(L144)*Assumptions!$B$4+IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N144)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(N144)+(L144)*AG144*(Assumptions!$B$12+Assumptions!$B$13+IF((L144)*AG144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L144)*AG144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>489784.11375</v>
+      </c>
+      <c r="AI144" s="47" t="n">
+        <f aca="false">(L144)*AE144-(((D144)+(L144)*Assumptions!$B$25+IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N144)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(N144)+(L144)*AE144*(Assumptions!$B$12+Assumptions!$B$13+IF((L144)*AE144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L144)*AE144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>178511.44125</v>
+      </c>
+      <c r="AJ144" s="47" t="n">
+        <f aca="false">(L144)*AE144-(((D144)+(L144)*Assumptions!$B$26+IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N144)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(N144)+(L144)*AE144*(Assumptions!$B$12+Assumptions!$B$13+IF((L144)*AE144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L144)*AE144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>629329.428750001</v>
+      </c>
+      <c r="AK144" s="40" t="s">
+        <v>267</v>
+      </c>
+      <c r="AL144" s="45" t="n">
+        <f aca="false">IF(G144&gt;0,G144,ROUND(F144*Assumptions!$B$18,0))</f>
+        <v>8289</v>
+      </c>
+      <c r="AM144" s="45" t="n">
+        <f aca="false">IF(H144="Yes",AL144,MAX(AL144,MIN(Assumptions!$B$20,ROUND(E144*Assumptions!$B$19,0))))</f>
+        <v>8289</v>
+      </c>
+      <c r="AN144" s="47" t="n">
+        <f aca="false">(AL144)*AE144-(((D144)+(AL144)*Assumptions!$B$4+IF(H144="Yes",Assumptions!$B$6*(D144),(AL144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(Assumptions!$B$21)+(AL144)*AE144*(Assumptions!$B$12+Assumptions!$B$13+IF((AL144)*AE144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL144)*AE144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-272306.546250001</v>
+      </c>
+      <c r="AO144" s="47" t="n">
+        <f aca="false">(AM144)*AE144-(((D144)+(AM144)*Assumptions!$B$4+IF(H144="Yes",Assumptions!$B$6*(D144),(AM144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM144&gt;AL144,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(IF(AM144&gt;AL144,Assumptions!$B$22,Assumptions!$B$21))+(AM144)*AE144*(Assumptions!$B$12+Assumptions!$B$13+IF((AM144)*AE144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM144)*AE144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-272306.546250001</v>
+      </c>
+      <c r="AP144" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q144+R144+S144)</f>
+        <v>5150583.75</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="40" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="40" t="s">
+        <v>310</v>
+      </c>
+      <c r="C145" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D145" s="41" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="E145" s="42" t="n">
+        <v>6493</v>
+      </c>
+      <c r="F145" s="42" t="n">
+        <v>2032</v>
+      </c>
+      <c r="G145" s="42"/>
+      <c r="H145" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="I145" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J145" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K145" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="L145" s="45" t="n">
+        <f aca="false">IF(AO145&gt;AN145,AM145,AL145)</f>
+        <v>2235</v>
+      </c>
+      <c r="M145" s="40" t="str">
+        <f aca="false">IF(AO145&gt;AN145,"Zoning estimate",IF(H145="Yes","Approved plans",IF(G145&gt;0,"Listing claim","110% old house")))</f>
+        <v>110% old house</v>
+      </c>
+      <c r="N145" s="45" t="n">
+        <f aca="false">IF(AO145&gt;AN145,IF(AM145&gt;AL145,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O145" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK145,Assumptions!$A$36:$A$48,0))+IF(I145="Yes",Assumptions!$B$23,0)+IF(J145="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1650</v>
+      </c>
+      <c r="P145" s="47" t="n">
+        <f aca="false">L145*O145</f>
+        <v>3687750</v>
+      </c>
+      <c r="Q145" s="47" t="n">
+        <f aca="false">D145</f>
+        <v>5500000</v>
+      </c>
+      <c r="R145" s="47" t="n">
+        <f aca="false">L145*Assumptions!$B$4</f>
+        <v>1564500</v>
+      </c>
+      <c r="S145" s="47" t="n">
+        <f aca="false">IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5)</f>
+        <v>167625</v>
+      </c>
+      <c r="T145" s="47" t="n">
+        <f aca="false">AP145*(Assumptions!$B$8*N145*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>634618.96875</v>
+      </c>
+      <c r="U145" s="47" t="n">
+        <f aca="false">Q145*Assumptions!$B$11*N145</f>
+        <v>132000</v>
+      </c>
+      <c r="V145" s="47" t="n">
+        <f aca="false">P145*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>149722.65</v>
+      </c>
+      <c r="W145" s="47" t="n">
+        <f aca="false">P145*IF(P145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X145" s="48" t="n">
+        <f aca="false">SUM(Q145:W145)</f>
+        <v>8148466.61875</v>
+      </c>
+      <c r="Y145" s="48" t="n">
+        <f aca="false">P145-X145</f>
+        <v>-4460716.61875</v>
+      </c>
+      <c r="Z145" s="49" t="n">
+        <f aca="false">IF(X145=0,0,Y145/X145)</f>
+        <v>-0.547430188703932</v>
+      </c>
+      <c r="AA145" s="47" t="n">
+        <f aca="false">MAX(0,(P145/(1+Assumptions!$B$27)-(L145*(Assumptions!$B$4+IF(H145="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N145*Assumptions!$B$9+Assumptions!$B$10)))-P145*(Assumptions!$B$12+Assumptions!$B$13+IF(P145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H145="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N145*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N145))</f>
+        <v>1055001.13486376</v>
+      </c>
+      <c r="AB145" s="50" t="n">
+        <f aca="false">IF(AA145&lt;=0,"no price works",D145/AA145)</f>
+        <v>5.21326453427016</v>
+      </c>
+      <c r="AC145" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK145,Assumptions!$A$36:$A$48,0))+IF(I145="Yes",Assumptions!$B$23,0)+IF(J145="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1500</v>
+      </c>
+      <c r="AD145" s="47" t="n">
+        <f aca="false">(L145)*AC145-(((D145)+(L145)*Assumptions!$B$4+IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N145)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(N145)+(L145)*AC145*(Assumptions!$B$12+Assumptions!$B$13+IF((L145)*AC145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L145)*AC145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-4782355.46875</v>
+      </c>
+      <c r="AE145" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK145,Assumptions!$A$36:$A$48,0))+IF(I145="Yes",Assumptions!$B$23,0)+IF(J145="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1650</v>
+      </c>
+      <c r="AF145" s="47" t="n">
+        <f aca="false">(L145)*AE145-(((D145)+(L145)*Assumptions!$B$4+IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N145)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(N145)+(L145)*AE145*(Assumptions!$B$12+Assumptions!$B$13+IF((L145)*AE145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L145)*AE145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-4460716.61875</v>
+      </c>
+      <c r="AG145" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK145,Assumptions!$A$36:$A$48,0))+IF(I145="Yes",Assumptions!$B$23,0)+IF(J145="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1800</v>
+      </c>
+      <c r="AH145" s="47" t="n">
+        <f aca="false">(L145)*AG145-(((D145)+(L145)*Assumptions!$B$4+IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N145)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(N145)+(L145)*AG145*(Assumptions!$B$12+Assumptions!$B$13+IF((L145)*AG145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L145)*AG145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-4139077.76875</v>
+      </c>
+      <c r="AI145" s="47" t="n">
+        <f aca="false">(L145)*AE145-(((D145)+(L145)*Assumptions!$B$25+IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N145)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(N145)+(L145)*AE145*(Assumptions!$B$12+Assumptions!$B$13+IF((L145)*AE145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L145)*AE145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-4339160.55625</v>
+      </c>
+      <c r="AJ145" s="47" t="n">
+        <f aca="false">(L145)*AE145-(((D145)+(L145)*Assumptions!$B$26+IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N145)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(N145)+(L145)*AE145*(Assumptions!$B$12+Assumptions!$B$13+IF((L145)*AE145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L145)*AE145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-4217604.49375</v>
+      </c>
+      <c r="AK145" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL145" s="45" t="n">
+        <f aca="false">IF(G145&gt;0,G145,ROUND(F145*Assumptions!$B$18,0))</f>
+        <v>2235</v>
+      </c>
+      <c r="AM145" s="45" t="n">
+        <f aca="false">IF(H145="Yes",AL145,MAX(AL145,MIN(Assumptions!$B$20,ROUND(E145*Assumptions!$B$19,0))))</f>
+        <v>2597</v>
+      </c>
+      <c r="AN145" s="47" t="n">
+        <f aca="false">(AL145)*AE145-(((D145)+(AL145)*Assumptions!$B$4+IF(H145="Yes",Assumptions!$B$6*(D145),(AL145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(Assumptions!$B$21)+(AL145)*AE145*(Assumptions!$B$12+Assumptions!$B$13+IF((AL145)*AE145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL145)*AE145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-4460716.61875</v>
+      </c>
+      <c r="AO145" s="47" t="n">
+        <f aca="false">(AM145)*AE145-(((D145)+(AM145)*Assumptions!$B$4+IF(H145="Yes",Assumptions!$B$6*(D145),(AM145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM145&gt;AL145,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(IF(AM145&gt;AL145,Assumptions!$B$22,Assumptions!$B$21))+(AM145)*AE145*(Assumptions!$B$12+Assumptions!$B$13+IF((AM145)*AE145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM145)*AE145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-4551829.58625</v>
+      </c>
+      <c r="AP145" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q145+R145+S145)</f>
+        <v>4700881.25</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AP138"/>
+  <autoFilter ref="A2:AP145"/>
   <mergeCells count="6">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="L1:P1"/>
@@ -24686,7 +25824,7 @@
     <mergeCell ref="AC1:AJ1"/>
     <mergeCell ref="AK1:AP1"/>
   </mergeCells>
-  <conditionalFormatting sqref="AB3:AB138">
+  <conditionalFormatting sqref="AB3:AB145">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(AB3),AB3&lt;=1)</formula>
     </cfRule>
@@ -24720,342 +25858,342 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="51" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B4" s="52" t="n">
         <v>700</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B5" s="52" t="n">
         <v>75</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B6" s="53" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B7" s="53" t="n">
         <v>0.65</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B8" s="53" t="n">
         <v>0.1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B9" s="53" t="n">
         <v>0.6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="B10" s="53" t="n">
         <v>0.015</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B11" s="53" t="n">
         <v>0.012</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B12" s="53" t="n">
         <v>0.035</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="B13" s="53" t="n">
         <v>0.0056</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B14" s="52" t="n">
         <v>5400000</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="B15" s="53" t="n">
         <v>0.04</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B16" s="52" t="n">
         <v>10900000</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B17" s="53" t="n">
         <v>0.055</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B18" s="54" t="n">
         <v>1.1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="B19" s="54" t="n">
         <v>0.4</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B20" s="55" t="n">
         <v>8000</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="B21" s="55" t="n">
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B22" s="55" t="n">
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B23" s="52" t="n">
         <v>100</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B24" s="52" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B25" s="52" t="n">
         <v>650</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="B26" s="52" t="n">
         <v>600</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="B27" s="53" t="n">
         <v>0.15</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B28" s="53" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B29" s="53" t="n">
         <v>0.1</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B30" s="53" t="n">
         <v>0.2</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="57" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="51" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="C35" s="51" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25066,7 +26204,7 @@
         <v>1860</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25077,18 +26215,18 @@
         <v>1850</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B38" s="52" t="n">
         <v>1750</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25099,7 +26237,7 @@
         <v>1400</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25110,7 +26248,7 @@
         <v>1400</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25121,7 +26259,7 @@
         <v>1300</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25132,7 +26270,7 @@
         <v>1250</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25143,7 +26281,7 @@
         <v>1250</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25154,7 +26292,7 @@
         <v>1250</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25165,7 +26303,7 @@
         <v>1200</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25176,7 +26314,7 @@
         <v>1000</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25187,7 +26325,7 @@
         <v>900</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25198,7 +26336,7 @@
         <v>900</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -25233,12 +26371,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="51" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B2" s="51" t="s">
         <v>49</v>
@@ -25247,30 +26385,30 @@
         <v>9</v>
       </c>
       <c r="D2" s="51" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="G2" s="51" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="H2" s="51" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="I2" s="51" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>126</v>
@@ -25288,18 +26426,18 @@
         <v>2026</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>75</v>
@@ -25317,18 +26455,18 @@
         <v>2014</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>75</v>
@@ -25346,18 +26484,18 @@
         <v>2018</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>70</v>
@@ -25375,18 +26513,18 @@
         <v>2021</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>79</v>
@@ -25404,21 +26542,21 @@
         <v>2013</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="D8" s="58" t="n">
         <v>9735000</v>
@@ -25433,18 +26571,18 @@
         <v>2012</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>202</v>
@@ -25462,18 +26600,18 @@
         <v>2020</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>202</v>
@@ -25491,18 +26629,18 @@
         <v>2016</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>70</v>
@@ -25520,18 +26658,18 @@
         <v>2025</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>70</v>
@@ -25549,18 +26687,18 @@
         <v>2021</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>70</v>
@@ -25578,18 +26716,18 @@
         <v>2022</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>75</v>
@@ -25607,18 +26745,18 @@
         <v>2020</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>202</v>
@@ -25636,18 +26774,18 @@
         <v>2015</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>117</v>
@@ -25665,18 +26803,18 @@
         <v>2010</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>117</v>
@@ -25694,18 +26832,18 @@
         <v>2019</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>70</v>
@@ -25723,18 +26861,18 @@
         <v>2020</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>70</v>
@@ -25752,18 +26890,18 @@
         <v>2023</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>70</v>
@@ -25781,18 +26919,18 @@
         <v>2019</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>126</v>
@@ -25810,18 +26948,18 @@
         <v>2019</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>70</v>
@@ -25839,18 +26977,18 @@
         <v>2013</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>79</v>
@@ -25868,10 +27006,10 @@
         <v>2017</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25887,7 +27025,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -25900,7 +27038,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="60" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="B26" s="60" t="s">
         <v>49</v>
@@ -25909,33 +27047,33 @@
         <v>9</v>
       </c>
       <c r="D26" s="60" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="E26" s="60" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="F26" s="60" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="G26" s="60" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="H26" s="60" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="I26" s="60" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="D27" s="58" t="n">
         <v>9990000</v>
@@ -25947,24 +27085,24 @@
         <v>1523</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="D28" s="58" t="n">
         <v>4295000</v>
@@ -25976,22 +27114,22 @@
         <v>1387</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="7" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="D29" s="58" t="n">
         <v>5495000</v>
@@ -26003,24 +27141,24 @@
         <v>1390</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="D30" s="58" t="n">
         <v>4995000</v>
@@ -26032,24 +27170,24 @@
         <v>1362</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="D31" s="58" t="n">
         <v>13995000</v>
@@ -26061,24 +27199,24 @@
         <v>2149</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="D32" s="58" t="n">
         <v>5995000</v>
@@ -26090,13 +27228,13 @@
         <v>1389</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>

--- a/palisades_lots/Palisades_Lot_Screen.xlsx
+++ b/palisades_lots/Palisades_Lot_Screen.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Sold Comps" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'All Lots'!$A$2:$AP$143</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'All Lots'!$A$2:$AP$149</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="507">
   <si>
     <t xml:space="preserve">Palisades lots — deal breakdown for the shortlist</t>
   </si>
@@ -916,12 +916,6 @@
     <t xml:space="preserve">new listing 2026-10-05; no new-house application in LADBS open data (APN 4423023002, 10/5/26)</t>
   </si>
   <si>
-    <t xml:space="preserve">1115 Via De La Paz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">new listing 2026-10-05; LADBS 25010-30000-01756: new-house application, verifications in progress 9/25/26, not approved</t>
-  </si>
-  <si>
     <t xml:space="preserve">15241 Via de las Olas</t>
   </si>
   <si>
@@ -962,6 +956,48 @@
   </si>
   <si>
     <t xml:space="preserve">new listing 2026-10-08; no permit records of any kind in LADBS open data (APN 4431013012, 10/8/26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17056 Livorno Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-09; no permit records in LADBS open data (APN 4419017019, 10/9/26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15305 De Pauw St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-09; LADBS 25010-30000-05056: wildfire rebuild SFD, PC Info Complete 12/4/25, 5,309 sf (open-data square_footage; basement walls and part of foundation to remain); second application 26014-30000-03089 Quality Review Completed 8/19/26, same 5,309 sf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14902 Mc Kendree Ave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-09; no permit records in LADBS open data (APN 4422011024, 10/9/26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14912 Mc Kendree Ave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-09; no permit records in LADBS open data (APN 4422011002, 10/9/26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827 Lachman Ln</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-09; no rebuild application in LADBS open data; only a 2020 trellis permit (APN 4419006029, 10/9/26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14629 Whitfield Ave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-09; no permit records in LADBS open data (APN 4422009005, 10/9/26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17834 Porto Marina Way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new listing 2026-10-09; no permit records in LADBS open data (APN 4416015061, 10/9/26)</t>
   </si>
   <si>
     <t xml:space="preserve">Assumptions — change the yellow cells and the whole workbook updates</t>
@@ -2460,27 +2496,27 @@
         <v>9</v>
       </c>
       <c r="B7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>Huntington</v>
       </c>
       <c r="C7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>Huntington</v>
       </c>
       <c r="D7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>Bluffs / El Medio</v>
       </c>
       <c r="E7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>Riviera</v>
       </c>
       <c r="F7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>Riviera</v>
       </c>
       <c r="G7" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$C$3:$C$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$C$3:$C$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>Bluffs / El Medio</v>
       </c>
     </row>
@@ -2489,27 +2525,27 @@
         <v>10</v>
       </c>
       <c r="B8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>4375000</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>4495000</v>
       </c>
       <c r="D8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>1345000</v>
       </c>
       <c r="E8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
-        <v>2795000</v>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
+        <v>2525000</v>
       </c>
       <c r="F8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>3750000</v>
       </c>
       <c r="G8" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$D$3:$D$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$D$3:$D$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>995000</v>
       </c>
     </row>
@@ -2518,27 +2554,27 @@
         <v>11</v>
       </c>
       <c r="B9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>8008</v>
       </c>
       <c r="C9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>8205</v>
       </c>
       <c r="D9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>5556</v>
       </c>
       <c r="E9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>13724</v>
       </c>
       <c r="F9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>18344</v>
       </c>
       <c r="G9" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$E$3:$E$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$E$3:$E$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>4382</v>
       </c>
     </row>
@@ -2547,27 +2583,27 @@
         <v>12</v>
       </c>
       <c r="B10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>Yes</v>
       </c>
       <c r="C10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>Yes</v>
       </c>
       <c r="D10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>Yes</v>
       </c>
       <c r="E10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>No</v>
       </c>
       <c r="F10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>No</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$H$3:$H$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$H$3:$H$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>No</v>
       </c>
     </row>
@@ -2587,27 +2623,27 @@
         <v>14</v>
       </c>
       <c r="B12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>7504</v>
       </c>
       <c r="C12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>7154</v>
       </c>
       <c r="D12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>4270</v>
       </c>
       <c r="E12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>5490</v>
       </c>
       <c r="F12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>7338</v>
       </c>
       <c r="G12" s="10" t="n">
-        <f aca="false">INDEX('All Lots'!$L$3:$L$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$L$3:$L$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>3315</v>
       </c>
     </row>
@@ -2616,27 +2652,27 @@
         <v>15</v>
       </c>
       <c r="B13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>Approved plans</v>
       </c>
       <c r="C13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>Approved plans</v>
       </c>
       <c r="D13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>Approved plans</v>
       </c>
       <c r="E13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>Zoning estimate</v>
       </c>
       <c r="F13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>Zoning estimate</v>
       </c>
       <c r="G13" s="8" t="str">
-        <f aca="false">INDEX('All Lots'!$M$3:$M$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$M$3:$M$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>110% old house</v>
       </c>
     </row>
@@ -2645,27 +2681,27 @@
         <v>16</v>
       </c>
       <c r="B14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>2035</v>
       </c>
       <c r="C14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>2035</v>
       </c>
       <c r="D14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>1540</v>
       </c>
       <c r="E14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>2046</v>
       </c>
       <c r="F14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>2046</v>
       </c>
       <c r="G14" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$O$3:$O$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$O$3:$O$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>1540</v>
       </c>
     </row>
@@ -2674,27 +2710,27 @@
         <v>17</v>
       </c>
       <c r="B15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>15270640</v>
       </c>
       <c r="C15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>14558390</v>
       </c>
       <c r="D15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>6575800</v>
       </c>
       <c r="E15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>11232540</v>
       </c>
       <c r="F15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>15013548</v>
       </c>
       <c r="G15" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$P$3:$P$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$P$3:$P$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>5105100</v>
       </c>
     </row>
@@ -2714,27 +2750,27 @@
         <v>19</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>4375000</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>4495000</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>1345000</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
-        <v>2795000</v>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
+        <v>2525000</v>
       </c>
       <c r="F17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>3750000</v>
       </c>
       <c r="G17" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$Q$3:$Q$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Q$3:$Q$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>995000</v>
       </c>
     </row>
@@ -2743,27 +2779,27 @@
         <v>20</v>
       </c>
       <c r="B18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>5252800</v>
       </c>
       <c r="C18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>5007800</v>
       </c>
       <c r="D18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>2989000</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>3843000</v>
       </c>
       <c r="F18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>5136600</v>
       </c>
       <c r="G18" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$R$3:$R$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$R$3:$R$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>2320500</v>
       </c>
     </row>
@@ -2772,27 +2808,27 @@
         <v>21</v>
       </c>
       <c r="B19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>218750</v>
       </c>
       <c r="C19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>224750</v>
       </c>
       <c r="D19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>67250</v>
       </c>
       <c r="E19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>411750</v>
       </c>
       <c r="F19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>550350</v>
       </c>
       <c r="G19" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$S$3:$S$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$S$3:$S$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>248625</v>
       </c>
     </row>
@@ -2801,27 +2837,27 @@
         <v>22</v>
       </c>
       <c r="B20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>864034.7625</v>
       </c>
       <c r="C20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>853592.5125</v>
       </c>
       <c r="D20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>386209.6875</v>
       </c>
       <c r="E20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
-        <v>893555.8125</v>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
+        <v>859333.3125</v>
       </c>
       <c r="F20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>1196133.4125</v>
       </c>
       <c r="G20" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$T$3:$T$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$T$3:$T$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>312751.96875</v>
       </c>
     </row>
@@ -2830,27 +2866,27 @@
         <v>23</v>
       </c>
       <c r="B21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>105000</v>
       </c>
       <c r="C21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>107880</v>
       </c>
       <c r="D21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>32280</v>
       </c>
       <c r="E21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
-        <v>100620</v>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
+        <v>90900</v>
       </c>
       <c r="F21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>135000</v>
       </c>
       <c r="G21" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$U$3:$U$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$U$3:$U$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>23880</v>
       </c>
     </row>
@@ -2859,27 +2895,27 @@
         <v>24</v>
       </c>
       <c r="B22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>619987.984</v>
       </c>
       <c r="C22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>591070.634</v>
       </c>
       <c r="D22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>266977.48</v>
       </c>
       <c r="E22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>456041.124</v>
       </c>
       <c r="F22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>609550.0488</v>
       </c>
       <c r="G22" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$V$3:$V$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$V$3:$V$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>207267.06</v>
       </c>
     </row>
@@ -2888,27 +2924,27 @@
         <v>25</v>
       </c>
       <c r="B23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>839885.2</v>
       </c>
       <c r="C23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>800711.45</v>
       </c>
       <c r="D23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>263032</v>
       </c>
       <c r="E23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>617789.7</v>
       </c>
       <c r="F23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>825745.14</v>
       </c>
       <c r="G23" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$W$3:$W$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$W$3:$W$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -2917,27 +2953,27 @@
         <v>26</v>
       </c>
       <c r="B24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>12275457.9465</v>
       </c>
       <c r="C24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>12080804.5965</v>
       </c>
       <c r="D24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>5349749.1675</v>
       </c>
       <c r="E24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
-        <v>9117756.6365</v>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
+        <v>8803814.1365</v>
       </c>
       <c r="F24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>12203378.6013</v>
       </c>
       <c r="G24" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$X$3:$X$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$X$3:$X$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>4108024.02875</v>
       </c>
     </row>
@@ -2957,27 +2993,27 @@
         <v>28</v>
       </c>
       <c r="B26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>2995182.0535</v>
       </c>
       <c r="C26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>2477585.4035</v>
       </c>
       <c r="D26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>1226050.8325</v>
       </c>
       <c r="E26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
-        <v>2114783.3635</v>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
+        <v>2428725.8635</v>
       </c>
       <c r="F26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>2810169.3987</v>
       </c>
       <c r="G26" s="19" t="n">
-        <f aca="false">INDEX('All Lots'!$Y$3:$Y$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Y$3:$Y$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>997075.971250001</v>
       </c>
     </row>
@@ -2986,27 +3022,27 @@
         <v>29</v>
       </c>
       <c r="B27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>0.243997581723947</v>
       </c>
       <c r="C27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>0.205084469640192</v>
       </c>
       <c r="D27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>0.229179124873428</v>
       </c>
       <c r="E27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
-        <v>0.231941194288313</v>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
+        <v>0.275872005683386</v>
       </c>
       <c r="F27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>0.230277982066429</v>
       </c>
       <c r="G27" s="22" t="n">
-        <f aca="false">INDEX('All Lots'!$Z$3:$Z$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$Z$3:$Z$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>0.242714250031637</v>
       </c>
     </row>
@@ -3015,27 +3051,27 @@
         <v>30</v>
       </c>
       <c r="B28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>5235412.63985109</v>
       </c>
       <c r="C28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>4991223.61746998</v>
       </c>
       <c r="D28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>1660861.37056886</v>
       </c>
       <c r="E28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>3353735.28312752</v>
       </c>
       <c r="F28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>4482642.89755733</v>
       </c>
       <c r="G28" s="9" t="n">
-        <f aca="false">INDEX('All Lots'!$AA$3:$AA$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AA$3:$AA$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>1292902.73222788</v>
       </c>
     </row>
@@ -3044,27 +3080,27 @@
         <v>31</v>
       </c>
       <c r="B29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>0.835655238843683</v>
       </c>
       <c r="C29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>0.900580768264294</v>
       </c>
       <c r="D29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>0.809820749542346</v>
       </c>
       <c r="E29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
-        <v>0.833399109960023</v>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
+        <v>0.752891861412901</v>
       </c>
       <c r="F29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>0.836560057470436</v>
       </c>
       <c r="G29" s="23" t="n">
-        <f aca="false">INDEX('All Lots'!$AB$3:$AB$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AB$3:$AB$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>0.769586122140412</v>
       </c>
     </row>
@@ -3084,27 +3120,27 @@
         <v>33</v>
       </c>
       <c r="B31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>1850</v>
       </c>
       <c r="C31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>1850</v>
       </c>
       <c r="D31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>1400</v>
       </c>
       <c r="E31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>1860</v>
       </c>
       <c r="F31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>1860</v>
       </c>
       <c r="G31" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AC$3:$AC$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AC$3:$AC$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>1400</v>
       </c>
     </row>
@@ -3113,27 +3149,27 @@
         <v>34</v>
       </c>
       <c r="B32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>1739657.7975</v>
       </c>
       <c r="C32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>1280621.0475</v>
       </c>
       <c r="D32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>676433.5125</v>
       </c>
       <c r="E32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
-        <v>1344435.3475</v>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
+        <v>1658377.8475</v>
       </c>
       <c r="F32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>1575782.7795</v>
       </c>
       <c r="G32" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AD$3:$AD$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AD$3:$AD$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>551818.43125</v>
       </c>
     </row>
@@ -3142,27 +3178,27 @@
         <v>35</v>
       </c>
       <c r="B33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>2035</v>
       </c>
       <c r="C33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>2035</v>
       </c>
       <c r="D33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>1540</v>
       </c>
       <c r="E33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>2046</v>
       </c>
       <c r="F33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>2046</v>
       </c>
       <c r="G33" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AE$3:$AE$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AE$3:$AE$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>1540</v>
       </c>
     </row>
@@ -3171,27 +3207,27 @@
         <v>36</v>
       </c>
       <c r="B34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>2995182.0535</v>
       </c>
       <c r="C34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>2477585.4035</v>
       </c>
       <c r="D34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>1226050.8325</v>
       </c>
       <c r="E34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
-        <v>2114783.3635</v>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
+        <v>2428725.8635</v>
       </c>
       <c r="F34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>2810169.3987</v>
       </c>
       <c r="G34" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AF$3:$AF$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AF$3:$AF$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>997075.971250001</v>
       </c>
     </row>
@@ -3200,27 +3236,27 @@
         <v>37</v>
       </c>
       <c r="B35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>2220</v>
       </c>
       <c r="C35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>2220</v>
       </c>
       <c r="D35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>1680</v>
       </c>
       <c r="E35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
         <v>2232</v>
       </c>
       <c r="F35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>2232</v>
       </c>
       <c r="G35" s="13" t="n">
-        <f aca="false">INDEX('All Lots'!$AG$3:$AG$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AG$3:$AG$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>1680</v>
       </c>
     </row>
@@ -3229,27 +3265,27 @@
         <v>38</v>
       </c>
       <c r="B36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$143,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$149,MATCH("711 Chapala Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>4250706.3095</v>
       </c>
       <c r="C36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$143,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$149,MATCH("611 Ocampo Dr",'All Lots'!$B$3:$B$149,0))</f>
         <v>3674549.7595</v>
       </c>
       <c r="D36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$143,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$149,MATCH("16150 Northfield St",'All Lots'!$B$3:$B$149,0))</f>
         <v>1775668.1525</v>
       </c>
       <c r="E36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$143,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$143,0))</f>
-        <v>3038302.3795</v>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$149,MATCH("14410 Villa Woods Pl",'All Lots'!$B$3:$B$149,0))</f>
+        <v>3352244.8795</v>
       </c>
       <c r="F36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$143,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$149,MATCH("909 Rivas Canyon Rd",'All Lots'!$B$3:$B$149,0))</f>
         <v>4044556.0179</v>
       </c>
       <c r="G36" s="15" t="n">
-        <f aca="false">INDEX('All Lots'!$AH$3:$AH$143,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$143,0))</f>
+        <f aca="false">INDEX('All Lots'!$AH$3:$AH$149,MATCH("545 N Las Casas Ave",'All Lots'!$B$3:$B$149,0))</f>
         <v>1219565.51125</v>
       </c>
     </row>
@@ -3371,7 +3407,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AP143"/>
+  <dimension ref="A1:AP149"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -4073,7 +4109,7 @@
         <v>70</v>
       </c>
       <c r="D6" s="41" t="n">
-        <v>2795000</v>
+        <v>2525000</v>
       </c>
       <c r="E6" s="42" t="n">
         <v>13724</v>
@@ -4116,7 +4152,7 @@
       </c>
       <c r="Q6" s="47" t="n">
         <f aca="false">D6</f>
-        <v>2795000</v>
+        <v>2525000</v>
       </c>
       <c r="R6" s="47" t="n">
         <f aca="false">L6*Assumptions!$B$4</f>
@@ -4128,11 +4164,11 @@
       </c>
       <c r="T6" s="47" t="n">
         <f aca="false">AP6*(Assumptions!$B$8*N6*Assumptions!$B$9+Assumptions!$B$10)</f>
-        <v>893555.8125</v>
+        <v>859333.3125</v>
       </c>
       <c r="U6" s="47" t="n">
         <f aca="false">Q6*Assumptions!$B$11*N6</f>
-        <v>100620</v>
+        <v>90900</v>
       </c>
       <c r="V6" s="47" t="n">
         <f aca="false">P6*(Assumptions!$B$12+Assumptions!$B$13)</f>
@@ -4144,15 +4180,15 @@
       </c>
       <c r="X6" s="48" t="n">
         <f aca="false">SUM(Q6:W6)</f>
-        <v>9117756.6365</v>
+        <v>8803814.1365</v>
       </c>
       <c r="Y6" s="48" t="n">
         <f aca="false">P6-X6</f>
-        <v>2114783.3635</v>
+        <v>2428725.8635</v>
       </c>
       <c r="Z6" s="49" t="n">
         <f aca="false">IF(X6=0,0,Y6/X6)</f>
-        <v>0.231941194288313</v>
+        <v>0.275872005683386</v>
       </c>
       <c r="AA6" s="47" t="n">
         <f aca="false">MAX(0,(P6/(1+Assumptions!$B$27)-(L6*(Assumptions!$B$4+IF(H6="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N6*Assumptions!$B$9+Assumptions!$B$10)))-P6*(Assumptions!$B$12+Assumptions!$B$13+IF(P6&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P6&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H6="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N6*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N6))</f>
@@ -4160,7 +4196,7 @@
       </c>
       <c r="AB6" s="50" t="n">
         <f aca="false">IF(AA6&lt;=0,"no price works",D6/AA6)</f>
-        <v>0.833399109960023</v>
+        <v>0.752891861412901</v>
       </c>
       <c r="AC6" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK6,Assumptions!$A$36:$A$48,0))+IF(I6="Yes",Assumptions!$B$23,0)+IF(J6="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
@@ -4168,7 +4204,7 @@
       </c>
       <c r="AD6" s="47" t="n">
         <f aca="false">(L6)*AC6-(((D6)+(L6)*Assumptions!$B$4+IF(H6="Yes",Assumptions!$B$6*(D6),(L6)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N6)*Assumptions!$B$9+Assumptions!$B$10))+(D6)*Assumptions!$B$11*(N6)+(L6)*AC6*(Assumptions!$B$12+Assumptions!$B$13+IF((L6)*AC6&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L6)*AC6&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>1344435.3475</v>
+        <v>1658377.8475</v>
       </c>
       <c r="AE6" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK6,Assumptions!$A$36:$A$48,0))+IF(I6="Yes",Assumptions!$B$23,0)+IF(J6="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
@@ -4176,7 +4212,7 @@
       </c>
       <c r="AF6" s="47" t="n">
         <f aca="false">(L6)*AE6-(((D6)+(L6)*Assumptions!$B$4+IF(H6="Yes",Assumptions!$B$6*(D6),(L6)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N6)*Assumptions!$B$9+Assumptions!$B$10))+(D6)*Assumptions!$B$11*(N6)+(L6)*AE6*(Assumptions!$B$12+Assumptions!$B$13+IF((L6)*AE6&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L6)*AE6&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>2114783.3635</v>
+        <v>2428725.8635</v>
       </c>
       <c r="AG6" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK6,Assumptions!$A$36:$A$48,0))+IF(I6="Yes",Assumptions!$B$23,0)+IF(J6="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
@@ -4184,15 +4220,15 @@
       </c>
       <c r="AH6" s="47" t="n">
         <f aca="false">(L6)*AG6-(((D6)+(L6)*Assumptions!$B$4+IF(H6="Yes",Assumptions!$B$6*(D6),(L6)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N6)*Assumptions!$B$9+Assumptions!$B$10))+(D6)*Assumptions!$B$11*(N6)+(L6)*AG6*(Assumptions!$B$12+Assumptions!$B$13+IF((L6)*AG6&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L6)*AG6&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>3038302.3795</v>
+        <v>3352244.8795</v>
       </c>
       <c r="AI6" s="47" t="n">
         <f aca="false">(L6)*AE6-(((D6)+(L6)*Assumptions!$B$25+IF(H6="Yes",Assumptions!$B$6*(D6),(L6)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N6)*Assumptions!$B$9+Assumptions!$B$10))+(D6)*Assumptions!$B$11*(N6)+(L6)*AE6*(Assumptions!$B$12+Assumptions!$B$13+IF((L6)*AE6&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L6)*AE6&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>2424076.2385</v>
+        <v>2738018.7385</v>
       </c>
       <c r="AJ6" s="47" t="n">
         <f aca="false">(L6)*AE6-(((D6)+(L6)*Assumptions!$B$26+IF(H6="Yes",Assumptions!$B$6*(D6),(L6)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N6)*Assumptions!$B$9+Assumptions!$B$10))+(D6)*Assumptions!$B$11*(N6)+(L6)*AE6*(Assumptions!$B$12+Assumptions!$B$13+IF((L6)*AE6&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L6)*AE6&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>2733369.1135</v>
+        <v>3047311.6135</v>
       </c>
       <c r="AK6" s="40" t="s">
         <v>73</v>
@@ -4207,15 +4243,15 @@
       </c>
       <c r="AN6" s="47" t="n">
         <f aca="false">(AL6)*AE6-(((D6)+(AL6)*Assumptions!$B$4+IF(H6="Yes",Assumptions!$B$6*(D6),(AL6)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D6)*Assumptions!$B$11*(Assumptions!$B$21)+(AL6)*AE6*(Assumptions!$B$12+Assumptions!$B$13+IF((AL6)*AE6&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL6)*AE6&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>1710416.57215</v>
+        <v>2010589.07215</v>
       </c>
       <c r="AO6" s="47" t="n">
         <f aca="false">(AM6)*AE6-(((D6)+(AM6)*Assumptions!$B$4+IF(H6="Yes",Assumptions!$B$6*(D6),(AM6)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM6&gt;AL6,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D6)*Assumptions!$B$11*(IF(AM6&gt;AL6,Assumptions!$B$22,Assumptions!$B$21))+(AM6)*AE6*(Assumptions!$B$12+Assumptions!$B$13+IF((AM6)*AE6&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM6)*AE6&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>2114783.3635</v>
+        <v>2428725.8635</v>
       </c>
       <c r="AP6" s="47" t="n">
         <f aca="false">Assumptions!$B$7*(Q6+R6+S6)</f>
-        <v>4582337.5</v>
+        <v>4406837.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24278,23 +24314,23 @@
         <v>296</v>
       </c>
       <c r="C136" s="40" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D136" s="41" t="n">
-        <v>2499000</v>
+        <v>5500000</v>
       </c>
       <c r="E136" s="42" t="n">
-        <v>7993</v>
+        <v>6493</v>
       </c>
       <c r="F136" s="42" t="n">
-        <v>5087</v>
+        <v>2032</v>
       </c>
       <c r="G136" s="42"/>
       <c r="H136" s="43" t="s">
         <v>71</v>
       </c>
       <c r="I136" s="43" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="J136" s="43" t="s">
         <v>71</v>
@@ -24304,7 +24340,7 @@
       </c>
       <c r="L136" s="45" t="n">
         <f aca="false">IF(AO136&gt;AN136,AM136,AL136)</f>
-        <v>5596</v>
+        <v>2235</v>
       </c>
       <c r="M136" s="40" t="str">
         <f aca="false">IF(AO136&gt;AN136,"Zoning estimate",IF(H136="Yes","Approved plans",IF(G136&gt;0,"Listing claim","110% old house")))</f>
@@ -24316,114 +24352,114 @@
       </c>
       <c r="O136" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK136,Assumptions!$A$36:$A$48,0))+IF(I136="Yes",Assumptions!$B$23,0)+IF(J136="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
-        <v>1430</v>
+        <v>1650</v>
       </c>
       <c r="P136" s="47" t="n">
         <f aca="false">L136*O136</f>
-        <v>8002280</v>
+        <v>3687750</v>
       </c>
       <c r="Q136" s="47" t="n">
         <f aca="false">D136</f>
-        <v>2499000</v>
+        <v>5500000</v>
       </c>
       <c r="R136" s="47" t="n">
         <f aca="false">L136*Assumptions!$B$4</f>
-        <v>3917200</v>
+        <v>1564500</v>
       </c>
       <c r="S136" s="47" t="n">
         <f aca="false">IF(H136="Yes",Assumptions!$B$6*(D136),(L136)*Assumptions!$B$5)</f>
-        <v>419700</v>
+        <v>167625</v>
       </c>
       <c r="T136" s="47" t="n">
         <f aca="false">AP136*(Assumptions!$B$8*N136*Assumptions!$B$9+Assumptions!$B$10)</f>
-        <v>599850.225</v>
+        <v>634618.96875</v>
       </c>
       <c r="U136" s="47" t="n">
         <f aca="false">Q136*Assumptions!$B$11*N136</f>
-        <v>59976</v>
+        <v>132000</v>
       </c>
       <c r="V136" s="47" t="n">
         <f aca="false">P136*(Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>324892.568</v>
+        <v>149722.65</v>
       </c>
       <c r="W136" s="47" t="n">
         <f aca="false">P136*IF(P136&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P136&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
-        <v>320091.2</v>
+        <v>0</v>
       </c>
       <c r="X136" s="48" t="n">
         <f aca="false">SUM(Q136:W136)</f>
-        <v>8140709.993</v>
+        <v>8148466.61875</v>
       </c>
       <c r="Y136" s="48" t="n">
         <f aca="false">P136-X136</f>
-        <v>-138429.993</v>
+        <v>-4460716.61875</v>
       </c>
       <c r="Z136" s="49" t="n">
         <f aca="false">IF(X136=0,0,Y136/X136)</f>
-        <v>-0.017004658453505</v>
+        <v>-0.547430188703932</v>
       </c>
       <c r="AA136" s="47" t="n">
         <f aca="false">MAX(0,(P136/(1+Assumptions!$B$27)-(L136*(Assumptions!$B$4+IF(H136="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N136*Assumptions!$B$9+Assumptions!$B$10)))-P136*(Assumptions!$B$12+Assumptions!$B$13+IF(P136&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P136&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H136="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N136*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N136))</f>
-        <v>1435626.35918695</v>
+        <v>1055001.13486376</v>
       </c>
       <c r="AB136" s="50" t="n">
         <f aca="false">IF(AA136&lt;=0,"no price works",D136/AA136)</f>
-        <v>1.74070361971849</v>
+        <v>5.21326453427016</v>
       </c>
       <c r="AC136" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK136,Assumptions!$A$36:$A$48,0))+IF(I136="Yes",Assumptions!$B$23,0)+IF(J136="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="AD136" s="47" t="n">
         <f aca="false">(L136)*AC136-(((D136)+(L136)*Assumptions!$B$4+IF(H136="Yes",Assumptions!$B$6*(D136),(L136)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N136)*Assumptions!$B$9+Assumptions!$B$10))+(D136)*Assumptions!$B$11*(N136)+(L136)*AC136*(Assumptions!$B$12+Assumptions!$B$13+IF((L136)*AC136&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L136)*AC136&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-807275.105</v>
+        <v>-4782355.46875</v>
       </c>
       <c r="AE136" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK136,Assumptions!$A$36:$A$48,0))+IF(I136="Yes",Assumptions!$B$23,0)+IF(J136="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
-        <v>1430</v>
+        <v>1650</v>
       </c>
       <c r="AF136" s="47" t="n">
         <f aca="false">(L136)*AE136-(((D136)+(L136)*Assumptions!$B$4+IF(H136="Yes",Assumptions!$B$6*(D136),(L136)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N136)*Assumptions!$B$9+Assumptions!$B$10))+(D136)*Assumptions!$B$11*(N136)+(L136)*AE136*(Assumptions!$B$12+Assumptions!$B$13+IF((L136)*AE136&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L136)*AE136&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-138429.992999999</v>
+        <v>-4460716.61875</v>
       </c>
       <c r="AG136" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK136,Assumptions!$A$36:$A$48,0))+IF(I136="Yes",Assumptions!$B$23,0)+IF(J136="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
-        <v>1560</v>
+        <v>1800</v>
       </c>
       <c r="AH136" s="47" t="n">
         <f aca="false">(L136)*AG136-(((D136)+(L136)*Assumptions!$B$4+IF(H136="Yes",Assumptions!$B$6*(D136),(L136)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N136)*Assumptions!$B$9+Assumptions!$B$10))+(D136)*Assumptions!$B$11*(N136)+(L136)*AG136*(Assumptions!$B$12+Assumptions!$B$13+IF((L136)*AG136&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L136)*AG136&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>530415.119</v>
+        <v>-4139077.76875</v>
       </c>
       <c r="AI136" s="47" t="n">
         <f aca="false">(L136)*AE136-(((D136)+(L136)*Assumptions!$B$25+IF(H136="Yes",Assumptions!$B$6*(D136),(L136)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N136)*Assumptions!$B$9+Assumptions!$B$10))+(D136)*Assumptions!$B$11*(N136)+(L136)*AE136*(Assumptions!$B$12+Assumptions!$B$13+IF((L136)*AE136&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L136)*AE136&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>165922.457</v>
+        <v>-4339160.55625</v>
       </c>
       <c r="AJ136" s="47" t="n">
         <f aca="false">(L136)*AE136-(((D136)+(L136)*Assumptions!$B$26+IF(H136="Yes",Assumptions!$B$6*(D136),(L136)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N136)*Assumptions!$B$9+Assumptions!$B$10))+(D136)*Assumptions!$B$11*(N136)+(L136)*AE136*(Assumptions!$B$12+Assumptions!$B$13+IF((L136)*AE136&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L136)*AE136&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>470274.907000001</v>
+        <v>-4217604.49375</v>
       </c>
       <c r="AK136" s="40" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="AL136" s="45" t="n">
         <f aca="false">IF(G136&gt;0,G136,ROUND(F136*Assumptions!$B$18,0))</f>
-        <v>5596</v>
+        <v>2235</v>
       </c>
       <c r="AM136" s="45" t="n">
         <f aca="false">IF(H136="Yes",AL136,MAX(AL136,MIN(Assumptions!$B$20,ROUND(E136*Assumptions!$B$19,0))))</f>
-        <v>5596</v>
+        <v>2597</v>
       </c>
       <c r="AN136" s="47" t="n">
         <f aca="false">(AL136)*AE136-(((D136)+(AL136)*Assumptions!$B$4+IF(H136="Yes",Assumptions!$B$6*(D136),(AL136)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D136)*Assumptions!$B$11*(Assumptions!$B$21)+(AL136)*AE136*(Assumptions!$B$12+Assumptions!$B$13+IF((AL136)*AE136&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL136)*AE136&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-138429.992999999</v>
+        <v>-4460716.61875</v>
       </c>
       <c r="AO136" s="47" t="n">
         <f aca="false">(AM136)*AE136-(((D136)+(AM136)*Assumptions!$B$4+IF(H136="Yes",Assumptions!$B$6*(D136),(AM136)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM136&gt;AL136,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D136)*Assumptions!$B$11*(IF(AM136&gt;AL136,Assumptions!$B$22,Assumptions!$B$21))+(AM136)*AE136*(Assumptions!$B$12+Assumptions!$B$13+IF((AM136)*AE136&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM136)*AE136&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-138429.992999999</v>
+        <v>-4551829.58625</v>
       </c>
       <c r="AP136" s="47" t="n">
         <f aca="false">Assumptions!$B$7*(Q136+R136+S136)</f>
-        <v>4443335</v>
+        <v>4700881.25</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24434,16 +24470,16 @@
         <v>298</v>
       </c>
       <c r="C137" s="40" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D137" s="41" t="n">
-        <v>5500000</v>
+        <v>1995000</v>
       </c>
       <c r="E137" s="42" t="n">
-        <v>6493</v>
+        <v>12128</v>
       </c>
       <c r="F137" s="42" t="n">
-        <v>2032</v>
+        <v>2598</v>
       </c>
       <c r="G137" s="42"/>
       <c r="H137" s="43" t="s">
@@ -24460,126 +24496,126 @@
       </c>
       <c r="L137" s="45" t="n">
         <f aca="false">IF(AO137&gt;AN137,AM137,AL137)</f>
-        <v>2235</v>
+        <v>4851</v>
       </c>
       <c r="M137" s="40" t="str">
         <f aca="false">IF(AO137&gt;AN137,"Zoning estimate",IF(H137="Yes","Approved plans",IF(G137&gt;0,"Listing claim","110% old house")))</f>
-        <v>110% old house</v>
+        <v>Zoning estimate</v>
       </c>
       <c r="N137" s="45" t="n">
         <f aca="false">IF(AO137&gt;AN137,IF(AM137&gt;AL137,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O137" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK137,Assumptions!$A$36:$A$48,0))+IF(I137="Yes",Assumptions!$B$23,0)+IF(J137="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
-        <v>1650</v>
+        <v>1485</v>
       </c>
       <c r="P137" s="47" t="n">
         <f aca="false">L137*O137</f>
-        <v>3687750</v>
+        <v>7203735</v>
       </c>
       <c r="Q137" s="47" t="n">
         <f aca="false">D137</f>
-        <v>5500000</v>
+        <v>1995000</v>
       </c>
       <c r="R137" s="47" t="n">
         <f aca="false">L137*Assumptions!$B$4</f>
-        <v>1564500</v>
+        <v>3395700</v>
       </c>
       <c r="S137" s="47" t="n">
         <f aca="false">IF(H137="Yes",Assumptions!$B$6*(D137),(L137)*Assumptions!$B$5)</f>
-        <v>167625</v>
+        <v>363825</v>
       </c>
       <c r="T137" s="47" t="n">
         <f aca="false">AP137*(Assumptions!$B$8*N137*Assumptions!$B$9+Assumptions!$B$10)</f>
-        <v>634618.96875</v>
+        <v>729386.04375</v>
       </c>
       <c r="U137" s="47" t="n">
         <f aca="false">Q137*Assumptions!$B$11*N137</f>
-        <v>132000</v>
+        <v>71820</v>
       </c>
       <c r="V137" s="47" t="n">
         <f aca="false">P137*(Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>149722.65</v>
+        <v>292471.641</v>
       </c>
       <c r="W137" s="47" t="n">
         <f aca="false">P137*IF(P137&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P137&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
-        <v>0</v>
+        <v>288149.4</v>
       </c>
       <c r="X137" s="48" t="n">
         <f aca="false">SUM(Q137:W137)</f>
-        <v>8148466.61875</v>
+        <v>7136352.08475</v>
       </c>
       <c r="Y137" s="48" t="n">
         <f aca="false">P137-X137</f>
-        <v>-4460716.61875</v>
+        <v>67382.9152500005</v>
       </c>
       <c r="Z137" s="49" t="n">
         <f aca="false">IF(X137=0,0,Y137/X137)</f>
-        <v>-0.547430188703932</v>
+        <v>0.00944220722993674</v>
       </c>
       <c r="AA137" s="47" t="n">
         <f aca="false">MAX(0,(P137/(1+Assumptions!$B$27)-(L137*(Assumptions!$B$4+IF(H137="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N137*Assumptions!$B$9+Assumptions!$B$10)))-P137*(Assumptions!$B$12+Assumptions!$B$13+IF(P137&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P137&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H137="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N137*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N137))</f>
-        <v>1055001.13486376</v>
+        <v>1244851.90845354</v>
       </c>
       <c r="AB137" s="50" t="n">
         <f aca="false">IF(AA137&lt;=0,"no price works",D137/AA137)</f>
-        <v>5.21326453427016</v>
+        <v>1.60260026630667</v>
       </c>
       <c r="AC137" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK137,Assumptions!$A$36:$A$48,0))+IF(I137="Yes",Assumptions!$B$23,0)+IF(J137="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="AD137" s="47" t="n">
         <f aca="false">(L137)*AC137-(((D137)+(L137)*Assumptions!$B$4+IF(H137="Yes",Assumptions!$B$6*(D137),(L137)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N137)*Assumptions!$B$9+Assumptions!$B$10))+(D137)*Assumptions!$B$11*(N137)+(L137)*AC137*(Assumptions!$B$12+Assumptions!$B$13+IF((L137)*AC137&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L137)*AC137&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-4782355.46875</v>
+        <v>-534718.35375</v>
       </c>
       <c r="AE137" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK137,Assumptions!$A$36:$A$48,0))+IF(I137="Yes",Assumptions!$B$23,0)+IF(J137="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
-        <v>1650</v>
+        <v>1485</v>
       </c>
       <c r="AF137" s="47" t="n">
         <f aca="false">(L137)*AE137-(((D137)+(L137)*Assumptions!$B$4+IF(H137="Yes",Assumptions!$B$6*(D137),(L137)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N137)*Assumptions!$B$9+Assumptions!$B$10))+(D137)*Assumptions!$B$11*(N137)+(L137)*AE137*(Assumptions!$B$12+Assumptions!$B$13+IF((L137)*AE137&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L137)*AE137&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-4460716.61875</v>
+        <v>67382.9152500015</v>
       </c>
       <c r="AG137" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK137,Assumptions!$A$36:$A$48,0))+IF(I137="Yes",Assumptions!$B$23,0)+IF(J137="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
-        <v>1800</v>
+        <v>1620</v>
       </c>
       <c r="AH137" s="47" t="n">
         <f aca="false">(L137)*AG137-(((D137)+(L137)*Assumptions!$B$4+IF(H137="Yes",Assumptions!$B$6*(D137),(L137)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N137)*Assumptions!$B$9+Assumptions!$B$10))+(D137)*Assumptions!$B$11*(N137)+(L137)*AG137*(Assumptions!$B$12+Assumptions!$B$13+IF((L137)*AG137&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L137)*AG137&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-4139077.76875</v>
+        <v>669484.184250001</v>
       </c>
       <c r="AI137" s="47" t="n">
         <f aca="false">(L137)*AE137-(((D137)+(L137)*Assumptions!$B$25+IF(H137="Yes",Assumptions!$B$6*(D137),(L137)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N137)*Assumptions!$B$9+Assumptions!$B$10))+(D137)*Assumptions!$B$11*(N137)+(L137)*AE137*(Assumptions!$B$12+Assumptions!$B$13+IF((L137)*AE137&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L137)*AE137&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-4339160.55625</v>
+        <v>340676.127750001</v>
       </c>
       <c r="AJ137" s="47" t="n">
         <f aca="false">(L137)*AE137-(((D137)+(L137)*Assumptions!$B$26+IF(H137="Yes",Assumptions!$B$6*(D137),(L137)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N137)*Assumptions!$B$9+Assumptions!$B$10))+(D137)*Assumptions!$B$11*(N137)+(L137)*AE137*(Assumptions!$B$12+Assumptions!$B$13+IF((L137)*AE137&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L137)*AE137&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-4217604.49375</v>
+        <v>613969.340250001</v>
       </c>
       <c r="AK137" s="40" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AL137" s="45" t="n">
         <f aca="false">IF(G137&gt;0,G137,ROUND(F137*Assumptions!$B$18,0))</f>
-        <v>2235</v>
+        <v>2858</v>
       </c>
       <c r="AM137" s="45" t="n">
         <f aca="false">IF(H137="Yes",AL137,MAX(AL137,MIN(Assumptions!$B$20,ROUND(E137*Assumptions!$B$19,0))))</f>
-        <v>2597</v>
+        <v>4851</v>
       </c>
       <c r="AN137" s="47" t="n">
         <f aca="false">(AL137)*AE137-(((D137)+(AL137)*Assumptions!$B$4+IF(H137="Yes",Assumptions!$B$6*(D137),(AL137)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D137)*Assumptions!$B$11*(Assumptions!$B$21)+(AL137)*AE137*(Assumptions!$B$12+Assumptions!$B$13+IF((AL137)*AE137&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL137)*AE137&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-4460716.61875</v>
+        <v>-555434.790499999</v>
       </c>
       <c r="AO137" s="47" t="n">
         <f aca="false">(AM137)*AE137-(((D137)+(AM137)*Assumptions!$B$4+IF(H137="Yes",Assumptions!$B$6*(D137),(AM137)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM137&gt;AL137,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D137)*Assumptions!$B$11*(IF(AM137&gt;AL137,Assumptions!$B$22,Assumptions!$B$21))+(AM137)*AE137*(Assumptions!$B$12+Assumptions!$B$13+IF((AM137)*AE137&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM137)*AE137&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-4551829.58625</v>
+        <v>67382.9152500015</v>
       </c>
       <c r="AP137" s="47" t="n">
         <f aca="false">Assumptions!$B$7*(Q137+R137+S137)</f>
-        <v>4700881.25</v>
+        <v>3740441.25</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24590,16 +24626,16 @@
         <v>300</v>
       </c>
       <c r="C138" s="40" t="s">
-        <v>102</v>
+        <v>257</v>
       </c>
       <c r="D138" s="41" t="n">
-        <v>1995000</v>
+        <v>1198000</v>
       </c>
       <c r="E138" s="42" t="n">
-        <v>12128</v>
+        <v>16621</v>
       </c>
       <c r="F138" s="42" t="n">
-        <v>2598</v>
+        <v>4600</v>
       </c>
       <c r="G138" s="42"/>
       <c r="H138" s="43" t="s">
@@ -24616,7 +24652,7 @@
       </c>
       <c r="L138" s="45" t="n">
         <f aca="false">IF(AO138&gt;AN138,AM138,AL138)</f>
-        <v>4851</v>
+        <v>6648</v>
       </c>
       <c r="M138" s="40" t="str">
         <f aca="false">IF(AO138&gt;AN138,"Zoning estimate",IF(H138="Yes","Approved plans",IF(G138&gt;0,"Listing claim","110% old house")))</f>
@@ -24628,117 +24664,117 @@
       </c>
       <c r="O138" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK138,Assumptions!$A$36:$A$48,0))+IF(I138="Yes",Assumptions!$B$23,0)+IF(J138="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
-        <v>1485</v>
+        <v>1100</v>
       </c>
       <c r="P138" s="47" t="n">
         <f aca="false">L138*O138</f>
-        <v>7203735</v>
+        <v>7312800</v>
       </c>
       <c r="Q138" s="47" t="n">
         <f aca="false">D138</f>
-        <v>1995000</v>
+        <v>1198000</v>
       </c>
       <c r="R138" s="47" t="n">
         <f aca="false">L138*Assumptions!$B$4</f>
-        <v>3395700</v>
+        <v>4653600</v>
       </c>
       <c r="S138" s="47" t="n">
         <f aca="false">IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5)</f>
-        <v>363825</v>
+        <v>498600</v>
       </c>
       <c r="T138" s="47" t="n">
         <f aca="false">AP138*(Assumptions!$B$8*N138*Assumptions!$B$9+Assumptions!$B$10)</f>
-        <v>729386.04375</v>
+        <v>804887.85</v>
       </c>
       <c r="U138" s="47" t="n">
         <f aca="false">Q138*Assumptions!$B$11*N138</f>
-        <v>71820</v>
+        <v>43128</v>
       </c>
       <c r="V138" s="47" t="n">
         <f aca="false">P138*(Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>292471.641</v>
+        <v>296899.68</v>
       </c>
       <c r="W138" s="47" t="n">
         <f aca="false">P138*IF(P138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
-        <v>288149.4</v>
+        <v>292512</v>
       </c>
       <c r="X138" s="48" t="n">
         <f aca="false">SUM(Q138:W138)</f>
-        <v>7136352.08475</v>
+        <v>7787627.53</v>
       </c>
       <c r="Y138" s="48" t="n">
         <f aca="false">P138-X138</f>
-        <v>67382.9152500005</v>
+        <v>-474827.53</v>
       </c>
       <c r="Z138" s="49" t="n">
         <f aca="false">IF(X138=0,0,Y138/X138)</f>
-        <v>0.00944220722993674</v>
+        <v>-0.0609720390672049</v>
       </c>
       <c r="AA138" s="47" t="n">
         <f aca="false">MAX(0,(P138/(1+Assumptions!$B$27)-(L138*(Assumptions!$B$4+IF(H138="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N138*Assumptions!$B$9+Assumptions!$B$10)))-P138*(Assumptions!$B$12+Assumptions!$B$13+IF(P138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H138="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N138*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N138))</f>
-        <v>1244851.90845354</v>
-      </c>
-      <c r="AB138" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" s="50" t="str">
         <f aca="false">IF(AA138&lt;=0,"no price works",D138/AA138)</f>
-        <v>1.60260026630667</v>
+        <v>no price works</v>
       </c>
       <c r="AC138" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK138,Assumptions!$A$36:$A$48,0))+IF(I138="Yes",Assumptions!$B$23,0)+IF(J138="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
-        <v>1350</v>
+        <v>1000</v>
       </c>
       <c r="AD138" s="47" t="n">
         <f aca="false">(L138)*AC138-(((D138)+(L138)*Assumptions!$B$4+IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N138)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(N138)+(L138)*AC138*(Assumptions!$B$12+Assumptions!$B$13+IF((L138)*AC138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L138)*AC138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-534718.35375</v>
+        <v>-1086044.65</v>
       </c>
       <c r="AE138" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK138,Assumptions!$A$36:$A$48,0))+IF(I138="Yes",Assumptions!$B$23,0)+IF(J138="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
-        <v>1485</v>
+        <v>1100</v>
       </c>
       <c r="AF138" s="47" t="n">
         <f aca="false">(L138)*AE138-(((D138)+(L138)*Assumptions!$B$4+IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N138)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(N138)+(L138)*AE138*(Assumptions!$B$12+Assumptions!$B$13+IF((L138)*AE138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L138)*AE138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>67382.9152500015</v>
+        <v>-474827.529999999</v>
       </c>
       <c r="AG138" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK138,Assumptions!$A$36:$A$48,0))+IF(I138="Yes",Assumptions!$B$23,0)+IF(J138="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
-        <v>1620</v>
+        <v>1200</v>
       </c>
       <c r="AH138" s="47" t="n">
         <f aca="false">(L138)*AG138-(((D138)+(L138)*Assumptions!$B$4+IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N138)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(N138)+(L138)*AG138*(Assumptions!$B$12+Assumptions!$B$13+IF((L138)*AG138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L138)*AG138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>669484.184250001</v>
+        <v>136389.59</v>
       </c>
       <c r="AI138" s="47" t="n">
         <f aca="false">(L138)*AE138-(((D138)+(L138)*Assumptions!$B$25+IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N138)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(N138)+(L138)*AE138*(Assumptions!$B$12+Assumptions!$B$13+IF((L138)*AE138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L138)*AE138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>340676.127750001</v>
+        <v>-100295.829999999</v>
       </c>
       <c r="AJ138" s="47" t="n">
         <f aca="false">(L138)*AE138-(((D138)+(L138)*Assumptions!$B$26+IF(H138="Yes",Assumptions!$B$6*(D138),(L138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N138)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(N138)+(L138)*AE138*(Assumptions!$B$12+Assumptions!$B$13+IF((L138)*AE138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L138)*AE138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>613969.340250001</v>
+        <v>274235.870000001</v>
       </c>
       <c r="AK138" s="40" t="s">
-        <v>103</v>
+        <v>258</v>
       </c>
       <c r="AL138" s="45" t="n">
         <f aca="false">IF(G138&gt;0,G138,ROUND(F138*Assumptions!$B$18,0))</f>
-        <v>2858</v>
+        <v>5060</v>
       </c>
       <c r="AM138" s="45" t="n">
         <f aca="false">IF(H138="Yes",AL138,MAX(AL138,MIN(Assumptions!$B$20,ROUND(E138*Assumptions!$B$19,0))))</f>
-        <v>4851</v>
+        <v>6648</v>
       </c>
       <c r="AN138" s="47" t="n">
         <f aca="false">(AL138)*AE138-(((D138)+(AL138)*Assumptions!$B$4+IF(H138="Yes",Assumptions!$B$6*(D138),(AL138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(Assumptions!$B$21)+(AL138)*AE138*(Assumptions!$B$12+Assumptions!$B$13+IF((AL138)*AE138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL138)*AE138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-555434.790499999</v>
+        <v>-480107.725</v>
       </c>
       <c r="AO138" s="47" t="n">
         <f aca="false">(AM138)*AE138-(((D138)+(AM138)*Assumptions!$B$4+IF(H138="Yes",Assumptions!$B$6*(D138),(AM138)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM138&gt;AL138,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D138)*Assumptions!$B$11*(IF(AM138&gt;AL138,Assumptions!$B$22,Assumptions!$B$21))+(AM138)*AE138*(Assumptions!$B$12+Assumptions!$B$13+IF((AM138)*AE138&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM138)*AE138&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>67382.9152500015</v>
+        <v>-474827.529999999</v>
       </c>
       <c r="AP138" s="47" t="n">
         <f aca="false">Assumptions!$B$7*(Q138+R138+S138)</f>
-        <v>3740441.25</v>
+        <v>4127630</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="40" t="n">
         <v>137</v>
       </c>
@@ -24746,16 +24782,16 @@
         <v>302</v>
       </c>
       <c r="C139" s="40" t="s">
-        <v>257</v>
+        <v>70</v>
       </c>
       <c r="D139" s="41" t="n">
-        <v>1198000</v>
+        <v>3477000</v>
       </c>
       <c r="E139" s="42" t="n">
-        <v>16621</v>
+        <v>17838</v>
       </c>
       <c r="F139" s="42" t="n">
-        <v>4600</v>
+        <v>2588</v>
       </c>
       <c r="G139" s="42"/>
       <c r="H139" s="43" t="s">
@@ -24772,7 +24808,7 @@
       </c>
       <c r="L139" s="45" t="n">
         <f aca="false">IF(AO139&gt;AN139,AM139,AL139)</f>
-        <v>6648</v>
+        <v>7135</v>
       </c>
       <c r="M139" s="40" t="str">
         <f aca="false">IF(AO139&gt;AN139,"Zoning estimate",IF(H139="Yes","Approved plans",IF(G139&gt;0,"Listing claim","110% old house")))</f>
@@ -24784,117 +24820,117 @@
       </c>
       <c r="O139" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK139,Assumptions!$A$36:$A$48,0))+IF(I139="Yes",Assumptions!$B$23,0)+IF(J139="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
-        <v>1100</v>
+        <v>2156</v>
       </c>
       <c r="P139" s="47" t="n">
         <f aca="false">L139*O139</f>
-        <v>7312800</v>
+        <v>15383060</v>
       </c>
       <c r="Q139" s="47" t="n">
         <f aca="false">D139</f>
-        <v>1198000</v>
+        <v>3477000</v>
       </c>
       <c r="R139" s="47" t="n">
         <f aca="false">L139*Assumptions!$B$4</f>
-        <v>4653600</v>
+        <v>4994500</v>
       </c>
       <c r="S139" s="47" t="n">
         <f aca="false">IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5)</f>
-        <v>498600</v>
+        <v>535125</v>
       </c>
       <c r="T139" s="47" t="n">
         <f aca="false">AP139*(Assumptions!$B$8*N139*Assumptions!$B$9+Assumptions!$B$10)</f>
-        <v>804887.85</v>
+        <v>1141589.71875</v>
       </c>
       <c r="U139" s="47" t="n">
         <f aca="false">Q139*Assumptions!$B$11*N139</f>
-        <v>43128</v>
+        <v>125172</v>
       </c>
       <c r="V139" s="47" t="n">
         <f aca="false">P139*(Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>296899.68</v>
+        <v>624552.236</v>
       </c>
       <c r="W139" s="47" t="n">
         <f aca="false">P139*IF(P139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
-        <v>292512</v>
+        <v>846068.3</v>
       </c>
       <c r="X139" s="48" t="n">
         <f aca="false">SUM(Q139:W139)</f>
-        <v>7787627.53</v>
+        <v>11744007.25475</v>
       </c>
       <c r="Y139" s="48" t="n">
         <f aca="false">P139-X139</f>
-        <v>-474827.53</v>
+        <v>3639052.74525</v>
       </c>
       <c r="Z139" s="49" t="n">
         <f aca="false">IF(X139=0,0,Y139/X139)</f>
-        <v>-0.0609720390672049</v>
+        <v>0.309864654058191</v>
       </c>
       <c r="AA139" s="47" t="n">
         <f aca="false">MAX(0,(P139/(1+Assumptions!$B$27)-(L139*(Assumptions!$B$4+IF(H139="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N139*Assumptions!$B$9+Assumptions!$B$10)))-P139*(Assumptions!$B$12+Assumptions!$B$13+IF(P139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H139="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N139*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N139))</f>
-        <v>0</v>
-      </c>
-      <c r="AB139" s="50" t="str">
+        <v>4881056.46810878</v>
+      </c>
+      <c r="AB139" s="50" t="n">
         <f aca="false">IF(AA139&lt;=0,"no price works",D139/AA139)</f>
-        <v>no price works</v>
+        <v>0.712345784712302</v>
       </c>
       <c r="AC139" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK139,Assumptions!$A$36:$A$48,0))+IF(I139="Yes",Assumptions!$B$23,0)+IF(J139="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
-        <v>1000</v>
+        <v>1960</v>
       </c>
       <c r="AD139" s="47" t="n">
         <f aca="false">(L139)*AC139-(((D139)+(L139)*Assumptions!$B$4+IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N139)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(N139)+(L139)*AC139*(Assumptions!$B$12+Assumptions!$B$13+IF((L139)*AC139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L139)*AC139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-1086044.65</v>
+        <v>2374285.52125</v>
       </c>
       <c r="AE139" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK139,Assumptions!$A$36:$A$48,0))+IF(I139="Yes",Assumptions!$B$23,0)+IF(J139="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
-        <v>1100</v>
+        <v>2156</v>
       </c>
       <c r="AF139" s="47" t="n">
         <f aca="false">(L139)*AE139-(((D139)+(L139)*Assumptions!$B$4+IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N139)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(N139)+(L139)*AE139*(Assumptions!$B$12+Assumptions!$B$13+IF((L139)*AE139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L139)*AE139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-474827.529999999</v>
+        <v>3639052.74525</v>
       </c>
       <c r="AG139" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK139,Assumptions!$A$36:$A$48,0))+IF(I139="Yes",Assumptions!$B$23,0)+IF(J139="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
-        <v>1200</v>
+        <v>2352</v>
       </c>
       <c r="AH139" s="47" t="n">
         <f aca="false">(L139)*AG139-(((D139)+(L139)*Assumptions!$B$4+IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N139)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(N139)+(L139)*AG139*(Assumptions!$B$12+Assumptions!$B$13+IF((L139)*AG139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L139)*AG139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>136389.59</v>
+        <v>4903819.96925</v>
       </c>
       <c r="AI139" s="47" t="n">
         <f aca="false">(L139)*AE139-(((D139)+(L139)*Assumptions!$B$25+IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N139)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(N139)+(L139)*AE139*(Assumptions!$B$12+Assumptions!$B$13+IF((L139)*AE139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L139)*AE139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-100295.829999999</v>
+        <v>4041020.80775</v>
       </c>
       <c r="AJ139" s="47" t="n">
         <f aca="false">(L139)*AE139-(((D139)+(L139)*Assumptions!$B$26+IF(H139="Yes",Assumptions!$B$6*(D139),(L139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N139)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(N139)+(L139)*AE139*(Assumptions!$B$12+Assumptions!$B$13+IF((L139)*AE139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L139)*AE139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>274235.870000001</v>
+        <v>4442988.87025</v>
       </c>
       <c r="AK139" s="40" t="s">
-        <v>258</v>
+        <v>73</v>
       </c>
       <c r="AL139" s="45" t="n">
         <f aca="false">IF(G139&gt;0,G139,ROUND(F139*Assumptions!$B$18,0))</f>
-        <v>5060</v>
+        <v>2847</v>
       </c>
       <c r="AM139" s="45" t="n">
         <f aca="false">IF(H139="Yes",AL139,MAX(AL139,MIN(Assumptions!$B$20,ROUND(E139*Assumptions!$B$19,0))))</f>
-        <v>6648</v>
+        <v>7135</v>
       </c>
       <c r="AN139" s="47" t="n">
         <f aca="false">(AL139)*AE139-(((D139)+(AL139)*Assumptions!$B$4+IF(H139="Yes",Assumptions!$B$6*(D139),(AL139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(Assumptions!$B$21)+(AL139)*AE139*(Assumptions!$B$12+Assumptions!$B$13+IF((AL139)*AE139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL139)*AE139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-480107.725</v>
+        <v>-622194.98295</v>
       </c>
       <c r="AO139" s="47" t="n">
         <f aca="false">(AM139)*AE139-(((D139)+(AM139)*Assumptions!$B$4+IF(H139="Yes",Assumptions!$B$6*(D139),(AM139)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM139&gt;AL139,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D139)*Assumptions!$B$11*(IF(AM139&gt;AL139,Assumptions!$B$22,Assumptions!$B$21))+(AM139)*AE139*(Assumptions!$B$12+Assumptions!$B$13+IF((AM139)*AE139&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM139)*AE139&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-474827.529999999</v>
+        <v>3639052.74525</v>
       </c>
       <c r="AP139" s="47" t="n">
         <f aca="false">Assumptions!$B$7*(Q139+R139+S139)</f>
-        <v>4127630</v>
+        <v>5854306.25</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="40" t="n">
         <v>138</v>
       </c>
@@ -24902,23 +24938,23 @@
         <v>304</v>
       </c>
       <c r="C140" s="40" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D140" s="41" t="n">
-        <v>3477000</v>
+        <v>1385000</v>
       </c>
       <c r="E140" s="42" t="n">
-        <v>17838</v>
+        <v>5624</v>
       </c>
       <c r="F140" s="42" t="n">
-        <v>2588</v>
+        <v>1148</v>
       </c>
       <c r="G140" s="42"/>
       <c r="H140" s="43" t="s">
         <v>71</v>
       </c>
       <c r="I140" s="43" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="J140" s="43" t="s">
         <v>71</v>
@@ -24928,7 +24964,7 @@
       </c>
       <c r="L140" s="45" t="n">
         <f aca="false">IF(AO140&gt;AN140,AM140,AL140)</f>
-        <v>7135</v>
+        <v>2250</v>
       </c>
       <c r="M140" s="40" t="str">
         <f aca="false">IF(AO140&gt;AN140,"Zoning estimate",IF(H140="Yes","Approved plans",IF(G140&gt;0,"Listing claim","110% old house")))</f>
@@ -24940,114 +24976,114 @@
       </c>
       <c r="O140" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK140,Assumptions!$A$36:$A$48,0))+IF(I140="Yes",Assumptions!$B$23,0)+IF(J140="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
-        <v>2156</v>
+        <v>1540</v>
       </c>
       <c r="P140" s="47" t="n">
         <f aca="false">L140*O140</f>
-        <v>15383060</v>
+        <v>3465000</v>
       </c>
       <c r="Q140" s="47" t="n">
         <f aca="false">D140</f>
-        <v>3477000</v>
+        <v>1385000</v>
       </c>
       <c r="R140" s="47" t="n">
         <f aca="false">L140*Assumptions!$B$4</f>
-        <v>4994500</v>
+        <v>1575000</v>
       </c>
       <c r="S140" s="47" t="n">
         <f aca="false">IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5)</f>
-        <v>535125</v>
+        <v>168750</v>
       </c>
       <c r="T140" s="47" t="n">
         <f aca="false">AP140*(Assumptions!$B$8*N140*Assumptions!$B$9+Assumptions!$B$10)</f>
-        <v>1141589.71875</v>
+        <v>396569.0625</v>
       </c>
       <c r="U140" s="47" t="n">
         <f aca="false">Q140*Assumptions!$B$11*N140</f>
-        <v>125172</v>
+        <v>49860</v>
       </c>
       <c r="V140" s="47" t="n">
         <f aca="false">P140*(Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>624552.236</v>
+        <v>140679</v>
       </c>
       <c r="W140" s="47" t="n">
         <f aca="false">P140*IF(P140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
-        <v>846068.3</v>
+        <v>0</v>
       </c>
       <c r="X140" s="48" t="n">
         <f aca="false">SUM(Q140:W140)</f>
-        <v>11744007.25475</v>
+        <v>3715858.0625</v>
       </c>
       <c r="Y140" s="48" t="n">
         <f aca="false">P140-X140</f>
-        <v>3639052.74525</v>
+        <v>-250858.0625</v>
       </c>
       <c r="Z140" s="49" t="n">
         <f aca="false">IF(X140=0,0,Y140/X140)</f>
-        <v>0.309864654058191</v>
+        <v>-0.0675101304411031</v>
       </c>
       <c r="AA140" s="47" t="n">
         <f aca="false">MAX(0,(P140/(1+Assumptions!$B$27)-(L140*(Assumptions!$B$4+IF(H140="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N140*Assumptions!$B$9+Assumptions!$B$10)))-P140*(Assumptions!$B$12+Assumptions!$B$13+IF(P140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H140="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N140*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N140))</f>
-        <v>4881056.46810878</v>
+        <v>780558.302094922</v>
       </c>
       <c r="AB140" s="50" t="n">
         <f aca="false">IF(AA140&lt;=0,"no price works",D140/AA140)</f>
-        <v>0.712345784712302</v>
+        <v>1.77437098072345</v>
       </c>
       <c r="AC140" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK140,Assumptions!$A$36:$A$48,0))+IF(I140="Yes",Assumptions!$B$23,0)+IF(J140="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
-        <v>1960</v>
+        <v>1400</v>
       </c>
       <c r="AD140" s="47" t="n">
         <f aca="false">(L140)*AC140-(((D140)+(L140)*Assumptions!$B$4+IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N140)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(N140)+(L140)*AC140*(Assumptions!$B$12+Assumptions!$B$13+IF((L140)*AC140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L140)*AC140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>2374285.52125</v>
+        <v>-553069.0625</v>
       </c>
       <c r="AE140" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK140,Assumptions!$A$36:$A$48,0))+IF(I140="Yes",Assumptions!$B$23,0)+IF(J140="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
-        <v>2156</v>
+        <v>1540</v>
       </c>
       <c r="AF140" s="47" t="n">
         <f aca="false">(L140)*AE140-(((D140)+(L140)*Assumptions!$B$4+IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N140)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(N140)+(L140)*AE140*(Assumptions!$B$12+Assumptions!$B$13+IF((L140)*AE140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L140)*AE140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>3639052.74525</v>
+        <v>-250858.062499999</v>
       </c>
       <c r="AG140" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK140,Assumptions!$A$36:$A$48,0))+IF(I140="Yes",Assumptions!$B$23,0)+IF(J140="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
-        <v>2352</v>
+        <v>1680</v>
       </c>
       <c r="AH140" s="47" t="n">
         <f aca="false">(L140)*AG140-(((D140)+(L140)*Assumptions!$B$4+IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N140)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(N140)+(L140)*AG140*(Assumptions!$B$12+Assumptions!$B$13+IF((L140)*AG140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L140)*AG140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>4903819.96925</v>
+        <v>51352.9375000005</v>
       </c>
       <c r="AI140" s="47" t="n">
         <f aca="false">(L140)*AE140-(((D140)+(L140)*Assumptions!$B$25+IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N140)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(N140)+(L140)*AE140*(Assumptions!$B$12+Assumptions!$B$13+IF((L140)*AE140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L140)*AE140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>4041020.80775</v>
+        <v>-124098.687499999</v>
       </c>
       <c r="AJ140" s="47" t="n">
         <f aca="false">(L140)*AE140-(((D140)+(L140)*Assumptions!$B$26+IF(H140="Yes",Assumptions!$B$6*(D140),(L140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N140)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(N140)+(L140)*AE140*(Assumptions!$B$12+Assumptions!$B$13+IF((L140)*AE140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L140)*AE140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>4442988.87025</v>
+        <v>2660.68750000093</v>
       </c>
       <c r="AK140" s="40" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AL140" s="45" t="n">
         <f aca="false">IF(G140&gt;0,G140,ROUND(F140*Assumptions!$B$18,0))</f>
-        <v>2847</v>
+        <v>1263</v>
       </c>
       <c r="AM140" s="45" t="n">
         <f aca="false">IF(H140="Yes",AL140,MAX(AL140,MIN(Assumptions!$B$20,ROUND(E140*Assumptions!$B$19,0))))</f>
-        <v>7135</v>
+        <v>2250</v>
       </c>
       <c r="AN140" s="47" t="n">
         <f aca="false">(AL140)*AE140-(((D140)+(AL140)*Assumptions!$B$4+IF(H140="Yes",Assumptions!$B$6*(D140),(AL140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(Assumptions!$B$21)+(AL140)*AE140*(Assumptions!$B$12+Assumptions!$B$13+IF((AL140)*AE140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL140)*AE140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-622194.98295</v>
+        <v>-738438.45575</v>
       </c>
       <c r="AO140" s="47" t="n">
         <f aca="false">(AM140)*AE140-(((D140)+(AM140)*Assumptions!$B$4+IF(H140="Yes",Assumptions!$B$6*(D140),(AM140)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM140&gt;AL140,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D140)*Assumptions!$B$11*(IF(AM140&gt;AL140,Assumptions!$B$22,Assumptions!$B$21))+(AM140)*AE140*(Assumptions!$B$12+Assumptions!$B$13+IF((AM140)*AE140&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM140)*AE140&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>3639052.74525</v>
+        <v>-250858.062499999</v>
       </c>
       <c r="AP140" s="47" t="n">
         <f aca="false">Assumptions!$B$7*(Q140+R140+S140)</f>
-        <v>5854306.25</v>
+        <v>2033687.5</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25058,16 +25094,16 @@
         <v>306</v>
       </c>
       <c r="C141" s="40" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D141" s="41" t="n">
-        <v>1385000</v>
+        <v>2295000</v>
       </c>
       <c r="E141" s="42" t="n">
-        <v>5624</v>
+        <v>8250</v>
       </c>
       <c r="F141" s="42" t="n">
-        <v>1148</v>
+        <v>1501</v>
       </c>
       <c r="G141" s="42"/>
       <c r="H141" s="43" t="s">
@@ -25084,7 +25120,7 @@
       </c>
       <c r="L141" s="45" t="n">
         <f aca="false">IF(AO141&gt;AN141,AM141,AL141)</f>
-        <v>2250</v>
+        <v>3300</v>
       </c>
       <c r="M141" s="40" t="str">
         <f aca="false">IF(AO141&gt;AN141,"Zoning estimate",IF(H141="Yes","Approved plans",IF(G141&gt;0,"Listing claim","110% old house")))</f>
@@ -25100,31 +25136,31 @@
       </c>
       <c r="P141" s="47" t="n">
         <f aca="false">L141*O141</f>
-        <v>3465000</v>
+        <v>5082000</v>
       </c>
       <c r="Q141" s="47" t="n">
         <f aca="false">D141</f>
-        <v>1385000</v>
+        <v>2295000</v>
       </c>
       <c r="R141" s="47" t="n">
         <f aca="false">L141*Assumptions!$B$4</f>
-        <v>1575000</v>
+        <v>2310000</v>
       </c>
       <c r="S141" s="47" t="n">
         <f aca="false">IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5)</f>
-        <v>168750</v>
+        <v>247500</v>
       </c>
       <c r="T141" s="47" t="n">
         <f aca="false">AP141*(Assumptions!$B$8*N141*Assumptions!$B$9+Assumptions!$B$10)</f>
-        <v>396569.0625</v>
+        <v>615054.375</v>
       </c>
       <c r="U141" s="47" t="n">
         <f aca="false">Q141*Assumptions!$B$11*N141</f>
-        <v>49860</v>
+        <v>82620</v>
       </c>
       <c r="V141" s="47" t="n">
         <f aca="false">P141*(Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>140679</v>
+        <v>206329.2</v>
       </c>
       <c r="W141" s="47" t="n">
         <f aca="false">P141*IF(P141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
@@ -25132,23 +25168,23 @@
       </c>
       <c r="X141" s="48" t="n">
         <f aca="false">SUM(Q141:W141)</f>
-        <v>3715858.0625</v>
+        <v>5756503.575</v>
       </c>
       <c r="Y141" s="48" t="n">
         <f aca="false">P141-X141</f>
-        <v>-250858.0625</v>
+        <v>-674503.574999999</v>
       </c>
       <c r="Z141" s="49" t="n">
         <f aca="false">IF(X141=0,0,Y141/X141)</f>
-        <v>-0.0675101304411031</v>
+        <v>-0.117172440911756</v>
       </c>
       <c r="AA141" s="47" t="n">
         <f aca="false">MAX(0,(P141/(1+Assumptions!$B$27)-(L141*(Assumptions!$B$4+IF(H141="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N141*Assumptions!$B$9+Assumptions!$B$10)))-P141*(Assumptions!$B$12+Assumptions!$B$13+IF(P141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H141="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N141*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N141))</f>
-        <v>780558.302094922</v>
+        <v>1144818.84307255</v>
       </c>
       <c r="AB141" s="50" t="n">
         <f aca="false">IF(AA141&lt;=0,"no price works",D141/AA141)</f>
-        <v>1.77437098072345</v>
+        <v>2.0046839846211</v>
       </c>
       <c r="AC141" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK141,Assumptions!$A$36:$A$48,0))+IF(I141="Yes",Assumptions!$B$23,0)+IF(J141="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
@@ -25156,7 +25192,7 @@
       </c>
       <c r="AD141" s="47" t="n">
         <f aca="false">(L141)*AC141-(((D141)+(L141)*Assumptions!$B$4+IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N141)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(N141)+(L141)*AC141*(Assumptions!$B$12+Assumptions!$B$13+IF((L141)*AC141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L141)*AC141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-553069.0625</v>
+        <v>-1117746.375</v>
       </c>
       <c r="AE141" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK141,Assumptions!$A$36:$A$48,0))+IF(I141="Yes",Assumptions!$B$23,0)+IF(J141="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
@@ -25164,7 +25200,7 @@
       </c>
       <c r="AF141" s="47" t="n">
         <f aca="false">(L141)*AE141-(((D141)+(L141)*Assumptions!$B$4+IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N141)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(N141)+(L141)*AE141*(Assumptions!$B$12+Assumptions!$B$13+IF((L141)*AE141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L141)*AE141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-250858.062499999</v>
+        <v>-674503.574999999</v>
       </c>
       <c r="AG141" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK141,Assumptions!$A$36:$A$48,0))+IF(I141="Yes",Assumptions!$B$23,0)+IF(J141="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
@@ -25172,38 +25208,38 @@
       </c>
       <c r="AH141" s="47" t="n">
         <f aca="false">(L141)*AG141-(((D141)+(L141)*Assumptions!$B$4+IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N141)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(N141)+(L141)*AG141*(Assumptions!$B$12+Assumptions!$B$13+IF((L141)*AG141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L141)*AG141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>51352.9375000005</v>
+        <v>-453020.775</v>
       </c>
       <c r="AI141" s="47" t="n">
         <f aca="false">(L141)*AE141-(((D141)+(L141)*Assumptions!$B$25+IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N141)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(N141)+(L141)*AE141*(Assumptions!$B$12+Assumptions!$B$13+IF((L141)*AE141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L141)*AE141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-124098.687499999</v>
+        <v>-488589.824999999</v>
       </c>
       <c r="AJ141" s="47" t="n">
         <f aca="false">(L141)*AE141-(((D141)+(L141)*Assumptions!$B$26+IF(H141="Yes",Assumptions!$B$6*(D141),(L141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N141)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(N141)+(L141)*AE141*(Assumptions!$B$12+Assumptions!$B$13+IF((L141)*AE141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L141)*AE141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>2660.68750000093</v>
+        <v>-302676.074999999</v>
       </c>
       <c r="AK141" s="40" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AL141" s="45" t="n">
         <f aca="false">IF(G141&gt;0,G141,ROUND(F141*Assumptions!$B$18,0))</f>
-        <v>1263</v>
+        <v>1651</v>
       </c>
       <c r="AM141" s="45" t="n">
         <f aca="false">IF(H141="Yes",AL141,MAX(AL141,MIN(Assumptions!$B$20,ROUND(E141*Assumptions!$B$19,0))))</f>
-        <v>2250</v>
+        <v>3300</v>
       </c>
       <c r="AN141" s="47" t="n">
         <f aca="false">(AL141)*AE141-(((D141)+(AL141)*Assumptions!$B$4+IF(H141="Yes",Assumptions!$B$6*(D141),(AL141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(Assumptions!$B$21)+(AL141)*AE141*(Assumptions!$B$12+Assumptions!$B$13+IF((AL141)*AE141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL141)*AE141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-738438.45575</v>
+        <v>-1503956.69275</v>
       </c>
       <c r="AO141" s="47" t="n">
         <f aca="false">(AM141)*AE141-(((D141)+(AM141)*Assumptions!$B$4+IF(H141="Yes",Assumptions!$B$6*(D141),(AM141)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM141&gt;AL141,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D141)*Assumptions!$B$11*(IF(AM141&gt;AL141,Assumptions!$B$22,Assumptions!$B$21))+(AM141)*AE141*(Assumptions!$B$12+Assumptions!$B$13+IF((AM141)*AE141&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM141)*AE141&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-250858.062499999</v>
+        <v>-674503.574999999</v>
       </c>
       <c r="AP141" s="47" t="n">
         <f aca="false">Assumptions!$B$7*(Q141+R141+S141)</f>
-        <v>2033687.5</v>
+        <v>3154125</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25214,16 +25250,16 @@
         <v>308</v>
       </c>
       <c r="C142" s="40" t="s">
-        <v>111</v>
+        <v>257</v>
       </c>
       <c r="D142" s="41" t="n">
-        <v>2295000</v>
+        <v>980000</v>
       </c>
       <c r="E142" s="42" t="n">
-        <v>8250</v>
+        <v>6162</v>
       </c>
       <c r="F142" s="42" t="n">
-        <v>1501</v>
+        <v>2958</v>
       </c>
       <c r="G142" s="42"/>
       <c r="H142" s="43" t="s">
@@ -25240,47 +25276,47 @@
       </c>
       <c r="L142" s="45" t="n">
         <f aca="false">IF(AO142&gt;AN142,AM142,AL142)</f>
-        <v>3300</v>
+        <v>3254</v>
       </c>
       <c r="M142" s="40" t="str">
         <f aca="false">IF(AO142&gt;AN142,"Zoning estimate",IF(H142="Yes","Approved plans",IF(G142&gt;0,"Listing claim","110% old house")))</f>
-        <v>Zoning estimate</v>
+        <v>110% old house</v>
       </c>
       <c r="N142" s="45" t="n">
         <f aca="false">IF(AO142&gt;AN142,IF(AM142&gt;AL142,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O142" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK142,Assumptions!$A$36:$A$48,0))+IF(I142="Yes",Assumptions!$B$23,0)+IF(J142="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
-        <v>1540</v>
+        <v>990</v>
       </c>
       <c r="P142" s="47" t="n">
         <f aca="false">L142*O142</f>
-        <v>5082000</v>
+        <v>3221460</v>
       </c>
       <c r="Q142" s="47" t="n">
         <f aca="false">D142</f>
-        <v>2295000</v>
+        <v>980000</v>
       </c>
       <c r="R142" s="47" t="n">
         <f aca="false">L142*Assumptions!$B$4</f>
-        <v>2310000</v>
+        <v>2277800</v>
       </c>
       <c r="S142" s="47" t="n">
         <f aca="false">IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5)</f>
-        <v>247500</v>
+        <v>244050</v>
       </c>
       <c r="T142" s="47" t="n">
         <f aca="false">AP142*(Assumptions!$B$8*N142*Assumptions!$B$9+Assumptions!$B$10)</f>
-        <v>615054.375</v>
+        <v>307287.3375</v>
       </c>
       <c r="U142" s="47" t="n">
         <f aca="false">Q142*Assumptions!$B$11*N142</f>
-        <v>82620</v>
+        <v>23520</v>
       </c>
       <c r="V142" s="47" t="n">
         <f aca="false">P142*(Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>206329.2</v>
+        <v>130791.276</v>
       </c>
       <c r="W142" s="47" t="n">
         <f aca="false">P142*IF(P142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
@@ -25288,81 +25324,81 @@
       </c>
       <c r="X142" s="48" t="n">
         <f aca="false">SUM(Q142:W142)</f>
-        <v>5756503.575</v>
+        <v>3963448.6135</v>
       </c>
       <c r="Y142" s="48" t="n">
         <f aca="false">P142-X142</f>
-        <v>-674503.574999999</v>
+        <v>-741988.6135</v>
       </c>
       <c r="Z142" s="49" t="n">
         <f aca="false">IF(X142=0,0,Y142/X142)</f>
-        <v>-0.117172440911756</v>
+        <v>-0.18720782981081</v>
       </c>
       <c r="AA142" s="47" t="n">
         <f aca="false">MAX(0,(P142/(1+Assumptions!$B$27)-(L142*(Assumptions!$B$4+IF(H142="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N142*Assumptions!$B$9+Assumptions!$B$10)))-P142*(Assumptions!$B$12+Assumptions!$B$13+IF(P142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H142="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N142*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N142))</f>
-        <v>1144818.84307255</v>
-      </c>
-      <c r="AB142" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" s="50" t="str">
         <f aca="false">IF(AA142&lt;=0,"no price works",D142/AA142)</f>
-        <v>2.0046839846211</v>
+        <v>no price works</v>
       </c>
       <c r="AC142" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK142,Assumptions!$A$36:$A$48,0))+IF(I142="Yes",Assumptions!$B$23,0)+IF(J142="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="AD142" s="47" t="n">
         <f aca="false">(L142)*AC142-(((D142)+(L142)*Assumptions!$B$4+IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N142)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(N142)+(L142)*AC142*(Assumptions!$B$12+Assumptions!$B$13+IF((L142)*AC142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L142)*AC142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-1117746.375</v>
+        <v>-1022958.4975</v>
       </c>
       <c r="AE142" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK142,Assumptions!$A$36:$A$48,0))+IF(I142="Yes",Assumptions!$B$23,0)+IF(J142="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
-        <v>1540</v>
+        <v>990</v>
       </c>
       <c r="AF142" s="47" t="n">
         <f aca="false">(L142)*AE142-(((D142)+(L142)*Assumptions!$B$4+IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N142)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(N142)+(L142)*AE142*(Assumptions!$B$12+Assumptions!$B$13+IF((L142)*AE142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L142)*AE142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-674503.574999999</v>
+        <v>-741988.6135</v>
       </c>
       <c r="AG142" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK142,Assumptions!$A$36:$A$48,0))+IF(I142="Yes",Assumptions!$B$23,0)+IF(J142="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
-        <v>1680</v>
+        <v>1080</v>
       </c>
       <c r="AH142" s="47" t="n">
         <f aca="false">(L142)*AG142-(((D142)+(L142)*Assumptions!$B$4+IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N142)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(N142)+(L142)*AG142*(Assumptions!$B$12+Assumptions!$B$13+IF((L142)*AG142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L142)*AG142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-453020.775</v>
+        <v>-461018.7295</v>
       </c>
       <c r="AI142" s="47" t="n">
         <f aca="false">(L142)*AE142-(((D142)+(L142)*Assumptions!$B$25+IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N142)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(N142)+(L142)*AE142*(Assumptions!$B$12+Assumptions!$B$13+IF((L142)*AE142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L142)*AE142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-488589.824999999</v>
+        <v>-565011.6885</v>
       </c>
       <c r="AJ142" s="47" t="n">
         <f aca="false">(L142)*AE142-(((D142)+(L142)*Assumptions!$B$26+IF(H142="Yes",Assumptions!$B$6*(D142),(L142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N142)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(N142)+(L142)*AE142*(Assumptions!$B$12+Assumptions!$B$13+IF((L142)*AE142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L142)*AE142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-302676.074999999</v>
+        <v>-388034.763499999</v>
       </c>
       <c r="AK142" s="40" t="s">
-        <v>113</v>
+        <v>258</v>
       </c>
       <c r="AL142" s="45" t="n">
         <f aca="false">IF(G142&gt;0,G142,ROUND(F142*Assumptions!$B$18,0))</f>
-        <v>1651</v>
+        <v>3254</v>
       </c>
       <c r="AM142" s="45" t="n">
         <f aca="false">IF(H142="Yes",AL142,MAX(AL142,MIN(Assumptions!$B$20,ROUND(E142*Assumptions!$B$19,0))))</f>
-        <v>3300</v>
+        <v>3254</v>
       </c>
       <c r="AN142" s="47" t="n">
         <f aca="false">(AL142)*AE142-(((D142)+(AL142)*Assumptions!$B$4+IF(H142="Yes",Assumptions!$B$6*(D142),(AL142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(Assumptions!$B$21)+(AL142)*AE142*(Assumptions!$B$12+Assumptions!$B$13+IF((AL142)*AE142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL142)*AE142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-1503956.69275</v>
+        <v>-741988.6135</v>
       </c>
       <c r="AO142" s="47" t="n">
         <f aca="false">(AM142)*AE142-(((D142)+(AM142)*Assumptions!$B$4+IF(H142="Yes",Assumptions!$B$6*(D142),(AM142)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM142&gt;AL142,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D142)*Assumptions!$B$11*(IF(AM142&gt;AL142,Assumptions!$B$22,Assumptions!$B$21))+(AM142)*AE142*(Assumptions!$B$12+Assumptions!$B$13+IF((AM142)*AE142&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM142)*AE142&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-674503.574999999</v>
+        <v>-741988.6135</v>
       </c>
       <c r="AP142" s="47" t="n">
         <f aca="false">Assumptions!$B$7*(Q142+R142+S142)</f>
-        <v>3154125</v>
+        <v>2276202.5</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="40" t="n">
         <v>141</v>
       </c>
@@ -25370,23 +25406,23 @@
         <v>310</v>
       </c>
       <c r="C143" s="40" t="s">
-        <v>257</v>
+        <v>102</v>
       </c>
       <c r="D143" s="41" t="n">
-        <v>980000</v>
+        <v>1395000</v>
       </c>
       <c r="E143" s="42" t="n">
-        <v>6162</v>
+        <v>6282</v>
       </c>
       <c r="F143" s="42" t="n">
-        <v>2958</v>
+        <v>1538</v>
       </c>
       <c r="G143" s="42"/>
       <c r="H143" s="43" t="s">
         <v>71</v>
       </c>
       <c r="I143" s="43" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="J143" s="43" t="s">
         <v>71</v>
@@ -25396,47 +25432,47 @@
       </c>
       <c r="L143" s="45" t="n">
         <f aca="false">IF(AO143&gt;AN143,AM143,AL143)</f>
-        <v>3254</v>
+        <v>2513</v>
       </c>
       <c r="M143" s="40" t="str">
         <f aca="false">IF(AO143&gt;AN143,"Zoning estimate",IF(H143="Yes","Approved plans",IF(G143&gt;0,"Listing claim","110% old house")))</f>
-        <v>110% old house</v>
+        <v>Zoning estimate</v>
       </c>
       <c r="N143" s="45" t="n">
         <f aca="false">IF(AO143&gt;AN143,IF(AM143&gt;AL143,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O143" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK143,Assumptions!$A$36:$A$48,0))+IF(I143="Yes",Assumptions!$B$23,0)+IF(J143="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
-        <v>990</v>
+        <v>1485</v>
       </c>
       <c r="P143" s="47" t="n">
         <f aca="false">L143*O143</f>
-        <v>3221460</v>
+        <v>3731805</v>
       </c>
       <c r="Q143" s="47" t="n">
         <f aca="false">D143</f>
-        <v>980000</v>
+        <v>1395000</v>
       </c>
       <c r="R143" s="47" t="n">
         <f aca="false">L143*Assumptions!$B$4</f>
-        <v>2277800</v>
+        <v>1759100</v>
       </c>
       <c r="S143" s="47" t="n">
         <f aca="false">IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5)</f>
-        <v>244050</v>
+        <v>188475</v>
       </c>
       <c r="T143" s="47" t="n">
         <f aca="false">AP143*(Assumptions!$B$8*N143*Assumptions!$B$9+Assumptions!$B$10)</f>
-        <v>307287.3375</v>
+        <v>423671.38125</v>
       </c>
       <c r="U143" s="47" t="n">
         <f aca="false">Q143*Assumptions!$B$11*N143</f>
-        <v>23520</v>
+        <v>50220</v>
       </c>
       <c r="V143" s="47" t="n">
         <f aca="false">P143*(Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>130791.276</v>
+        <v>151511.283</v>
       </c>
       <c r="W143" s="47" t="n">
         <f aca="false">P143*IF(P143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
@@ -25444,82 +25480,1020 @@
       </c>
       <c r="X143" s="48" t="n">
         <f aca="false">SUM(Q143:W143)</f>
-        <v>3963448.6135</v>
+        <v>3967977.66425</v>
       </c>
       <c r="Y143" s="48" t="n">
         <f aca="false">P143-X143</f>
-        <v>-741988.6135</v>
+        <v>-236172.664249999</v>
       </c>
       <c r="Z143" s="49" t="n">
         <f aca="false">IF(X143=0,0,Y143/X143)</f>
-        <v>-0.18720782981081</v>
+        <v>-0.0595196556618318</v>
       </c>
       <c r="AA143" s="47" t="n">
         <f aca="false">MAX(0,(P143/(1+Assumptions!$B$27)-(L143*(Assumptions!$B$4+IF(H143="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N143*Assumptions!$B$9+Assumptions!$B$10)))-P143*(Assumptions!$B$12+Assumptions!$B$13+IF(P143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H143="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N143*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N143))</f>
-        <v>0</v>
-      </c>
-      <c r="AB143" s="50" t="str">
+        <v>773258.578230021</v>
+      </c>
+      <c r="AB143" s="50" t="n">
         <f aca="false">IF(AA143&lt;=0,"no price works",D143/AA143)</f>
-        <v>no price works</v>
+        <v>1.8040537011476</v>
       </c>
       <c r="AC143" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK143,Assumptions!$A$36:$A$48,0))+IF(I143="Yes",Assumptions!$B$23,0)+IF(J143="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
-        <v>900</v>
+        <v>1350</v>
       </c>
       <c r="AD143" s="47" t="n">
         <f aca="false">(L143)*AC143-(((D143)+(L143)*Assumptions!$B$4+IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N143)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(N143)+(L143)*AC143*(Assumptions!$B$12+Assumptions!$B$13+IF((L143)*AC143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L143)*AC143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-1022958.4975</v>
+        <v>-561653.91125</v>
       </c>
       <c r="AE143" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK143,Assumptions!$A$36:$A$48,0))+IF(I143="Yes",Assumptions!$B$23,0)+IF(J143="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
-        <v>990</v>
+        <v>1485</v>
       </c>
       <c r="AF143" s="47" t="n">
         <f aca="false">(L143)*AE143-(((D143)+(L143)*Assumptions!$B$4+IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N143)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(N143)+(L143)*AE143*(Assumptions!$B$12+Assumptions!$B$13+IF((L143)*AE143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L143)*AE143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-741988.6135</v>
+        <v>-236172.664249999</v>
       </c>
       <c r="AG143" s="46" t="n">
         <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK143,Assumptions!$A$36:$A$48,0))+IF(I143="Yes",Assumptions!$B$23,0)+IF(J143="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
-        <v>1080</v>
+        <v>1620</v>
       </c>
       <c r="AH143" s="47" t="n">
         <f aca="false">(L143)*AG143-(((D143)+(L143)*Assumptions!$B$4+IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N143)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(N143)+(L143)*AG143*(Assumptions!$B$12+Assumptions!$B$13+IF((L143)*AG143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L143)*AG143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-461018.7295</v>
+        <v>89308.5827500005</v>
       </c>
       <c r="AI143" s="47" t="n">
         <f aca="false">(L143)*AE143-(((D143)+(L143)*Assumptions!$B$25+IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N143)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(N143)+(L143)*AE143*(Assumptions!$B$12+Assumptions!$B$13+IF((L143)*AE143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L143)*AE143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-565011.6885</v>
+        <v>-94596.5267499993</v>
       </c>
       <c r="AJ143" s="47" t="n">
         <f aca="false">(L143)*AE143-(((D143)+(L143)*Assumptions!$B$26+IF(H143="Yes",Assumptions!$B$6*(D143),(L143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N143)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(N143)+(L143)*AE143*(Assumptions!$B$12+Assumptions!$B$13+IF((L143)*AE143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L143)*AE143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-388034.763499999</v>
+        <v>46979.6107500009</v>
       </c>
       <c r="AK143" s="40" t="s">
-        <v>258</v>
+        <v>103</v>
       </c>
       <c r="AL143" s="45" t="n">
         <f aca="false">IF(G143&gt;0,G143,ROUND(F143*Assumptions!$B$18,0))</f>
-        <v>3254</v>
+        <v>1692</v>
       </c>
       <c r="AM143" s="45" t="n">
         <f aca="false">IF(H143="Yes",AL143,MAX(AL143,MIN(Assumptions!$B$20,ROUND(E143*Assumptions!$B$19,0))))</f>
-        <v>3254</v>
+        <v>2513</v>
       </c>
       <c r="AN143" s="47" t="n">
         <f aca="false">(AL143)*AE143-(((D143)+(AL143)*Assumptions!$B$4+IF(H143="Yes",Assumptions!$B$6*(D143),(AL143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(Assumptions!$B$21)+(AL143)*AE143*(Assumptions!$B$12+Assumptions!$B$13+IF((AL143)*AE143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL143)*AE143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-741988.6135</v>
+        <v>-566650.197</v>
       </c>
       <c r="AO143" s="47" t="n">
         <f aca="false">(AM143)*AE143-(((D143)+(AM143)*Assumptions!$B$4+IF(H143="Yes",Assumptions!$B$6*(D143),(AM143)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM143&gt;AL143,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D143)*Assumptions!$B$11*(IF(AM143&gt;AL143,Assumptions!$B$22,Assumptions!$B$21))+(AM143)*AE143*(Assumptions!$B$12+Assumptions!$B$13+IF((AM143)*AE143&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM143)*AE143&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
-        <v>-741988.6135</v>
+        <v>-236172.664249999</v>
       </c>
       <c r="AP143" s="47" t="n">
         <f aca="false">Assumptions!$B$7*(Q143+R143+S143)</f>
-        <v>2276202.5</v>
+        <v>2172673.75</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="40" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="40" t="s">
+        <v>312</v>
+      </c>
+      <c r="C144" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="D144" s="41" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="E144" s="42" t="n">
+        <v>7587</v>
+      </c>
+      <c r="F144" s="42" t="n">
+        <v>5309</v>
+      </c>
+      <c r="G144" s="42" t="n">
+        <v>5309</v>
+      </c>
+      <c r="H144" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="I144" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J144" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K144" s="44" t="s">
+        <v>313</v>
+      </c>
+      <c r="L144" s="45" t="n">
+        <f aca="false">IF(AO144&gt;AN144,AM144,AL144)</f>
+        <v>5309</v>
+      </c>
+      <c r="M144" s="40" t="str">
+        <f aca="false">IF(AO144&gt;AN144,"Zoning estimate",IF(H144="Yes","Approved plans",IF(G144&gt;0,"Listing claim","110% old house")))</f>
+        <v>Approved plans</v>
+      </c>
+      <c r="N144" s="45" t="n">
+        <f aca="false">IF(AO144&gt;AN144,IF(AM144&gt;AL144,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O144" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK144,Assumptions!$A$36:$A$48,0))+IF(I144="Yes",Assumptions!$B$23,0)+IF(J144="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1650</v>
+      </c>
+      <c r="P144" s="47" t="n">
+        <f aca="false">L144*O144</f>
+        <v>8759850</v>
+      </c>
+      <c r="Q144" s="47" t="n">
+        <f aca="false">D144</f>
+        <v>3250000</v>
+      </c>
+      <c r="R144" s="47" t="n">
+        <f aca="false">L144*Assumptions!$B$4</f>
+        <v>3716300</v>
+      </c>
+      <c r="S144" s="47" t="n">
+        <f aca="false">IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5)</f>
+        <v>162500</v>
+      </c>
+      <c r="T144" s="47" t="n">
+        <f aca="false">AP144*(Assumptions!$B$8*N144*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>625552.2</v>
+      </c>
+      <c r="U144" s="47" t="n">
+        <f aca="false">Q144*Assumptions!$B$11*N144</f>
+        <v>78000</v>
+      </c>
+      <c r="V144" s="47" t="n">
+        <f aca="false">P144*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>355649.91</v>
+      </c>
+      <c r="W144" s="47" t="n">
+        <f aca="false">P144*IF(P144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>350394</v>
+      </c>
+      <c r="X144" s="48" t="n">
+        <f aca="false">SUM(Q144:W144)</f>
+        <v>8538396.11</v>
+      </c>
+      <c r="Y144" s="48" t="n">
+        <f aca="false">P144-X144</f>
+        <v>221453.890000001</v>
+      </c>
+      <c r="Z144" s="49" t="n">
+        <f aca="false">IF(X144=0,0,Y144/X144)</f>
+        <v>0.0259362399152035</v>
+      </c>
+      <c r="AA144" s="47" t="n">
+        <f aca="false">MAX(0,(P144/(1+Assumptions!$B$27)-(L144*(Assumptions!$B$4+IF(H144="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N144*Assumptions!$B$9+Assumptions!$B$10)))-P144*(Assumptions!$B$12+Assumptions!$B$13+IF(P144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H144="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N144*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N144))</f>
+        <v>2460097.23087133</v>
+      </c>
+      <c r="AB144" s="50" t="n">
+        <f aca="false">IF(AA144&lt;=0,"no price works",D144/AA144)</f>
+        <v>1.32108599579574</v>
+      </c>
+      <c r="AC144" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK144,Assumptions!$A$36:$A$48,0))+IF(I144="Yes",Assumptions!$B$23,0)+IF(J144="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1500</v>
+      </c>
+      <c r="AD144" s="47" t="n">
+        <f aca="false">(L144)*AC144-(((D144)+(L144)*Assumptions!$B$4+IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N144)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(N144)+(L144)*AC144*(Assumptions!$B$12+Assumptions!$B$13+IF((L144)*AC144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L144)*AC144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-510710.300000001</v>
+      </c>
+      <c r="AE144" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK144,Assumptions!$A$36:$A$48,0))+IF(I144="Yes",Assumptions!$B$23,0)+IF(J144="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1650</v>
+      </c>
+      <c r="AF144" s="47" t="n">
+        <f aca="false">(L144)*AE144-(((D144)+(L144)*Assumptions!$B$4+IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N144)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(N144)+(L144)*AE144*(Assumptions!$B$12+Assumptions!$B$13+IF((L144)*AE144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L144)*AE144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>221453.890000002</v>
+      </c>
+      <c r="AG144" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK144,Assumptions!$A$36:$A$48,0))+IF(I144="Yes",Assumptions!$B$23,0)+IF(J144="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1800</v>
+      </c>
+      <c r="AH144" s="47" t="n">
+        <f aca="false">(L144)*AG144-(((D144)+(L144)*Assumptions!$B$4+IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N144)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(N144)+(L144)*AG144*(Assumptions!$B$12+Assumptions!$B$13+IF((L144)*AG144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L144)*AG144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>953618.08</v>
+      </c>
+      <c r="AI144" s="47" t="n">
+        <f aca="false">(L144)*AE144-(((D144)+(L144)*Assumptions!$B$25+IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N144)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(N144)+(L144)*AE144*(Assumptions!$B$12+Assumptions!$B$13+IF((L144)*AE144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L144)*AE144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>510197.127500001</v>
+      </c>
+      <c r="AJ144" s="47" t="n">
+        <f aca="false">(L144)*AE144-(((D144)+(L144)*Assumptions!$B$26+IF(H144="Yes",Assumptions!$B$6*(D144),(L144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N144)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(N144)+(L144)*AE144*(Assumptions!$B$12+Assumptions!$B$13+IF((L144)*AE144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L144)*AE144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>798940.365000002</v>
+      </c>
+      <c r="AK144" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL144" s="45" t="n">
+        <f aca="false">IF(G144&gt;0,G144,ROUND(F144*Assumptions!$B$18,0))</f>
+        <v>5309</v>
+      </c>
+      <c r="AM144" s="45" t="n">
+        <f aca="false">IF(H144="Yes",AL144,MAX(AL144,MIN(Assumptions!$B$20,ROUND(E144*Assumptions!$B$19,0))))</f>
+        <v>5309</v>
+      </c>
+      <c r="AN144" s="47" t="n">
+        <f aca="false">(AL144)*AE144-(((D144)+(AL144)*Assumptions!$B$4+IF(H144="Yes",Assumptions!$B$6*(D144),(AL144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(Assumptions!$B$21)+(AL144)*AE144*(Assumptions!$B$12+Assumptions!$B$13+IF((AL144)*AE144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL144)*AE144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>221453.890000002</v>
+      </c>
+      <c r="AO144" s="47" t="n">
+        <f aca="false">(AM144)*AE144-(((D144)+(AM144)*Assumptions!$B$4+IF(H144="Yes",Assumptions!$B$6*(D144),(AM144)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM144&gt;AL144,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D144)*Assumptions!$B$11*(IF(AM144&gt;AL144,Assumptions!$B$22,Assumptions!$B$21))+(AM144)*AE144*(Assumptions!$B$12+Assumptions!$B$13+IF((AM144)*AE144&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM144)*AE144&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>221453.890000002</v>
+      </c>
+      <c r="AP144" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q144+R144+S144)</f>
+        <v>4633720</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="40" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="C145" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D145" s="41" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="E145" s="42" t="n">
+        <v>8753</v>
+      </c>
+      <c r="F145" s="42" t="n">
+        <v>3450</v>
+      </c>
+      <c r="G145" s="42"/>
+      <c r="H145" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="I145" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J145" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K145" s="44" t="s">
+        <v>315</v>
+      </c>
+      <c r="L145" s="45" t="n">
+        <f aca="false">IF(AO145&gt;AN145,AM145,AL145)</f>
+        <v>3795</v>
+      </c>
+      <c r="M145" s="40" t="str">
+        <f aca="false">IF(AO145&gt;AN145,"Zoning estimate",IF(H145="Yes","Approved plans",IF(G145&gt;0,"Listing claim","110% old house")))</f>
+        <v>110% old house</v>
+      </c>
+      <c r="N145" s="45" t="n">
+        <f aca="false">IF(AO145&gt;AN145,IF(AM145&gt;AL145,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O145" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK145,Assumptions!$A$36:$A$48,0))+IF(I145="Yes",Assumptions!$B$23,0)+IF(J145="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1540</v>
+      </c>
+      <c r="P145" s="47" t="n">
+        <f aca="false">L145*O145</f>
+        <v>5844300</v>
+      </c>
+      <c r="Q145" s="47" t="n">
+        <f aca="false">D145</f>
+        <v>3500000</v>
+      </c>
+      <c r="R145" s="47" t="n">
+        <f aca="false">L145*Assumptions!$B$4</f>
+        <v>2656500</v>
+      </c>
+      <c r="S145" s="47" t="n">
+        <f aca="false">IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5)</f>
+        <v>284625</v>
+      </c>
+      <c r="T145" s="47" t="n">
+        <f aca="false">AP145*(Assumptions!$B$8*N145*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>565208.71875</v>
+      </c>
+      <c r="U145" s="47" t="n">
+        <f aca="false">Q145*Assumptions!$B$11*N145</f>
+        <v>84000</v>
+      </c>
+      <c r="V145" s="47" t="n">
+        <f aca="false">P145*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>237278.58</v>
+      </c>
+      <c r="W145" s="47" t="n">
+        <f aca="false">P145*IF(P145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>233772</v>
+      </c>
+      <c r="X145" s="48" t="n">
+        <f aca="false">SUM(Q145:W145)</f>
+        <v>7561384.29875</v>
+      </c>
+      <c r="Y145" s="48" t="n">
+        <f aca="false">P145-X145</f>
+        <v>-1717084.29875</v>
+      </c>
+      <c r="Z145" s="49" t="n">
+        <f aca="false">IF(X145=0,0,Y145/X145)</f>
+        <v>-0.227085971418469</v>
+      </c>
+      <c r="AA145" s="47" t="n">
+        <f aca="false">MAX(0,(P145/(1+Assumptions!$B$27)-(L145*(Assumptions!$B$4+IF(H145="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N145*Assumptions!$B$9+Assumptions!$B$10)))-P145*(Assumptions!$B$12+Assumptions!$B$13+IF(P145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H145="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N145*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N145))</f>
+        <v>1269836.47515179</v>
+      </c>
+      <c r="AB145" s="50" t="n">
+        <f aca="false">IF(AA145&lt;=0,"no price works",D145/AA145)</f>
+        <v>2.75626040713757</v>
+      </c>
+      <c r="AC145" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK145,Assumptions!$A$36:$A$48,0))+IF(I145="Yes",Assumptions!$B$23,0)+IF(J145="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1400</v>
+      </c>
+      <c r="AD145" s="47" t="n">
+        <f aca="false">(L145)*AC145-(((D145)+(L145)*Assumptions!$B$4+IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N145)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(N145)+(L145)*AC145*(Assumptions!$B$12+Assumptions!$B$13+IF((L145)*AC145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L145)*AC145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1993041.51875</v>
+      </c>
+      <c r="AE145" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK145,Assumptions!$A$36:$A$48,0))+IF(I145="Yes",Assumptions!$B$23,0)+IF(J145="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1540</v>
+      </c>
+      <c r="AF145" s="47" t="n">
+        <f aca="false">(L145)*AE145-(((D145)+(L145)*Assumptions!$B$4+IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N145)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(N145)+(L145)*AE145*(Assumptions!$B$12+Assumptions!$B$13+IF((L145)*AE145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L145)*AE145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1717084.29875</v>
+      </c>
+      <c r="AG145" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK145,Assumptions!$A$36:$A$48,0))+IF(I145="Yes",Assumptions!$B$23,0)+IF(J145="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1680</v>
+      </c>
+      <c r="AH145" s="47" t="n">
+        <f aca="false">(L145)*AG145-(((D145)+(L145)*Assumptions!$B$4+IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N145)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(N145)+(L145)*AG145*(Assumptions!$B$12+Assumptions!$B$13+IF((L145)*AG145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L145)*AG145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1228607.07875</v>
+      </c>
+      <c r="AI145" s="47" t="n">
+        <f aca="false">(L145)*AE145-(((D145)+(L145)*Assumptions!$B$25+IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N145)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(N145)+(L145)*AE145*(Assumptions!$B$12+Assumptions!$B$13+IF((L145)*AE145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L145)*AE145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1510683.73625</v>
+      </c>
+      <c r="AJ145" s="47" t="n">
+        <f aca="false">(L145)*AE145-(((D145)+(L145)*Assumptions!$B$26+IF(H145="Yes",Assumptions!$B$6*(D145),(L145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N145)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(N145)+(L145)*AE145*(Assumptions!$B$12+Assumptions!$B$13+IF((L145)*AE145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L145)*AE145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1304283.17375</v>
+      </c>
+      <c r="AK145" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="AL145" s="45" t="n">
+        <f aca="false">IF(G145&gt;0,G145,ROUND(F145*Assumptions!$B$18,0))</f>
+        <v>3795</v>
+      </c>
+      <c r="AM145" s="45" t="n">
+        <f aca="false">IF(H145="Yes",AL145,MAX(AL145,MIN(Assumptions!$B$20,ROUND(E145*Assumptions!$B$19,0))))</f>
+        <v>3795</v>
+      </c>
+      <c r="AN145" s="47" t="n">
+        <f aca="false">(AL145)*AE145-(((D145)+(AL145)*Assumptions!$B$4+IF(H145="Yes",Assumptions!$B$6*(D145),(AL145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(Assumptions!$B$21)+(AL145)*AE145*(Assumptions!$B$12+Assumptions!$B$13+IF((AL145)*AE145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL145)*AE145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1717084.29875</v>
+      </c>
+      <c r="AO145" s="47" t="n">
+        <f aca="false">(AM145)*AE145-(((D145)+(AM145)*Assumptions!$B$4+IF(H145="Yes",Assumptions!$B$6*(D145),(AM145)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM145&gt;AL145,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D145)*Assumptions!$B$11*(IF(AM145&gt;AL145,Assumptions!$B$22,Assumptions!$B$21))+(AM145)*AE145*(Assumptions!$B$12+Assumptions!$B$13+IF((AM145)*AE145&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM145)*AE145&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1717084.29875</v>
+      </c>
+      <c r="AP145" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q145+R145+S145)</f>
+        <v>4186731.25</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="40" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="40" t="s">
+        <v>316</v>
+      </c>
+      <c r="C146" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D146" s="41" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="E146" s="42" t="n">
+        <v>8439</v>
+      </c>
+      <c r="F146" s="42" t="n">
+        <v>3247</v>
+      </c>
+      <c r="G146" s="42"/>
+      <c r="H146" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="I146" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J146" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K146" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="L146" s="45" t="n">
+        <f aca="false">IF(AO146&gt;AN146,AM146,AL146)</f>
+        <v>3572</v>
+      </c>
+      <c r="M146" s="40" t="str">
+        <f aca="false">IF(AO146&gt;AN146,"Zoning estimate",IF(H146="Yes","Approved plans",IF(G146&gt;0,"Listing claim","110% old house")))</f>
+        <v>110% old house</v>
+      </c>
+      <c r="N146" s="45" t="n">
+        <f aca="false">IF(AO146&gt;AN146,IF(AM146&gt;AL146,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O146" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK146,Assumptions!$A$36:$A$48,0))+IF(I146="Yes",Assumptions!$B$23,0)+IF(J146="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1540</v>
+      </c>
+      <c r="P146" s="47" t="n">
+        <f aca="false">L146*O146</f>
+        <v>5500880</v>
+      </c>
+      <c r="Q146" s="47" t="n">
+        <f aca="false">D146</f>
+        <v>3500000</v>
+      </c>
+      <c r="R146" s="47" t="n">
+        <f aca="false">L146*Assumptions!$B$4</f>
+        <v>2500400</v>
+      </c>
+      <c r="S146" s="47" t="n">
+        <f aca="false">IF(H146="Yes",Assumptions!$B$6*(D146),(L146)*Assumptions!$B$5)</f>
+        <v>267900</v>
+      </c>
+      <c r="T146" s="47" t="n">
+        <f aca="false">AP146*(Assumptions!$B$8*N146*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>550043.325</v>
+      </c>
+      <c r="U146" s="47" t="n">
+        <f aca="false">Q146*Assumptions!$B$11*N146</f>
+        <v>84000</v>
+      </c>
+      <c r="V146" s="47" t="n">
+        <f aca="false">P146*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>223335.728</v>
+      </c>
+      <c r="W146" s="47" t="n">
+        <f aca="false">P146*IF(P146&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P146&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>220035.2</v>
+      </c>
+      <c r="X146" s="48" t="n">
+        <f aca="false">SUM(Q146:W146)</f>
+        <v>7345714.253</v>
+      </c>
+      <c r="Y146" s="48" t="n">
+        <f aca="false">P146-X146</f>
+        <v>-1844834.253</v>
+      </c>
+      <c r="Z146" s="49" t="n">
+        <f aca="false">IF(X146=0,0,Y146/X146)</f>
+        <v>-0.251144298493039</v>
+      </c>
+      <c r="AA146" s="47" t="n">
+        <f aca="false">MAX(0,(P146/(1+Assumptions!$B$27)-(L146*(Assumptions!$B$4+IF(H146="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N146*Assumptions!$B$9+Assumptions!$B$10)))-P146*(Assumptions!$B$12+Assumptions!$B$13+IF(P146&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P146&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H146="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N146*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N146))</f>
+        <v>1195218.94314682</v>
+      </c>
+      <c r="AB146" s="50" t="n">
+        <f aca="false">IF(AA146&lt;=0,"no price works",D146/AA146)</f>
+        <v>2.92833377522034</v>
+      </c>
+      <c r="AC146" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK146,Assumptions!$A$36:$A$48,0))+IF(I146="Yes",Assumptions!$B$23,0)+IF(J146="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1400</v>
+      </c>
+      <c r="AD146" s="47" t="n">
+        <f aca="false">(L146)*AC146-(((D146)+(L146)*Assumptions!$B$4+IF(H146="Yes",Assumptions!$B$6*(D146),(L146)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N146)*Assumptions!$B$9+Assumptions!$B$10))+(D146)*Assumptions!$B$11*(N146)+(L146)*AC146*(Assumptions!$B$12+Assumptions!$B$13+IF((L146)*AC146&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L146)*AC146&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-2104575.805</v>
+      </c>
+      <c r="AE146" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK146,Assumptions!$A$36:$A$48,0))+IF(I146="Yes",Assumptions!$B$23,0)+IF(J146="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1540</v>
+      </c>
+      <c r="AF146" s="47" t="n">
+        <f aca="false">(L146)*AE146-(((D146)+(L146)*Assumptions!$B$4+IF(H146="Yes",Assumptions!$B$6*(D146),(L146)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N146)*Assumptions!$B$9+Assumptions!$B$10))+(D146)*Assumptions!$B$11*(N146)+(L146)*AE146*(Assumptions!$B$12+Assumptions!$B$13+IF((L146)*AE146&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L146)*AE146&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1844834.253</v>
+      </c>
+      <c r="AG146" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK146,Assumptions!$A$36:$A$48,0))+IF(I146="Yes",Assumptions!$B$23,0)+IF(J146="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1680</v>
+      </c>
+      <c r="AH146" s="47" t="n">
+        <f aca="false">(L146)*AG146-(((D146)+(L146)*Assumptions!$B$4+IF(H146="Yes",Assumptions!$B$6*(D146),(L146)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N146)*Assumptions!$B$9+Assumptions!$B$10))+(D146)*Assumptions!$B$11*(N146)+(L146)*AG146*(Assumptions!$B$12+Assumptions!$B$13+IF((L146)*AG146&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L146)*AG146&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1385060.701</v>
+      </c>
+      <c r="AI146" s="47" t="n">
+        <f aca="false">(L146)*AE146-(((D146)+(L146)*Assumptions!$B$25+IF(H146="Yes",Assumptions!$B$6*(D146),(L146)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N146)*Assumptions!$B$9+Assumptions!$B$10))+(D146)*Assumptions!$B$11*(N146)+(L146)*AE146*(Assumptions!$B$12+Assumptions!$B$13+IF((L146)*AE146&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L146)*AE146&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1650562.103</v>
+      </c>
+      <c r="AJ146" s="47" t="n">
+        <f aca="false">(L146)*AE146-(((D146)+(L146)*Assumptions!$B$26+IF(H146="Yes",Assumptions!$B$6*(D146),(L146)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N146)*Assumptions!$B$9+Assumptions!$B$10))+(D146)*Assumptions!$B$11*(N146)+(L146)*AE146*(Assumptions!$B$12+Assumptions!$B$13+IF((L146)*AE146&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L146)*AE146&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1456289.953</v>
+      </c>
+      <c r="AK146" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="AL146" s="45" t="n">
+        <f aca="false">IF(G146&gt;0,G146,ROUND(F146*Assumptions!$B$18,0))</f>
+        <v>3572</v>
+      </c>
+      <c r="AM146" s="45" t="n">
+        <f aca="false">IF(H146="Yes",AL146,MAX(AL146,MIN(Assumptions!$B$20,ROUND(E146*Assumptions!$B$19,0))))</f>
+        <v>3572</v>
+      </c>
+      <c r="AN146" s="47" t="n">
+        <f aca="false">(AL146)*AE146-(((D146)+(AL146)*Assumptions!$B$4+IF(H146="Yes",Assumptions!$B$6*(D146),(AL146)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D146)*Assumptions!$B$11*(Assumptions!$B$21)+(AL146)*AE146*(Assumptions!$B$12+Assumptions!$B$13+IF((AL146)*AE146&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL146)*AE146&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1844834.253</v>
+      </c>
+      <c r="AO146" s="47" t="n">
+        <f aca="false">(AM146)*AE146-(((D146)+(AM146)*Assumptions!$B$4+IF(H146="Yes",Assumptions!$B$6*(D146),(AM146)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM146&gt;AL146,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D146)*Assumptions!$B$11*(IF(AM146&gt;AL146,Assumptions!$B$22,Assumptions!$B$21))+(AM146)*AE146*(Assumptions!$B$12+Assumptions!$B$13+IF((AM146)*AE146&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM146)*AE146&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1844834.253</v>
+      </c>
+      <c r="AP146" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q146+R146+S146)</f>
+        <v>4074395</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="40" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="40" t="s">
+        <v>318</v>
+      </c>
+      <c r="C147" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D147" s="41" t="n">
+        <v>6895000</v>
+      </c>
+      <c r="E147" s="42" t="n">
+        <v>29285</v>
+      </c>
+      <c r="F147" s="42" t="n">
+        <v>3417</v>
+      </c>
+      <c r="G147" s="42"/>
+      <c r="H147" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="I147" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J147" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K147" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="L147" s="45" t="n">
+        <f aca="false">IF(AO147&gt;AN147,AM147,AL147)</f>
+        <v>8000</v>
+      </c>
+      <c r="M147" s="40" t="str">
+        <f aca="false">IF(AO147&gt;AN147,"Zoning estimate",IF(H147="Yes","Approved plans",IF(G147&gt;0,"Listing claim","110% old house")))</f>
+        <v>Zoning estimate</v>
+      </c>
+      <c r="N147" s="45" t="n">
+        <f aca="false">IF(AO147&gt;AN147,IF(AM147&gt;AL147,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>3</v>
+      </c>
+      <c r="O147" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK147,Assumptions!$A$36:$A$48,0))+IF(I147="Yes",Assumptions!$B$23,0)+IF(J147="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1485</v>
+      </c>
+      <c r="P147" s="47" t="n">
+        <f aca="false">L147*O147</f>
+        <v>11880000</v>
+      </c>
+      <c r="Q147" s="47" t="n">
+        <f aca="false">D147</f>
+        <v>6895000</v>
+      </c>
+      <c r="R147" s="47" t="n">
+        <f aca="false">L147*Assumptions!$B$4</f>
+        <v>5600000</v>
+      </c>
+      <c r="S147" s="47" t="n">
+        <f aca="false">IF(H147="Yes",Assumptions!$B$6*(D147),(L147)*Assumptions!$B$5)</f>
+        <v>600000</v>
+      </c>
+      <c r="T147" s="47" t="n">
+        <f aca="false">AP147*(Assumptions!$B$8*N147*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>1659791.25</v>
+      </c>
+      <c r="U147" s="47" t="n">
+        <f aca="false">Q147*Assumptions!$B$11*N147</f>
+        <v>248220</v>
+      </c>
+      <c r="V147" s="47" t="n">
+        <f aca="false">P147*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>482328</v>
+      </c>
+      <c r="W147" s="47" t="n">
+        <f aca="false">P147*IF(P147&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P147&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>653400</v>
+      </c>
+      <c r="X147" s="48" t="n">
+        <f aca="false">SUM(Q147:W147)</f>
+        <v>16138739.25</v>
+      </c>
+      <c r="Y147" s="48" t="n">
+        <f aca="false">P147-X147</f>
+        <v>-4258739.25</v>
+      </c>
+      <c r="Z147" s="49" t="n">
+        <f aca="false">IF(X147=0,0,Y147/X147)</f>
+        <v>-0.263883019858568</v>
+      </c>
+      <c r="AA147" s="47" t="n">
+        <f aca="false">MAX(0,(P147/(1+Assumptions!$B$27)-(L147*(Assumptions!$B$4+IF(H147="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N147*Assumptions!$B$9+Assumptions!$B$10)))-P147*(Assumptions!$B$12+Assumptions!$B$13+IF(P147&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P147&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H147="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N147*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N147))</f>
+        <v>1899683.32195975</v>
+      </c>
+      <c r="AB147" s="50" t="n">
+        <f aca="false">IF(AA147&lt;=0,"no price works",D147/AA147)</f>
+        <v>3.62955231553383</v>
+      </c>
+      <c r="AC147" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK147,Assumptions!$A$36:$A$48,0))+IF(I147="Yes",Assumptions!$B$23,0)+IF(J147="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1350</v>
+      </c>
+      <c r="AD147" s="47" t="n">
+        <f aca="false">(L147)*AC147-(((D147)+(L147)*Assumptions!$B$4+IF(H147="Yes",Assumptions!$B$6*(D147),(L147)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N147)*Assumptions!$B$9+Assumptions!$B$10))+(D147)*Assumptions!$B$11*(N147)+(L147)*AC147*(Assumptions!$B$12+Assumptions!$B$13+IF((L147)*AC147&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L147)*AC147&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-5073491.25</v>
+      </c>
+      <c r="AE147" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK147,Assumptions!$A$36:$A$48,0))+IF(I147="Yes",Assumptions!$B$23,0)+IF(J147="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1485</v>
+      </c>
+      <c r="AF147" s="47" t="n">
+        <f aca="false">(L147)*AE147-(((D147)+(L147)*Assumptions!$B$4+IF(H147="Yes",Assumptions!$B$6*(D147),(L147)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N147)*Assumptions!$B$9+Assumptions!$B$10))+(D147)*Assumptions!$B$11*(N147)+(L147)*AE147*(Assumptions!$B$12+Assumptions!$B$13+IF((L147)*AE147&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L147)*AE147&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-4258739.25</v>
+      </c>
+      <c r="AG147" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK147,Assumptions!$A$36:$A$48,0))+IF(I147="Yes",Assumptions!$B$23,0)+IF(J147="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1620</v>
+      </c>
+      <c r="AH147" s="47" t="n">
+        <f aca="false">(L147)*AG147-(((D147)+(L147)*Assumptions!$B$4+IF(H147="Yes",Assumptions!$B$6*(D147),(L147)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N147)*Assumptions!$B$9+Assumptions!$B$10))+(D147)*Assumptions!$B$11*(N147)+(L147)*AG147*(Assumptions!$B$12+Assumptions!$B$13+IF((L147)*AG147&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L147)*AG147&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-3281987.25</v>
+      </c>
+      <c r="AI147" s="47" t="n">
+        <f aca="false">(L147)*AE147-(((D147)+(L147)*Assumptions!$B$25+IF(H147="Yes",Assumptions!$B$6*(D147),(L147)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N147)*Assumptions!$B$9+Assumptions!$B$10))+(D147)*Assumptions!$B$11*(N147)+(L147)*AE147*(Assumptions!$B$12+Assumptions!$B$13+IF((L147)*AE147&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L147)*AE147&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-3808039.25</v>
+      </c>
+      <c r="AJ147" s="47" t="n">
+        <f aca="false">(L147)*AE147-(((D147)+(L147)*Assumptions!$B$26+IF(H147="Yes",Assumptions!$B$6*(D147),(L147)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N147)*Assumptions!$B$9+Assumptions!$B$10))+(D147)*Assumptions!$B$11*(N147)+(L147)*AE147*(Assumptions!$B$12+Assumptions!$B$13+IF((L147)*AE147&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L147)*AE147&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-3357339.25</v>
+      </c>
+      <c r="AK147" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL147" s="45" t="n">
+        <f aca="false">IF(G147&gt;0,G147,ROUND(F147*Assumptions!$B$18,0))</f>
+        <v>3759</v>
+      </c>
+      <c r="AM147" s="45" t="n">
+        <f aca="false">IF(H147="Yes",AL147,MAX(AL147,MIN(Assumptions!$B$20,ROUND(E147*Assumptions!$B$19,0))))</f>
+        <v>8000</v>
+      </c>
+      <c r="AN147" s="47" t="n">
+        <f aca="false">(AL147)*AE147-(((D147)+(AL147)*Assumptions!$B$4+IF(H147="Yes",Assumptions!$B$6*(D147),(AL147)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D147)*Assumptions!$B$11*(Assumptions!$B$21)+(AL147)*AE147*(Assumptions!$B$12+Assumptions!$B$13+IF((AL147)*AE147&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL147)*AE147&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-5702180.21275</v>
+      </c>
+      <c r="AO147" s="47" t="n">
+        <f aca="false">(AM147)*AE147-(((D147)+(AM147)*Assumptions!$B$4+IF(H147="Yes",Assumptions!$B$6*(D147),(AM147)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM147&gt;AL147,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D147)*Assumptions!$B$11*(IF(AM147&gt;AL147,Assumptions!$B$22,Assumptions!$B$21))+(AM147)*AE147*(Assumptions!$B$12+Assumptions!$B$13+IF((AM147)*AE147&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM147)*AE147&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-4258739.25</v>
+      </c>
+      <c r="AP147" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q147+R147+S147)</f>
+        <v>8511750</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="40" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="40" t="s">
+        <v>320</v>
+      </c>
+      <c r="C148" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D148" s="41" t="n">
+        <v>2995000</v>
+      </c>
+      <c r="E148" s="42" t="n">
+        <v>9753</v>
+      </c>
+      <c r="F148" s="42" t="n">
+        <v>2448</v>
+      </c>
+      <c r="G148" s="42"/>
+      <c r="H148" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="I148" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J148" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K148" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="L148" s="45" t="n">
+        <f aca="false">IF(AO148&gt;AN148,AM148,AL148)</f>
+        <v>3901</v>
+      </c>
+      <c r="M148" s="40" t="str">
+        <f aca="false">IF(AO148&gt;AN148,"Zoning estimate",IF(H148="Yes","Approved plans",IF(G148&gt;0,"Listing claim","110% old house")))</f>
+        <v>Zoning estimate</v>
+      </c>
+      <c r="N148" s="45" t="n">
+        <f aca="false">IF(AO148&gt;AN148,IF(AM148&gt;AL148,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>3</v>
+      </c>
+      <c r="O148" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK148,Assumptions!$A$36:$A$48,0))+IF(I148="Yes",Assumptions!$B$23,0)+IF(J148="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1540</v>
+      </c>
+      <c r="P148" s="47" t="n">
+        <f aca="false">L148*O148</f>
+        <v>6007540</v>
+      </c>
+      <c r="Q148" s="47" t="n">
+        <f aca="false">D148</f>
+        <v>2995000</v>
+      </c>
+      <c r="R148" s="47" t="n">
+        <f aca="false">L148*Assumptions!$B$4</f>
+        <v>2730700</v>
+      </c>
+      <c r="S148" s="47" t="n">
+        <f aca="false">IF(H148="Yes",Assumptions!$B$6*(D148),(L148)*Assumptions!$B$5)</f>
+        <v>292575</v>
+      </c>
+      <c r="T148" s="47" t="n">
+        <f aca="false">AP148*(Assumptions!$B$8*N148*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>762816.35625</v>
+      </c>
+      <c r="U148" s="47" t="n">
+        <f aca="false">Q148*Assumptions!$B$11*N148</f>
+        <v>107820</v>
+      </c>
+      <c r="V148" s="47" t="n">
+        <f aca="false">P148*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>243906.124</v>
+      </c>
+      <c r="W148" s="47" t="n">
+        <f aca="false">P148*IF(P148&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P148&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>240301.6</v>
+      </c>
+      <c r="X148" s="48" t="n">
+        <f aca="false">SUM(Q148:W148)</f>
+        <v>7373119.08025</v>
+      </c>
+      <c r="Y148" s="48" t="n">
+        <f aca="false">P148-X148</f>
+        <v>-1365579.08025</v>
+      </c>
+      <c r="Z148" s="49" t="n">
+        <f aca="false">IF(X148=0,0,Y148/X148)</f>
+        <v>-0.185210501198591</v>
+      </c>
+      <c r="AA148" s="47" t="n">
+        <f aca="false">MAX(0,(P148/(1+Assumptions!$B$27)-(L148*(Assumptions!$B$4+IF(H148="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N148*Assumptions!$B$9+Assumptions!$B$10)))-P148*(Assumptions!$B$12+Assumptions!$B$13+IF(P148&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P148&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H148="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N148*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N148))</f>
+        <v>1146648.0291008</v>
+      </c>
+      <c r="AB148" s="50" t="n">
+        <f aca="false">IF(AA148&lt;=0,"no price works",D148/AA148)</f>
+        <v>2.61196105865953</v>
+      </c>
+      <c r="AC148" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK148,Assumptions!$A$36:$A$48,0))+IF(I148="Yes",Assumptions!$B$23,0)+IF(J148="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1400</v>
+      </c>
+      <c r="AD148" s="47" t="n">
+        <f aca="false">(L148)*AC148-(((D148)+(L148)*Assumptions!$B$4+IF(H148="Yes",Assumptions!$B$6*(D148),(L148)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N148)*Assumptions!$B$9+Assumptions!$B$10))+(D148)*Assumptions!$B$11*(N148)+(L148)*AC148*(Assumptions!$B$12+Assumptions!$B$13+IF((L148)*AC148&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L148)*AC148&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1867700.19625</v>
+      </c>
+      <c r="AE148" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK148,Assumptions!$A$36:$A$48,0))+IF(I148="Yes",Assumptions!$B$23,0)+IF(J148="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1540</v>
+      </c>
+      <c r="AF148" s="47" t="n">
+        <f aca="false">(L148)*AE148-(((D148)+(L148)*Assumptions!$B$4+IF(H148="Yes",Assumptions!$B$6*(D148),(L148)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N148)*Assumptions!$B$9+Assumptions!$B$10))+(D148)*Assumptions!$B$11*(N148)+(L148)*AE148*(Assumptions!$B$12+Assumptions!$B$13+IF((L148)*AE148&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L148)*AE148&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1365579.08025</v>
+      </c>
+      <c r="AG148" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK148,Assumptions!$A$36:$A$48,0))+IF(I148="Yes",Assumptions!$B$23,0)+IF(J148="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1680</v>
+      </c>
+      <c r="AH148" s="47" t="n">
+        <f aca="false">(L148)*AG148-(((D148)+(L148)*Assumptions!$B$4+IF(H148="Yes",Assumptions!$B$6*(D148),(L148)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N148)*Assumptions!$B$9+Assumptions!$B$10))+(D148)*Assumptions!$B$11*(N148)+(L148)*AG148*(Assumptions!$B$12+Assumptions!$B$13+IF((L148)*AG148&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L148)*AG148&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-863457.964249999</v>
+      </c>
+      <c r="AI148" s="47" t="n">
+        <f aca="false">(L148)*AE148-(((D148)+(L148)*Assumptions!$B$25+IF(H148="Yes",Assumptions!$B$6*(D148),(L148)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N148)*Assumptions!$B$9+Assumptions!$B$10))+(D148)*Assumptions!$B$11*(N148)+(L148)*AE148*(Assumptions!$B$12+Assumptions!$B$13+IF((L148)*AE148&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L148)*AE148&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1145806.49275</v>
+      </c>
+      <c r="AJ148" s="47" t="n">
+        <f aca="false">(L148)*AE148-(((D148)+(L148)*Assumptions!$B$26+IF(H148="Yes",Assumptions!$B$6*(D148),(L148)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N148)*Assumptions!$B$9+Assumptions!$B$10))+(D148)*Assumptions!$B$11*(N148)+(L148)*AE148*(Assumptions!$B$12+Assumptions!$B$13+IF((L148)*AE148&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L148)*AE148&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-926033.905249999</v>
+      </c>
+      <c r="AK148" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="AL148" s="45" t="n">
+        <f aca="false">IF(G148&gt;0,G148,ROUND(F148*Assumptions!$B$18,0))</f>
+        <v>2693</v>
+      </c>
+      <c r="AM148" s="45" t="n">
+        <f aca="false">IF(H148="Yes",AL148,MAX(AL148,MIN(Assumptions!$B$20,ROUND(E148*Assumptions!$B$19,0))))</f>
+        <v>3901</v>
+      </c>
+      <c r="AN148" s="47" t="n">
+        <f aca="false">(AL148)*AE148-(((D148)+(AL148)*Assumptions!$B$4+IF(H148="Yes",Assumptions!$B$6*(D148),(AL148)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D148)*Assumptions!$B$11*(Assumptions!$B$21)+(AL148)*AE148*(Assumptions!$B$12+Assumptions!$B$13+IF((AL148)*AE148&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL148)*AE148&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1621064.21325</v>
+      </c>
+      <c r="AO148" s="47" t="n">
+        <f aca="false">(AM148)*AE148-(((D148)+(AM148)*Assumptions!$B$4+IF(H148="Yes",Assumptions!$B$6*(D148),(AM148)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM148&gt;AL148,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D148)*Assumptions!$B$11*(IF(AM148&gt;AL148,Assumptions!$B$22,Assumptions!$B$21))+(AM148)*AE148*(Assumptions!$B$12+Assumptions!$B$13+IF((AM148)*AE148&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM148)*AE148&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-1365579.08025</v>
+      </c>
+      <c r="AP148" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q148+R148+S148)</f>
+        <v>3911878.75</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="40" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="40" t="s">
+        <v>322</v>
+      </c>
+      <c r="C149" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D149" s="41" t="n">
+        <v>1299000</v>
+      </c>
+      <c r="E149" s="42" t="n">
+        <v>3747</v>
+      </c>
+      <c r="F149" s="42" t="n">
+        <v>1776</v>
+      </c>
+      <c r="G149" s="42"/>
+      <c r="H149" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="I149" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J149" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="K149" s="44" t="s">
+        <v>323</v>
+      </c>
+      <c r="L149" s="45" t="n">
+        <f aca="false">IF(AO149&gt;AN149,AM149,AL149)</f>
+        <v>1954</v>
+      </c>
+      <c r="M149" s="40" t="str">
+        <f aca="false">IF(AO149&gt;AN149,"Zoning estimate",IF(H149="Yes","Approved plans",IF(G149&gt;0,"Listing claim","110% old house")))</f>
+        <v>110% old house</v>
+      </c>
+      <c r="N149" s="45" t="n">
+        <f aca="false">IF(AO149&gt;AN149,IF(AM149&gt;AL149,Assumptions!$B$22,Assumptions!$B$21),Assumptions!$B$21)</f>
+        <v>2</v>
+      </c>
+      <c r="O149" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK149,Assumptions!$A$36:$A$48,0))+IF(I149="Yes",Assumptions!$B$23,0)+IF(J149="Yes",Assumptions!$B$24,0))*(1+IF(UPPER(Assumptions!$B$31)="WORST",Assumptions!$B$28,IF(UPPER(Assumptions!$B$31)="BEST",Assumptions!$B$30,Assumptions!$B$29)))</f>
+        <v>1430</v>
+      </c>
+      <c r="P149" s="47" t="n">
+        <f aca="false">L149*O149</f>
+        <v>2794220</v>
+      </c>
+      <c r="Q149" s="47" t="n">
+        <f aca="false">D149</f>
+        <v>1299000</v>
+      </c>
+      <c r="R149" s="47" t="n">
+        <f aca="false">L149*Assumptions!$B$4</f>
+        <v>1367800</v>
+      </c>
+      <c r="S149" s="47" t="n">
+        <f aca="false">IF(H149="Yes",Assumptions!$B$6*(D149),(L149)*Assumptions!$B$5)</f>
+        <v>146550</v>
+      </c>
+      <c r="T149" s="47" t="n">
+        <f aca="false">AP149*(Assumptions!$B$8*N149*Assumptions!$B$9+Assumptions!$B$10)</f>
+        <v>246871.4625</v>
+      </c>
+      <c r="U149" s="47" t="n">
+        <f aca="false">Q149*Assumptions!$B$11*N149</f>
+        <v>31176</v>
+      </c>
+      <c r="V149" s="47" t="n">
+        <f aca="false">P149*(Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>113445.332</v>
+      </c>
+      <c r="W149" s="47" t="n">
+        <f aca="false">P149*IF(P149&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P149&gt;=Assumptions!$B$14,Assumptions!$B$15,0))</f>
+        <v>0</v>
+      </c>
+      <c r="X149" s="48" t="n">
+        <f aca="false">SUM(Q149:W149)</f>
+        <v>3204842.7945</v>
+      </c>
+      <c r="Y149" s="48" t="n">
+        <f aca="false">P149-X149</f>
+        <v>-410622.794499999</v>
+      </c>
+      <c r="Z149" s="49" t="n">
+        <f aca="false">IF(X149=0,0,Y149/X149)</f>
+        <v>-0.128125721238087</v>
+      </c>
+      <c r="AA149" s="47" t="n">
+        <f aca="false">MAX(0,(P149/(1+Assumptions!$B$27)-(L149*(Assumptions!$B$4+IF(H149="Yes",0,Assumptions!$B$5)))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N149*Assumptions!$B$9+Assumptions!$B$10)))-P149*(Assumptions!$B$12+Assumptions!$B$13+IF(P149&gt;=Assumptions!$B$16,Assumptions!$B$17,IF(P149&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))/((1+IF(H149="Yes",Assumptions!$B$6,0))*(1+(Assumptions!$B$7*(Assumptions!$B$8*N149*Assumptions!$B$9+Assumptions!$B$10)))+Assumptions!$B$11*N149))</f>
+        <v>601823.231157302</v>
+      </c>
+      <c r="AB149" s="50" t="n">
+        <f aca="false">IF(AA149&lt;=0,"no price works",D149/AA149)</f>
+        <v>2.15844110487731</v>
+      </c>
+      <c r="AC149" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK149,Assumptions!$A$36:$A$48,0))+IF(I149="Yes",Assumptions!$B$23,0)+IF(J149="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$28)</f>
+        <v>1300</v>
+      </c>
+      <c r="AD149" s="47" t="n">
+        <f aca="false">(L149)*AC149-(((D149)+(L149)*Assumptions!$B$4+IF(H149="Yes",Assumptions!$B$6*(D149),(L149)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N149)*Assumptions!$B$9+Assumptions!$B$10))+(D149)*Assumptions!$B$11*(N149)+(L149)*AC149*(Assumptions!$B$12+Assumptions!$B$13+IF((L149)*AC149&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L149)*AC149&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-654329.5825</v>
+      </c>
+      <c r="AE149" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK149,Assumptions!$A$36:$A$48,0))+IF(I149="Yes",Assumptions!$B$23,0)+IF(J149="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$29)</f>
+        <v>1430</v>
+      </c>
+      <c r="AF149" s="47" t="n">
+        <f aca="false">(L149)*AE149-(((D149)+(L149)*Assumptions!$B$4+IF(H149="Yes",Assumptions!$B$6*(D149),(L149)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N149)*Assumptions!$B$9+Assumptions!$B$10))+(D149)*Assumptions!$B$11*(N149)+(L149)*AE149*(Assumptions!$B$12+Assumptions!$B$13+IF((L149)*AE149&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L149)*AE149&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-410622.794499999</v>
+      </c>
+      <c r="AG149" s="46" t="n">
+        <f aca="false">(INDEX(Assumptions!$B$36:$B$48,MATCH(AK149,Assumptions!$A$36:$A$48,0))+IF(I149="Yes",Assumptions!$B$23,0)+IF(J149="Yes",Assumptions!$B$24,0))*(1+Assumptions!$B$30)</f>
+        <v>1560</v>
+      </c>
+      <c r="AH149" s="47" t="n">
+        <f aca="false">(L149)*AG149-(((D149)+(L149)*Assumptions!$B$4+IF(H149="Yes",Assumptions!$B$6*(D149),(L149)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N149)*Assumptions!$B$9+Assumptions!$B$10))+(D149)*Assumptions!$B$11*(N149)+(L149)*AG149*(Assumptions!$B$12+Assumptions!$B$13+IF((L149)*AG149&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L149)*AG149&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-166916.0065</v>
+      </c>
+      <c r="AI149" s="47" t="n">
+        <f aca="false">(L149)*AE149-(((D149)+(L149)*Assumptions!$B$25+IF(H149="Yes",Assumptions!$B$6*(D149),(L149)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N149)*Assumptions!$B$9+Assumptions!$B$10))+(D149)*Assumptions!$B$11*(N149)+(L149)*AE149*(Assumptions!$B$12+Assumptions!$B$13+IF((L149)*AE149&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L149)*AE149&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-304349.6195</v>
+      </c>
+      <c r="AJ149" s="47" t="n">
+        <f aca="false">(L149)*AE149-(((D149)+(L149)*Assumptions!$B$26+IF(H149="Yes",Assumptions!$B$6*(D149),(L149)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(N149)*Assumptions!$B$9+Assumptions!$B$10))+(D149)*Assumptions!$B$11*(N149)+(L149)*AE149*(Assumptions!$B$12+Assumptions!$B$13+IF((L149)*AE149&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((L149)*AE149&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-198076.444499999</v>
+      </c>
+      <c r="AK149" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL149" s="45" t="n">
+        <f aca="false">IF(G149&gt;0,G149,ROUND(F149*Assumptions!$B$18,0))</f>
+        <v>1954</v>
+      </c>
+      <c r="AM149" s="45" t="n">
+        <f aca="false">IF(H149="Yes",AL149,MAX(AL149,MIN(Assumptions!$B$20,ROUND(E149*Assumptions!$B$19,0))))</f>
+        <v>1954</v>
+      </c>
+      <c r="AN149" s="47" t="n">
+        <f aca="false">(AL149)*AE149-(((D149)+(AL149)*Assumptions!$B$4+IF(H149="Yes",Assumptions!$B$6*(D149),(AL149)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(Assumptions!$B$21)*Assumptions!$B$9+Assumptions!$B$10))+(D149)*Assumptions!$B$11*(Assumptions!$B$21)+(AL149)*AE149*(Assumptions!$B$12+Assumptions!$B$13+IF((AL149)*AE149&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AL149)*AE149&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-410622.794499999</v>
+      </c>
+      <c r="AO149" s="47" t="n">
+        <f aca="false">(AM149)*AE149-(((D149)+(AM149)*Assumptions!$B$4+IF(H149="Yes",Assumptions!$B$6*(D149),(AM149)*Assumptions!$B$5))*(1+Assumptions!$B$7*(Assumptions!$B$8*(IF(AM149&gt;AL149,Assumptions!$B$22,Assumptions!$B$21))*Assumptions!$B$9+Assumptions!$B$10))+(D149)*Assumptions!$B$11*(IF(AM149&gt;AL149,Assumptions!$B$22,Assumptions!$B$21))+(AM149)*AE149*(Assumptions!$B$12+Assumptions!$B$13+IF((AM149)*AE149&gt;=Assumptions!$B$16,Assumptions!$B$17,IF((AM149)*AE149&gt;=Assumptions!$B$14,Assumptions!$B$15,0))))</f>
+        <v>-410622.794499999</v>
+      </c>
+      <c r="AP149" s="47" t="n">
+        <f aca="false">Assumptions!$B$7*(Q149+R149+S149)</f>
+        <v>1828677.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AP143"/>
+  <autoFilter ref="A2:AP149"/>
   <mergeCells count="6">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="L1:P1"/>
@@ -25528,7 +26502,7 @@
     <mergeCell ref="AC1:AJ1"/>
     <mergeCell ref="AK1:AP1"/>
   </mergeCells>
-  <conditionalFormatting sqref="AB3:AB143">
+  <conditionalFormatting sqref="AB3:AB149">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(AB3),AB3&lt;=1)</formula>
     </cfRule>
@@ -25562,342 +26536,342 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="51" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B4" s="52" t="n">
         <v>700</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B5" s="52" t="n">
         <v>75</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B6" s="53" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B7" s="53" t="n">
         <v>0.65</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B8" s="53" t="n">
         <v>0.1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B9" s="53" t="n">
         <v>0.6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B10" s="53" t="n">
         <v>0.015</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B11" s="53" t="n">
         <v>0.012</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B12" s="53" t="n">
         <v>0.035</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B13" s="53" t="n">
         <v>0.0056</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B14" s="52" t="n">
         <v>5400000</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B15" s="53" t="n">
         <v>0.04</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B16" s="52" t="n">
         <v>10900000</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B17" s="53" t="n">
         <v>0.055</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B18" s="54" t="n">
         <v>1.1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B19" s="54" t="n">
         <v>0.4</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B20" s="55" t="n">
         <v>8000</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="B21" s="55" t="n">
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="B22" s="55" t="n">
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="B23" s="52" t="n">
         <v>100</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B24" s="52" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B25" s="52" t="n">
         <v>650</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B26" s="52" t="n">
         <v>600</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B27" s="53" t="n">
         <v>0.15</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="B28" s="53" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B29" s="53" t="n">
         <v>0.1</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B30" s="53" t="n">
         <v>0.2</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="57" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="51" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C35" s="51" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25908,7 +26882,7 @@
         <v>1860</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25919,18 +26893,18 @@
         <v>1850</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B38" s="52" t="n">
         <v>1750</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25941,7 +26915,7 @@
         <v>1400</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25952,7 +26926,7 @@
         <v>1400</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25963,7 +26937,7 @@
         <v>1300</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25974,7 +26948,7 @@
         <v>1250</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25985,7 +26959,7 @@
         <v>1250</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25996,7 +26970,7 @@
         <v>1250</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26007,7 +26981,7 @@
         <v>1200</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26018,7 +26992,7 @@
         <v>1000</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26029,7 +27003,7 @@
         <v>900</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26040,7 +27014,7 @@
         <v>900</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -26075,12 +27049,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="51" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="B2" s="51" t="s">
         <v>49</v>
@@ -26089,30 +27063,30 @@
         <v>9</v>
       </c>
       <c r="D2" s="51" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="G2" s="51" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="H2" s="51" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="I2" s="51" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>120</v>
@@ -26130,18 +27104,18 @@
         <v>2026</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>75</v>
@@ -26159,18 +27133,18 @@
         <v>2014</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>75</v>
@@ -26188,18 +27162,18 @@
         <v>2018</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>70</v>
@@ -26217,18 +27191,18 @@
         <v>2021</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>79</v>
@@ -26246,21 +27220,21 @@
         <v>2013</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="D8" s="58" t="n">
         <v>9735000</v>
@@ -26275,18 +27249,18 @@
         <v>2012</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>195</v>
@@ -26304,18 +27278,18 @@
         <v>2020</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>195</v>
@@ -26333,18 +27307,18 @@
         <v>2016</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>70</v>
@@ -26362,18 +27336,18 @@
         <v>2025</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>70</v>
@@ -26391,18 +27365,18 @@
         <v>2021</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>70</v>
@@ -26420,18 +27394,18 @@
         <v>2022</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>75</v>
@@ -26449,18 +27423,18 @@
         <v>2020</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>195</v>
@@ -26478,18 +27452,18 @@
         <v>2015</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>111</v>
@@ -26507,18 +27481,18 @@
         <v>2010</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>111</v>
@@ -26536,18 +27510,18 @@
         <v>2019</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>70</v>
@@ -26565,18 +27539,18 @@
         <v>2020</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>70</v>
@@ -26594,18 +27568,18 @@
         <v>2023</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>70</v>
@@ -26623,18 +27597,18 @@
         <v>2019</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>120</v>
@@ -26652,18 +27626,18 @@
         <v>2019</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>70</v>
@@ -26681,18 +27655,18 @@
         <v>2013</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>79</v>
@@ -26710,10 +27684,10 @@
         <v>2017</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26729,7 +27703,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -26742,7 +27716,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="60" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B26" s="60" t="s">
         <v>49</v>
@@ -26751,33 +27725,33 @@
         <v>9</v>
       </c>
       <c r="D26" s="60" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E26" s="60" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F26" s="60" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="G26" s="60" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="H26" s="60" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="I26" s="60" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D27" s="58" t="n">
         <v>9990000</v>
@@ -26789,24 +27763,24 @@
         <v>1523</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="D28" s="58" t="n">
         <v>4295000</v>
@@ -26818,22 +27792,22 @@
         <v>1387</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="7" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="D29" s="58" t="n">
         <v>5495000</v>
@@ -26845,24 +27819,24 @@
         <v>1390</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="D30" s="58" t="n">
         <v>4995000</v>
@@ -26874,24 +27848,24 @@
         <v>1362</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="D31" s="58" t="n">
         <v>13995000</v>
@@ -26903,24 +27877,24 @@
         <v>2149</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="D32" s="58" t="n">
         <v>5995000</v>
@@ -26932,24 +27906,24 @@
         <v>1389</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="H32" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="I32" s="7" t="s">
         <v>490</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="D33" s="58" t="n">
         <v>4498000</v>
@@ -26961,13 +27935,13 @@
         <v>1268</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
